--- a/public/files/ironbend-buyer-tracker.xlsx
+++ b/public/files/ironbend-buyer-tracker.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{AF776A23-09B8-48A0-AEAE-A9512CBBDED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Diligence Checklist'!$A$3:$G$29</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Dashboard!$A$1:$K$77</definedName>
   </definedNames>
-  <calcPr calcId="191028" iterateDelta="1E-4"/>
+  <calcPr calcId="191028" iterateDelta="1E-4" fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1461" uniqueCount="806">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1461" uniqueCount="831">
   <si>
     <t>PROJECT IRONBEND</t>
   </si>
@@ -2101,7 +2101,7 @@
     <t>Lower-middle-market PE firm with 'Environmental &amp; Industrial Services' as one of three named core sectors and 500+ investments/add-ons since 2003. Platform-and-bolt-on model suits a certification-protected niche fabricator; scale is a modest stretch above their typical minimum.</t>
   </si>
   <si>
-    <t>Stated criteria: US$10-50mm equity checks; EV range US$25-150mm — above Northline's $9-14mm indicative range, but a new lower middle-market vehicle (Kinderhook Strategic Opportunities Fund I, $1.1bn, closed 2026) may flex smaller.</t>
+    <t>Stated criteria: US$10-50mm equity checks; EV range US$25-150mm — above Northline's $9-13mm indicative range, but a new lower middle-market vehicle (Kinderhook Strategic Opportunities Fund I, $1.1bn, closed 2026) may flex smaller.</t>
   </si>
   <si>
     <t>No pipe/pressure-vessel-fabrication acquisition identified specifically.</t>
@@ -2173,7 +2173,7 @@
     <t>Established Canadian mid-market generalist sponsor (Energy Services and Equipment named as a sector of interest) with a long history of Canadian industrial deals — included for completeness, but its stated deal-size floor is well above this target.</t>
   </si>
   <si>
-    <t>Targets control/significant-minority deals valued C$75mm-$3bn (per Mergr) — roughly 5-10x larger than Northline's indicative $9-14mm EV; a size mismatch unless deployed as an add-on to an existing platform.</t>
+    <t>Targets control/significant-minority deals valued C$75mm-$3bn (per Mergr) — roughly 5-10x larger than Northline's indicative $9-13mm EV; a size mismatch unless deployed as an add-on to an existing platform.</t>
   </si>
   <si>
     <t>90 M&amp;A transactions on record; none identified in pipe/pressure-vessel fabrication specifically.</t>
@@ -2185,7 +2185,7 @@
     <t>LEGEND</t>
   </si>
   <si>
-    <t>Green = sector fit AND check size plausibly matches Northline's $9-14mm indicative EV.   Yellow = sector fit confirmed, but firm's typical/stated deal size is larger than this target — a realistic bolt-on/add-on candidate rather than a standalone lead bidder.</t>
+    <t>Green = sector fit AND check size plausibly matches Northline's $9-13mm indicative EV.   Yellow = sector fit confirmed, but firm's typical/stated deal size is larger than this target — a realistic bolt-on/add-on candidate rather than a standalone lead bidder.</t>
   </si>
   <si>
     <t>Research notes: all organizations above are real, named companies verified via public filings, company websites, and news/PE-database sources as of August 2026 (see Source column for each). Fields marked 'not publicly disclosed' reflect genuine gaps in available public data for privately held companies — left blank/noted rather than estimated. This is a screened starting universe (16 names) for further analyst diligence, not an exhaustive or final buyer list; actual check size and appetite would be confirmed through direct buyer-side conversations.</t>
@@ -2462,6 +2462,81 @@
   </si>
   <si>
     <t>Blue text = manual input (safe to edit). Dark grey/black text = formula output (leave alone). Navy header bands mark table headers. Status is shown by text styling rather than colour fills: bold navy = active / in progress, grey = not started or no longer in play, italic grey = no response / on hold. Amber bold in 'Days Since Update' flags an Active buyer with no movement for 21+ days.</t>
+  </si>
+  <si>
+    <t>1. Teaser Sent</t>
+  </si>
+  <si>
+    <t>2. NDA Signed</t>
+  </si>
+  <si>
+    <t>138 buyers in universe (122 contacted with the blind teaser + 16 newly sourced, not yet contacted)  |  Snapshot as of the Dashboard report date  |  Columns I–T = process dates (edit as milestones occur)  |  Column V (Current Stage) and W (Days Since Update) calculate automatically — do not edit  |  Column U (Status) is a dropdown</t>
+  </si>
+  <si>
+    <t>Selected buyer: LOI countersigned 21-Jul-2026 (60-day exclusivity to 19-Sep-2026); confirmatory diligence since 28-Jul-2026, see Diligence Checklist.</t>
+  </si>
+  <si>
+    <t>On Hold</t>
+  </si>
+  <si>
+    <t>Final-round bidder: submitted a competing LOI on 21-Jul-2026 that was not countersigned (weaker certainty of financing). Backup bidder; on hold during B001 exclusivity.</t>
+  </si>
+  <si>
+    <t>Final-round bidder after management meeting; did not submit an LOI by the 21-Jul deadline. On hold during B001 exclusivity.</t>
+  </si>
+  <si>
+    <t>IOI received but not advanced to management meetings (lower or less certain bid). Held in reserve during exclusivity.</t>
+  </si>
+  <si>
+    <t>Received CIM; did not submit an IOI by the round-1 deadline (18-Jun-2026).</t>
+  </si>
+  <si>
+    <t>Reviewed CIM; passed before IOIs (not a strategic fit at this time).</t>
+  </si>
+  <si>
+    <t>Received blind teaser and NDA; NDA not executed (passed on size or sector fit).</t>
+  </si>
+  <si>
+    <t>Reviewed teaser; passed before signing the NDA (not a strategic fit at this time).</t>
+  </si>
+  <si>
+    <t>No response to teaser outreach after two follow-ups.</t>
+  </si>
+  <si>
+    <t>Received blind teaser; did not sign the NDA (passed on size or sector fit).</t>
+  </si>
+  <si>
+    <t>1. Teaser</t>
+  </si>
+  <si>
+    <t>2. NDA</t>
+  </si>
+  <si>
+    <t>Top 5 customers = ~59% of revenue; largest ~18% (matches CIM)</t>
+  </si>
+  <si>
+    <t>This dashboard is fully linked to the Buyer Tracker tab — funnel counts, status mix, IOI range and the current-stage line recalculate automatically as tracker rows are updated. Manual inputs: the report date (top right) and the milestone table (Target/Actual Date, Status). See the Instructions tab.</t>
+  </si>
+  <si>
+    <t>• Dashboard — the one-pager. Shows the 9-stage deal funnel (Teaser → NDA → CIM → IOI → Management Meeting → LOI → Diligence → Definitive Agreement → Close), pipeline status mix, IOI valuation range, and the overall deal milestone timeline for Project Ironbend. Everything except the report date and the milestone table is a live formula.</t>
+  </si>
+  <si>
+    <t>• Buyer Tracker — the working tracker. 138 rows pre-loaded: 122 buyers contacted with the blind teaser, plus 16 real buyers freshly sourced from the Buyer Universe tab (Status = Not Contacted, no dates yet). Add new buyers by inserting rows within the table range (row 4 through the last data row) so formulas and formatting copy down automatically.</t>
+  </si>
+  <si>
+    <t>Buyer Tracker — edit freely (shown in blue font): columns G-T (process dates), M-N (IOI value range), U (Status dropdown), C (Type dropdown), D (Priority dropdown), X (Notes). Enter a date the moment a milestone happens (e.g. the day an NDA is countersigned goes in column J).</t>
+  </si>
+  <si>
+    <t>Dashboard — only the report date (I6) and the Target Date / Actual Date / Status cells in the 'Overall Deal Milestone Timeline' table are manual. Everything else (KPI strip, funnel, pipeline status, IOI range, current-stage line) is a formula — do not type over it.</t>
+  </si>
+  <si>
+    <t>Current Stage (Buyer Tracker, col V): checks each buyer's date columns from Close backward to Teaser Sent and returns the furthest milestone reached — no manual selection needed.</t>
+  </si>
+  <si>
+    <t>Days Since Update (col W): the Dashboard report date minus the most recent date entered for that buyer — flags stale rows in bold amber automatically if a buyer marked Active hasn't moved in 21+ days. Set the report date to today's date when you update the tracker.</t>
+  </si>
+  <si>
+    <t>Dashboard funnel counts: each stage box uses COUNT() on the corresponding Buyer Tracker date column (e.g. NDA count = COUNT of non-blank cells in column J), so it always reflects the current state of the tracker.</t>
   </si>
 </sst>
 </file>
@@ -3409,10 +3484,10 @@
               <c:strCache>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>1. NDA</c:v>
+                  <c:v>1. Teaser</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2. Teaser</c:v>
+                  <c:v>2. NDA</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>3. CIM Sent</c:v>
@@ -3445,13 +3520,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
+                  <c:v>122</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>70</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>66</c:v>
-                </c:pt>
                 <c:pt idx="2">
-                  <c:v>50</c:v>
+                  <c:v>70</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>23</c:v>
@@ -3460,7 +3535,7 @@
                   <c:v>13</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>1</c:v>
@@ -3894,13 +3969,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>71</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>32</c:v>
+                  <c:v>93</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>35</c:v>
+                  <c:v>44</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4102,7 +4177,7 @@
                   <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>10.658695652173915</c:v>
+                  <c:v>10.6586956521739</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>13.7</c:v>
@@ -4627,7 +4702,9 @@
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
-      <c r="I6" s="2"/>
+      <c r="I6" s="26">
+        <v>46244</v>
+      </c>
       <c r="J6" s="2"/>
       <c r="K6" s="16"/>
     </row>
@@ -4675,13 +4752,13 @@
       </c>
       <c r="C9" s="71"/>
       <c r="D9" s="71">
-        <f>COUNT('Buyer Tracker'!$I$4:$I$141)</f>
+        <f>COUNT('Buyer Tracker'!$J$4:$J$141)</f>
         <v>70</v>
       </c>
       <c r="E9" s="71"/>
       <c r="F9" s="71">
         <f>COUNT('Buyer Tracker'!$K$4:$K$141)</f>
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="G9" s="71"/>
       <c r="H9" s="71">
@@ -4733,10 +4810,10 @@
     <row r="12" spans="1:11" ht="25.5" customHeight="1">
       <c r="A12" s="16"/>
       <c r="B12" s="18" t="s">
-        <v>11</v>
+        <v>820</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>12</v>
+        <v>821</v>
       </c>
       <c r="D12" s="18" t="s">
         <v>13</v>
@@ -4765,15 +4842,15 @@
       <c r="A13" s="16"/>
       <c r="B13" s="19">
         <f>COUNT('Buyer Tracker'!$I$4:$I$141)</f>
-        <v>70</v>
+        <v>122</v>
       </c>
       <c r="C13" s="19">
         <f>COUNT('Buyer Tracker'!$J$4:$J$141)</f>
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D13" s="19">
         <f>COUNT('Buyer Tracker'!$K$4:$K$141)</f>
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E13" s="19">
         <f>COUNT('Buyer Tracker'!$L$4:$L$141)</f>
@@ -4785,7 +4862,7 @@
       </c>
       <c r="G13" s="19">
         <f>COUNT('Buyer Tracker'!$P$4:$P$141)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H13" s="19">
         <f>COUNT('Buyer Tracker'!$Q$4:$Q$141)</f>
@@ -4808,27 +4885,27 @@
       </c>
       <c r="C14" s="21">
         <f>IFERROR(C13/B13,0)</f>
-        <v>0.94285714285714284</v>
+        <v>0.573770491803279</v>
       </c>
       <c r="D14" s="21">
         <f>IFERROR(D13/C13,0)</f>
-        <v>0.75757575757575757</v>
+        <v>1</v>
       </c>
       <c r="E14" s="21">
         <f>IFERROR(E13/D13,0)</f>
-        <v>0.46</v>
+        <v>0.328571428571429</v>
       </c>
       <c r="F14" s="21">
         <f>IFERROR(F13/E13,0)</f>
-        <v>0.56521739130434778</v>
+        <v>0.565217391304348</v>
       </c>
       <c r="G14" s="21">
         <f>IFERROR(G13/F13,0)</f>
-        <v>0.15384615384615385</v>
+        <v>0.0769230769230769</v>
       </c>
       <c r="H14" s="21">
         <f>IFERROR(H13/G13,0)</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I14" s="21">
         <f>IFERROR(I13/H13,0)</f>
@@ -4876,7 +4953,7 @@
       <c r="C17" s="76"/>
       <c r="D17" s="22">
         <f>COUNTIF('Buyer Tracker'!$U$4:$U$141,"Active*")</f>
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="E17" s="76" t="s">
         <v>23</v>
@@ -4884,7 +4961,7 @@
       <c r="F17" s="76"/>
       <c r="G17" s="22">
         <f>COUNTIF('Buyer Tracker'!$U$4:$U$141,"Declined")+COUNTIF('Buyer Tracker'!$U$4:$U$141,"Passed")</f>
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="H17" s="76" t="s">
         <v>24</v>
@@ -4892,7 +4969,7 @@
       <c r="I17" s="76"/>
       <c r="J17" s="22">
         <f>COUNTIF('Buyer Tracker'!$U$4:$U$141,"No Response")+COUNTIF('Buyer Tracker'!$U$4:$U$141,"On Hold")+COUNTIF('Buyer Tracker'!$U$4:$U$141,"Not Contacted")</f>
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="K17" s="16"/>
     </row>
@@ -4940,7 +5017,7 @@
       <c r="F20" s="76"/>
       <c r="G20" s="23">
         <f>IFERROR((AVERAGE('Buyer Tracker'!$M$4:$M$141)+AVERAGE('Buyer Tracker'!$N$4:$N$141))/2,"n/a")</f>
-        <v>10.658695652173915</v>
+        <v>10.6586956521739</v>
       </c>
       <c r="H20" s="76" t="s">
         <v>28</v>
@@ -5009,7 +5086,7 @@
         <v>1</v>
       </c>
       <c r="C24" s="78" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D24" s="78"/>
       <c r="E24" s="78"/>
@@ -5017,7 +5094,7 @@
         <v>46083</v>
       </c>
       <c r="G24" s="26">
-        <v>46106</v>
+        <v>46083</v>
       </c>
       <c r="H24" s="79" t="s">
         <v>36</v>
@@ -5032,15 +5109,15 @@
         <v>2</v>
       </c>
       <c r="C25" s="78" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D25" s="78"/>
       <c r="E25" s="78"/>
       <c r="F25" s="26">
-        <v>46083</v>
+        <v>46097</v>
       </c>
       <c r="G25" s="26">
-        <v>46108</v>
+        <v>46106</v>
       </c>
       <c r="H25" s="79" t="s">
         <v>36</v>
@@ -5063,7 +5140,7 @@
         <v>46127</v>
       </c>
       <c r="G26" s="26">
-        <v>46162</v>
+        <v>46127</v>
       </c>
       <c r="H26" s="79" t="s">
         <v>36</v>
@@ -5109,7 +5186,7 @@
         <v>46218</v>
       </c>
       <c r="G28" s="26">
-        <v>46227</v>
+        <v>46221</v>
       </c>
       <c r="H28" s="79" t="s">
         <v>36</v>
@@ -5129,7 +5206,7 @@
       <c r="D29" s="78"/>
       <c r="E29" s="78"/>
       <c r="F29" s="26">
-        <v>46218</v>
+        <v>46223</v>
       </c>
       <c r="G29" s="26">
         <v>46224</v>
@@ -5152,7 +5229,7 @@
       <c r="D30" s="78"/>
       <c r="E30" s="78"/>
       <c r="F30" s="26">
-        <v>46280</v>
+        <v>46276</v>
       </c>
       <c r="G30" s="27" t="s">
         <v>43</v>
@@ -5175,7 +5252,7 @@
       <c r="D31" s="78"/>
       <c r="E31" s="78"/>
       <c r="F31" s="26">
-        <v>46296</v>
+        <v>46283</v>
       </c>
       <c r="G31" s="27" t="s">
         <v>43</v>
@@ -5225,8 +5302,9 @@
     </row>
     <row r="34" spans="1:11" ht="27.75" customHeight="1">
       <c r="A34" s="16"/>
-      <c r="B34" s="82" t="s">
-        <v>48</v>
+      <c r="B34" s="82" t="str">
+        <f>"Current stage: 7 — Diligence (in progress, "&amp;COUNTIF('Diligence Checklist'!E4:E29,"Complete")&amp;" of "&amp;COUNTA('Diligence Checklist'!E4:E29)&amp;" items complete). Lead buyer B001 under 60-day exclusivity from 21-Jul-2026 (to 19-Sep-2026); definitive agreement targeted 18-Sep-2026, close 31-Oct-2026."</f>
+        <v>Current stage: 7 — Diligence (in progress, 9 of 26 items complete). Lead buyer B001 under 60-day exclusivity from 21-Jul-2026 (to 19-Sep-2026); definitive agreement targeted 18-Sep-2026, close 31-Oct-2026.</v>
       </c>
       <c r="C34" s="82"/>
       <c r="D34" s="82"/>
@@ -5254,7 +5332,7 @@
     <row r="36" spans="1:11" ht="25.5" customHeight="1">
       <c r="A36" s="16"/>
       <c r="B36" s="83" t="s">
-        <v>49</v>
+        <v>823</v>
       </c>
       <c r="C36" s="83"/>
       <c r="D36" s="83"/>
@@ -5298,7 +5376,7 @@
       </c>
       <c r="C57" s="28">
         <f>D17</f>
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="E57" s="28" t="s">
         <v>53</v>
@@ -5314,14 +5392,14 @@
       </c>
       <c r="C58" s="28">
         <f>G17</f>
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="E58" s="28" t="s">
         <v>54</v>
       </c>
       <c r="F58" s="29">
         <f>G20</f>
-        <v>10.658695652173915</v>
+        <v>10.6586956521739</v>
       </c>
     </row>
     <row r="59" spans="2:10">
@@ -5330,7 +5408,7 @@
       </c>
       <c r="C59" s="28">
         <f>J17</f>
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E59" s="28" t="s">
         <v>56</v>
@@ -5467,7 +5545,7 @@
     </row>
     <row r="2" spans="1:24" ht="13.5" customHeight="1">
       <c r="A2" s="86" t="s">
-        <v>58</v>
+        <v>808</v>
       </c>
       <c r="B2" s="86"/>
       <c r="C2" s="86"/>
@@ -5519,10 +5597,10 @@
         <v>66</v>
       </c>
       <c r="I3" s="30" t="s">
-        <v>67</v>
+        <v>806</v>
       </c>
       <c r="J3" s="30" t="s">
-        <v>68</v>
+        <v>807</v>
       </c>
       <c r="K3" s="30" t="s">
         <v>13</v>
@@ -5593,10 +5671,10 @@
         <v>46111</v>
       </c>
       <c r="I4" s="34">
+        <v>46107</v>
+      </c>
+      <c r="J4" s="34">
         <v>46117</v>
-      </c>
-      <c r="J4" s="34">
-        <v>46119</v>
       </c>
       <c r="K4" s="34">
         <v>46125</v>
@@ -5620,7 +5698,8 @@
         <v>46231</v>
       </c>
       <c r="R4" s="36">
-        <v>0.6</v>
+        <f>'Diligence Checklist'!F32</f>
+        <v>0.346153846153846</v>
       </c>
       <c r="S4" s="37"/>
       <c r="T4" s="37"/>
@@ -5628,15 +5707,15 @@
         <v>83</v>
       </c>
       <c r="V4" s="39" t="str">
-        <f>IF(T4&lt;&gt;"","9 - Closed",IF(S4&lt;&gt;"","8 - Definitive Agreement",IF(Q4&lt;&gt;"","7 - Diligence",IF(P4&lt;&gt;"","6 - LOI Signed",IF(O4&lt;&gt;"","5 - Mgmt Meeting",IF(L4&lt;&gt;"","4 - IOI Received",IF(K4&lt;&gt;"","3 - CIM Sent",IF(J4&lt;&gt;"","2 - Teaser Sent",IF(I4&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
+        <f>IF(T4&lt;&gt;"","9 - Closed",IF(S4&lt;&gt;"","8 - Definitive Agreement",IF(Q4&lt;&gt;"","7 - Diligence",IF(P4&lt;&gt;"","6 - LOI Signed",IF(O4&lt;&gt;"","5 - Mgmt Meeting",IF(L4&lt;&gt;"","4 - IOI Received",IF(K4&lt;&gt;"","3 - CIM Sent",IF(J4&lt;&gt;"","2 - NDA Signed",IF(I4&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
         <v>7 - Diligence</v>
       </c>
       <c r="W4" s="39">
-        <f ca="1">IF(COUNT(G4:T4)=0,"-",TODAY()-MAX(G4:T4))</f>
-        <v>9</v>
+        <f>IF(COUNT(G4:T4)=0,"-",Dashboard!$I$6-MAX(G4:T4))</f>
+        <v>13</v>
       </c>
       <c r="X4" s="40" t="s">
-        <v>84</v>
+        <v>809</v>
       </c>
     </row>
     <row r="5" spans="1:24" ht="15" customHeight="1">
@@ -5665,7 +5744,7 @@
         <v>46095</v>
       </c>
       <c r="I5" s="34">
-        <v>46105</v>
+        <v>46091</v>
       </c>
       <c r="J5" s="34">
         <v>46105</v>
@@ -5685,26 +5764,24 @@
       <c r="O5" s="34">
         <v>46203</v>
       </c>
-      <c r="P5" s="34">
-        <v>46224</v>
-      </c>
+      <c r="P5" s="34"/>
       <c r="Q5" s="37"/>
       <c r="R5" s="33"/>
       <c r="S5" s="37"/>
       <c r="T5" s="37"/>
       <c r="U5" s="38" t="s">
-        <v>89</v>
+        <v>810</v>
       </c>
       <c r="V5" s="39" t="str">
-        <f>IF(T5&lt;&gt;"","9 - Closed",IF(S5&lt;&gt;"","8 - Definitive Agreement",IF(Q5&lt;&gt;"","7 - Diligence",IF(P5&lt;&gt;"","6 - LOI Signed",IF(O5&lt;&gt;"","5 - Mgmt Meeting",IF(L5&lt;&gt;"","4 - IOI Received",IF(K5&lt;&gt;"","3 - CIM Sent",IF(J5&lt;&gt;"","2 - Teaser Sent",IF(I5&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>6 - LOI Signed</v>
+        <f>IF(T5&lt;&gt;"","9 - Closed",IF(S5&lt;&gt;"","8 - Definitive Agreement",IF(Q5&lt;&gt;"","7 - Diligence",IF(P5&lt;&gt;"","6 - LOI Signed",IF(O5&lt;&gt;"","5 - Mgmt Meeting",IF(L5&lt;&gt;"","4 - IOI Received",IF(K5&lt;&gt;"","3 - CIM Sent",IF(J5&lt;&gt;"","2 - NDA Signed",IF(I5&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>5 - Mgmt Meeting</v>
       </c>
       <c r="W5" s="39">
-        <f ca="1">IF(COUNT(G5:T5)=0,"-",TODAY()-MAX(G5:T5))</f>
-        <v>16</v>
+        <f>IF(COUNT(G5:T5)=0,"-",Dashboard!$I$6-MAX(G5:T5))</f>
+        <v>41</v>
       </c>
       <c r="X5" s="40" t="s">
-        <v>90</v>
+        <v>811</v>
       </c>
     </row>
     <row r="6" spans="1:24" ht="15" customHeight="1">
@@ -5733,10 +5810,10 @@
         <v>46093</v>
       </c>
       <c r="I6" s="34">
+        <v>46090</v>
+      </c>
+      <c r="J6" s="34">
         <v>46101</v>
-      </c>
-      <c r="J6" s="34">
-        <v>46102</v>
       </c>
       <c r="K6" s="34">
         <v>46112</v>
@@ -5759,18 +5836,18 @@
       <c r="S6" s="37"/>
       <c r="T6" s="37"/>
       <c r="U6" s="38" t="s">
-        <v>52</v>
+        <v>810</v>
       </c>
       <c r="V6" s="39" t="str">
-        <f>IF(T6&lt;&gt;"","9 - Closed",IF(S6&lt;&gt;"","8 - Definitive Agreement",IF(Q6&lt;&gt;"","7 - Diligence",IF(P6&lt;&gt;"","6 - LOI Signed",IF(O6&lt;&gt;"","5 - Mgmt Meeting",IF(L6&lt;&gt;"","4 - IOI Received",IF(K6&lt;&gt;"","3 - CIM Sent",IF(J6&lt;&gt;"","2 - Teaser Sent",IF(I6&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
+        <f>IF(T6&lt;&gt;"","9 - Closed",IF(S6&lt;&gt;"","8 - Definitive Agreement",IF(Q6&lt;&gt;"","7 - Diligence",IF(P6&lt;&gt;"","6 - LOI Signed",IF(O6&lt;&gt;"","5 - Mgmt Meeting",IF(L6&lt;&gt;"","4 - IOI Received",IF(K6&lt;&gt;"","3 - CIM Sent",IF(J6&lt;&gt;"","2 - NDA Signed",IF(I6&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
         <v>5 - Mgmt Meeting</v>
       </c>
       <c r="W6" s="39">
-        <f ca="1">IF(COUNT(G6:T6)=0,"-",TODAY()-MAX(G6:T6))</f>
-        <v>26</v>
+        <f>IF(COUNT(G6:T6)=0,"-",Dashboard!$I$6-MAX(G6:T6))</f>
+        <v>30</v>
       </c>
       <c r="X6" s="40" t="s">
-        <v>96</v>
+        <v>812</v>
       </c>
     </row>
     <row r="7" spans="1:24" ht="15" customHeight="1">
@@ -5799,10 +5876,10 @@
         <v>46104</v>
       </c>
       <c r="I7" s="34">
+        <v>46100</v>
+      </c>
+      <c r="J7" s="34">
         <v>46108</v>
-      </c>
-      <c r="J7" s="34">
-        <v>46109</v>
       </c>
       <c r="K7" s="34">
         <v>46119</v>
@@ -5828,12 +5905,12 @@
         <v>102</v>
       </c>
       <c r="V7" s="39" t="str">
-        <f>IF(T7&lt;&gt;"","9 - Closed",IF(S7&lt;&gt;"","8 - Definitive Agreement",IF(Q7&lt;&gt;"","7 - Diligence",IF(P7&lt;&gt;"","6 - LOI Signed",IF(O7&lt;&gt;"","5 - Mgmt Meeting",IF(L7&lt;&gt;"","4 - IOI Received",IF(K7&lt;&gt;"","3 - CIM Sent",IF(J7&lt;&gt;"","2 - Teaser Sent",IF(I7&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
+        <f>IF(T7&lt;&gt;"","9 - Closed",IF(S7&lt;&gt;"","8 - Definitive Agreement",IF(Q7&lt;&gt;"","7 - Diligence",IF(P7&lt;&gt;"","6 - LOI Signed",IF(O7&lt;&gt;"","5 - Mgmt Meeting",IF(L7&lt;&gt;"","4 - IOI Received",IF(K7&lt;&gt;"","3 - CIM Sent",IF(J7&lt;&gt;"","2 - NDA Signed",IF(I7&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
         <v>5 - Mgmt Meeting</v>
       </c>
       <c r="W7" s="39">
-        <f ca="1">IF(COUNT(G7:T7)=0,"-",TODAY()-MAX(G7:T7))</f>
-        <v>21</v>
+        <f>IF(COUNT(G7:T7)=0,"-",Dashboard!$I$6-MAX(G7:T7))</f>
+        <v>25</v>
       </c>
       <c r="X7" s="40" t="s">
         <v>103</v>
@@ -5865,10 +5942,10 @@
         <v>46098</v>
       </c>
       <c r="I8" s="34">
+        <v>46095</v>
+      </c>
+      <c r="J8" s="34">
         <v>46103</v>
-      </c>
-      <c r="J8" s="34">
-        <v>46105</v>
       </c>
       <c r="K8" s="34">
         <v>46110</v>
@@ -5894,12 +5971,12 @@
         <v>102</v>
       </c>
       <c r="V8" s="39" t="str">
-        <f>IF(T8&lt;&gt;"","9 - Closed",IF(S8&lt;&gt;"","8 - Definitive Agreement",IF(Q8&lt;&gt;"","7 - Diligence",IF(P8&lt;&gt;"","6 - LOI Signed",IF(O8&lt;&gt;"","5 - Mgmt Meeting",IF(L8&lt;&gt;"","4 - IOI Received",IF(K8&lt;&gt;"","3 - CIM Sent",IF(J8&lt;&gt;"","2 - Teaser Sent",IF(I8&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
+        <f>IF(T8&lt;&gt;"","9 - Closed",IF(S8&lt;&gt;"","8 - Definitive Agreement",IF(Q8&lt;&gt;"","7 - Diligence",IF(P8&lt;&gt;"","6 - LOI Signed",IF(O8&lt;&gt;"","5 - Mgmt Meeting",IF(L8&lt;&gt;"","4 - IOI Received",IF(K8&lt;&gt;"","3 - CIM Sent",IF(J8&lt;&gt;"","2 - NDA Signed",IF(I8&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
         <v>5 - Mgmt Meeting</v>
       </c>
       <c r="W8" s="39">
-        <f ca="1">IF(COUNT(G8:T8)=0,"-",TODAY()-MAX(G8:T8))</f>
-        <v>19</v>
+        <f>IF(COUNT(G8:T8)=0,"-",Dashboard!$I$6-MAX(G8:T8))</f>
+        <v>23</v>
       </c>
       <c r="X8" s="40" t="s">
         <v>103</v>
@@ -5931,10 +6008,10 @@
         <v>46089</v>
       </c>
       <c r="I9" s="34">
+        <v>46085</v>
+      </c>
+      <c r="J9" s="34">
         <v>46097</v>
-      </c>
-      <c r="J9" s="34">
-        <v>46098</v>
       </c>
       <c r="K9" s="34">
         <v>46102</v>
@@ -5957,18 +6034,18 @@
       <c r="S9" s="37"/>
       <c r="T9" s="37"/>
       <c r="U9" s="38" t="s">
-        <v>52</v>
+        <v>810</v>
       </c>
       <c r="V9" s="39" t="str">
-        <f>IF(T9&lt;&gt;"","9 - Closed",IF(S9&lt;&gt;"","8 - Definitive Agreement",IF(Q9&lt;&gt;"","7 - Diligence",IF(P9&lt;&gt;"","6 - LOI Signed",IF(O9&lt;&gt;"","5 - Mgmt Meeting",IF(L9&lt;&gt;"","4 - IOI Received",IF(K9&lt;&gt;"","3 - CIM Sent",IF(J9&lt;&gt;"","2 - Teaser Sent",IF(I9&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
+        <f>IF(T9&lt;&gt;"","9 - Closed",IF(S9&lt;&gt;"","8 - Definitive Agreement",IF(Q9&lt;&gt;"","7 - Diligence",IF(P9&lt;&gt;"","6 - LOI Signed",IF(O9&lt;&gt;"","5 - Mgmt Meeting",IF(L9&lt;&gt;"","4 - IOI Received",IF(K9&lt;&gt;"","3 - CIM Sent",IF(J9&lt;&gt;"","2 - NDA Signed",IF(I9&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
         <v>5 - Mgmt Meeting</v>
       </c>
       <c r="W9" s="39">
-        <f ca="1">IF(COUNT(G9:T9)=0,"-",TODAY()-MAX(G9:T9))</f>
-        <v>24</v>
+        <f>IF(COUNT(G9:T9)=0,"-",Dashboard!$I$6-MAX(G9:T9))</f>
+        <v>28</v>
       </c>
       <c r="X9" s="40" t="s">
-        <v>96</v>
+        <v>812</v>
       </c>
     </row>
     <row r="10" spans="1:24" ht="15" customHeight="1">
@@ -5997,10 +6074,10 @@
         <v>46101</v>
       </c>
       <c r="I10" s="34">
+        <v>46097</v>
+      </c>
+      <c r="J10" s="34">
         <v>46104</v>
-      </c>
-      <c r="J10" s="34">
-        <v>46106</v>
       </c>
       <c r="K10" s="34">
         <v>46115</v>
@@ -6026,12 +6103,12 @@
         <v>102</v>
       </c>
       <c r="V10" s="39" t="str">
-        <f>IF(T10&lt;&gt;"","9 - Closed",IF(S10&lt;&gt;"","8 - Definitive Agreement",IF(Q10&lt;&gt;"","7 - Diligence",IF(P10&lt;&gt;"","6 - LOI Signed",IF(O10&lt;&gt;"","5 - Mgmt Meeting",IF(L10&lt;&gt;"","4 - IOI Received",IF(K10&lt;&gt;"","3 - CIM Sent",IF(J10&lt;&gt;"","2 - Teaser Sent",IF(I10&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
+        <f>IF(T10&lt;&gt;"","9 - Closed",IF(S10&lt;&gt;"","8 - Definitive Agreement",IF(Q10&lt;&gt;"","7 - Diligence",IF(P10&lt;&gt;"","6 - LOI Signed",IF(O10&lt;&gt;"","5 - Mgmt Meeting",IF(L10&lt;&gt;"","4 - IOI Received",IF(K10&lt;&gt;"","3 - CIM Sent",IF(J10&lt;&gt;"","2 - NDA Signed",IF(I10&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
         <v>5 - Mgmt Meeting</v>
       </c>
       <c r="W10" s="39">
-        <f ca="1">IF(COUNT(G10:T10)=0,"-",TODAY()-MAX(G10:T10))</f>
-        <v>36</v>
+        <f>IF(COUNT(G10:T10)=0,"-",Dashboard!$I$6-MAX(G10:T10))</f>
+        <v>40</v>
       </c>
       <c r="X10" s="40" t="s">
         <v>103</v>
@@ -6063,10 +6140,10 @@
         <v>46099</v>
       </c>
       <c r="I11" s="34">
+        <v>46096</v>
+      </c>
+      <c r="J11" s="34">
         <v>46106</v>
-      </c>
-      <c r="J11" s="34">
-        <v>46108</v>
       </c>
       <c r="K11" s="34">
         <v>46116</v>
@@ -6089,18 +6166,18 @@
       <c r="S11" s="37"/>
       <c r="T11" s="37"/>
       <c r="U11" s="38" t="s">
-        <v>52</v>
+        <v>810</v>
       </c>
       <c r="V11" s="39" t="str">
-        <f>IF(T11&lt;&gt;"","9 - Closed",IF(S11&lt;&gt;"","8 - Definitive Agreement",IF(Q11&lt;&gt;"","7 - Diligence",IF(P11&lt;&gt;"","6 - LOI Signed",IF(O11&lt;&gt;"","5 - Mgmt Meeting",IF(L11&lt;&gt;"","4 - IOI Received",IF(K11&lt;&gt;"","3 - CIM Sent",IF(J11&lt;&gt;"","2 - Teaser Sent",IF(I11&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
+        <f>IF(T11&lt;&gt;"","9 - Closed",IF(S11&lt;&gt;"","8 - Definitive Agreement",IF(Q11&lt;&gt;"","7 - Diligence",IF(P11&lt;&gt;"","6 - LOI Signed",IF(O11&lt;&gt;"","5 - Mgmt Meeting",IF(L11&lt;&gt;"","4 - IOI Received",IF(K11&lt;&gt;"","3 - CIM Sent",IF(J11&lt;&gt;"","2 - NDA Signed",IF(I11&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
         <v>5 - Mgmt Meeting</v>
       </c>
       <c r="W11" s="39">
-        <f ca="1">IF(COUNT(G11:T11)=0,"-",TODAY()-MAX(G11:T11))</f>
-        <v>21</v>
+        <f>IF(COUNT(G11:T11)=0,"-",Dashboard!$I$6-MAX(G11:T11))</f>
+        <v>25</v>
       </c>
       <c r="X11" s="40" t="s">
-        <v>96</v>
+        <v>812</v>
       </c>
     </row>
     <row r="12" spans="1:24" ht="15" customHeight="1">
@@ -6129,7 +6206,7 @@
         <v>46109</v>
       </c>
       <c r="I12" s="34">
-        <v>46119</v>
+        <v>46105</v>
       </c>
       <c r="J12" s="34">
         <v>46119</v>
@@ -6158,12 +6235,12 @@
         <v>102</v>
       </c>
       <c r="V12" s="39" t="str">
-        <f>IF(T12&lt;&gt;"","9 - Closed",IF(S12&lt;&gt;"","8 - Definitive Agreement",IF(Q12&lt;&gt;"","7 - Diligence",IF(P12&lt;&gt;"","6 - LOI Signed",IF(O12&lt;&gt;"","5 - Mgmt Meeting",IF(L12&lt;&gt;"","4 - IOI Received",IF(K12&lt;&gt;"","3 - CIM Sent",IF(J12&lt;&gt;"","2 - Teaser Sent",IF(I12&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
+        <f>IF(T12&lt;&gt;"","9 - Closed",IF(S12&lt;&gt;"","8 - Definitive Agreement",IF(Q12&lt;&gt;"","7 - Diligence",IF(P12&lt;&gt;"","6 - LOI Signed",IF(O12&lt;&gt;"","5 - Mgmt Meeting",IF(L12&lt;&gt;"","4 - IOI Received",IF(K12&lt;&gt;"","3 - CIM Sent",IF(J12&lt;&gt;"","2 - NDA Signed",IF(I12&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
         <v>5 - Mgmt Meeting</v>
       </c>
       <c r="W12" s="39">
-        <f ca="1">IF(COUNT(G12:T12)=0,"-",TODAY()-MAX(G12:T12))</f>
-        <v>31</v>
+        <f>IF(COUNT(G12:T12)=0,"-",Dashboard!$I$6-MAX(G12:T12))</f>
+        <v>35</v>
       </c>
       <c r="X12" s="40" t="s">
         <v>103</v>
@@ -6195,10 +6272,10 @@
         <v>46105</v>
       </c>
       <c r="I13" s="34">
+        <v>46101</v>
+      </c>
+      <c r="J13" s="34">
         <v>46108</v>
-      </c>
-      <c r="J13" s="34">
-        <v>46110</v>
       </c>
       <c r="K13" s="34">
         <v>46113</v>
@@ -6224,12 +6301,12 @@
         <v>102</v>
       </c>
       <c r="V13" s="39" t="str">
-        <f>IF(T13&lt;&gt;"","9 - Closed",IF(S13&lt;&gt;"","8 - Definitive Agreement",IF(Q13&lt;&gt;"","7 - Diligence",IF(P13&lt;&gt;"","6 - LOI Signed",IF(O13&lt;&gt;"","5 - Mgmt Meeting",IF(L13&lt;&gt;"","4 - IOI Received",IF(K13&lt;&gt;"","3 - CIM Sent",IF(J13&lt;&gt;"","2 - Teaser Sent",IF(I13&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
+        <f>IF(T13&lt;&gt;"","9 - Closed",IF(S13&lt;&gt;"","8 - Definitive Agreement",IF(Q13&lt;&gt;"","7 - Diligence",IF(P13&lt;&gt;"","6 - LOI Signed",IF(O13&lt;&gt;"","5 - Mgmt Meeting",IF(L13&lt;&gt;"","4 - IOI Received",IF(K13&lt;&gt;"","3 - CIM Sent",IF(J13&lt;&gt;"","2 - NDA Signed",IF(I13&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
         <v>5 - Mgmt Meeting</v>
       </c>
       <c r="W13" s="39">
-        <f ca="1">IF(COUNT(G13:T13)=0,"-",TODAY()-MAX(G13:T13))</f>
-        <v>44</v>
+        <f>IF(COUNT(G13:T13)=0,"-",Dashboard!$I$6-MAX(G13:T13))</f>
+        <v>48</v>
       </c>
       <c r="X13" s="40" t="s">
         <v>103</v>
@@ -6261,10 +6338,10 @@
         <v>46095</v>
       </c>
       <c r="I14" s="34">
+        <v>46094</v>
+      </c>
+      <c r="J14" s="34">
         <v>46101</v>
-      </c>
-      <c r="J14" s="34">
-        <v>46102</v>
       </c>
       <c r="K14" s="34">
         <v>46109</v>
@@ -6290,12 +6367,12 @@
         <v>102</v>
       </c>
       <c r="V14" s="39" t="str">
-        <f>IF(T14&lt;&gt;"","9 - Closed",IF(S14&lt;&gt;"","8 - Definitive Agreement",IF(Q14&lt;&gt;"","7 - Diligence",IF(P14&lt;&gt;"","6 - LOI Signed",IF(O14&lt;&gt;"","5 - Mgmt Meeting",IF(L14&lt;&gt;"","4 - IOI Received",IF(K14&lt;&gt;"","3 - CIM Sent",IF(J14&lt;&gt;"","2 - Teaser Sent",IF(I14&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
+        <f>IF(T14&lt;&gt;"","9 - Closed",IF(S14&lt;&gt;"","8 - Definitive Agreement",IF(Q14&lt;&gt;"","7 - Diligence",IF(P14&lt;&gt;"","6 - LOI Signed",IF(O14&lt;&gt;"","5 - Mgmt Meeting",IF(L14&lt;&gt;"","4 - IOI Received",IF(K14&lt;&gt;"","3 - CIM Sent",IF(J14&lt;&gt;"","2 - NDA Signed",IF(I14&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
         <v>5 - Mgmt Meeting</v>
       </c>
       <c r="W14" s="39">
-        <f ca="1">IF(COUNT(G14:T14)=0,"-",TODAY()-MAX(G14:T14))</f>
-        <v>34</v>
+        <f>IF(COUNT(G14:T14)=0,"-",Dashboard!$I$6-MAX(G14:T14))</f>
+        <v>38</v>
       </c>
       <c r="X14" s="40" t="s">
         <v>103</v>
@@ -6327,10 +6404,10 @@
         <v>46097</v>
       </c>
       <c r="I15" s="34">
+        <v>46096</v>
+      </c>
+      <c r="J15" s="34">
         <v>46108</v>
-      </c>
-      <c r="J15" s="34">
-        <v>46109</v>
       </c>
       <c r="K15" s="34">
         <v>46114</v>
@@ -6345,7 +6422,7 @@
         <v>13.3</v>
       </c>
       <c r="O15" s="34">
-        <v>46224</v>
+        <v>46217</v>
       </c>
       <c r="P15" s="37"/>
       <c r="Q15" s="37"/>
@@ -6356,12 +6433,12 @@
         <v>102</v>
       </c>
       <c r="V15" s="39" t="str">
-        <f>IF(T15&lt;&gt;"","9 - Closed",IF(S15&lt;&gt;"","8 - Definitive Agreement",IF(Q15&lt;&gt;"","7 - Diligence",IF(P15&lt;&gt;"","6 - LOI Signed",IF(O15&lt;&gt;"","5 - Mgmt Meeting",IF(L15&lt;&gt;"","4 - IOI Received",IF(K15&lt;&gt;"","3 - CIM Sent",IF(J15&lt;&gt;"","2 - Teaser Sent",IF(I15&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
+        <f>IF(T15&lt;&gt;"","9 - Closed",IF(S15&lt;&gt;"","8 - Definitive Agreement",IF(Q15&lt;&gt;"","7 - Diligence",IF(P15&lt;&gt;"","6 - LOI Signed",IF(O15&lt;&gt;"","5 - Mgmt Meeting",IF(L15&lt;&gt;"","4 - IOI Received",IF(K15&lt;&gt;"","3 - CIM Sent",IF(J15&lt;&gt;"","2 - NDA Signed",IF(I15&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
         <v>5 - Mgmt Meeting</v>
       </c>
       <c r="W15" s="39">
-        <f ca="1">IF(COUNT(G15:T15)=0,"-",TODAY()-MAX(G15:T15))</f>
-        <v>16</v>
+        <f>IF(COUNT(G15:T15)=0,"-",Dashboard!$I$6-MAX(G15:T15))</f>
+        <v>27</v>
       </c>
       <c r="X15" s="40" t="s">
         <v>103</v>
@@ -6393,10 +6470,10 @@
         <v>46112</v>
       </c>
       <c r="I16" s="34">
+        <v>46108</v>
+      </c>
+      <c r="J16" s="34">
         <v>46118</v>
-      </c>
-      <c r="J16" s="34">
-        <v>46120</v>
       </c>
       <c r="K16" s="34">
         <v>46122</v>
@@ -6422,12 +6499,12 @@
         <v>102</v>
       </c>
       <c r="V16" s="39" t="str">
-        <f>IF(T16&lt;&gt;"","9 - Closed",IF(S16&lt;&gt;"","8 - Definitive Agreement",IF(Q16&lt;&gt;"","7 - Diligence",IF(P16&lt;&gt;"","6 - LOI Signed",IF(O16&lt;&gt;"","5 - Mgmt Meeting",IF(L16&lt;&gt;"","4 - IOI Received",IF(K16&lt;&gt;"","3 - CIM Sent",IF(J16&lt;&gt;"","2 - Teaser Sent",IF(I16&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
+        <f>IF(T16&lt;&gt;"","9 - Closed",IF(S16&lt;&gt;"","8 - Definitive Agreement",IF(Q16&lt;&gt;"","7 - Diligence",IF(P16&lt;&gt;"","6 - LOI Signed",IF(O16&lt;&gt;"","5 - Mgmt Meeting",IF(L16&lt;&gt;"","4 - IOI Received",IF(K16&lt;&gt;"","3 - CIM Sent",IF(J16&lt;&gt;"","2 - NDA Signed",IF(I16&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
         <v>5 - Mgmt Meeting</v>
       </c>
       <c r="W16" s="39">
-        <f ca="1">IF(COUNT(G16:T16)=0,"-",TODAY()-MAX(G16:T16))</f>
-        <v>35</v>
+        <f>IF(COUNT(G16:T16)=0,"-",Dashboard!$I$6-MAX(G16:T16))</f>
+        <v>39</v>
       </c>
       <c r="X16" s="40" t="s">
         <v>103</v>
@@ -6459,10 +6536,10 @@
         <v>46093</v>
       </c>
       <c r="I17" s="34">
+        <v>46090</v>
+      </c>
+      <c r="J17" s="34">
         <v>46104</v>
-      </c>
-      <c r="J17" s="34">
-        <v>46105</v>
       </c>
       <c r="K17" s="34">
         <v>46113</v>
@@ -6486,12 +6563,12 @@
         <v>102</v>
       </c>
       <c r="V17" s="39" t="str">
-        <f>IF(T17&lt;&gt;"","9 - Closed",IF(S17&lt;&gt;"","8 - Definitive Agreement",IF(Q17&lt;&gt;"","7 - Diligence",IF(P17&lt;&gt;"","6 - LOI Signed",IF(O17&lt;&gt;"","5 - Mgmt Meeting",IF(L17&lt;&gt;"","4 - IOI Received",IF(K17&lt;&gt;"","3 - CIM Sent",IF(J17&lt;&gt;"","2 - Teaser Sent",IF(I17&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
+        <f>IF(T17&lt;&gt;"","9 - Closed",IF(S17&lt;&gt;"","8 - Definitive Agreement",IF(Q17&lt;&gt;"","7 - Diligence",IF(P17&lt;&gt;"","6 - LOI Signed",IF(O17&lt;&gt;"","5 - Mgmt Meeting",IF(L17&lt;&gt;"","4 - IOI Received",IF(K17&lt;&gt;"","3 - CIM Sent",IF(J17&lt;&gt;"","2 - NDA Signed",IF(I17&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
         <v>4 - IOI Received</v>
       </c>
       <c r="W17" s="39">
-        <f ca="1">IF(COUNT(G17:T17)=0,"-",TODAY()-MAX(G17:T17))</f>
-        <v>63</v>
+        <f>IF(COUNT(G17:T17)=0,"-",Dashboard!$I$6-MAX(G17:T17))</f>
+        <v>67</v>
       </c>
       <c r="X17" s="40" t="s">
         <v>103</v>
@@ -6523,7 +6600,7 @@
         <v>46099</v>
       </c>
       <c r="I18" s="34">
-        <v>46108</v>
+        <v>46095</v>
       </c>
       <c r="J18" s="34">
         <v>46108</v>
@@ -6547,18 +6624,18 @@
       <c r="S18" s="37"/>
       <c r="T18" s="37"/>
       <c r="U18" s="38" t="s">
-        <v>52</v>
+        <v>810</v>
       </c>
       <c r="V18" s="39" t="str">
-        <f>IF(T18&lt;&gt;"","9 - Closed",IF(S18&lt;&gt;"","8 - Definitive Agreement",IF(Q18&lt;&gt;"","7 - Diligence",IF(P18&lt;&gt;"","6 - LOI Signed",IF(O18&lt;&gt;"","5 - Mgmt Meeting",IF(L18&lt;&gt;"","4 - IOI Received",IF(K18&lt;&gt;"","3 - CIM Sent",IF(J18&lt;&gt;"","2 - Teaser Sent",IF(I18&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
+        <f>IF(T18&lt;&gt;"","9 - Closed",IF(S18&lt;&gt;"","8 - Definitive Agreement",IF(Q18&lt;&gt;"","7 - Diligence",IF(P18&lt;&gt;"","6 - LOI Signed",IF(O18&lt;&gt;"","5 - Mgmt Meeting",IF(L18&lt;&gt;"","4 - IOI Received",IF(K18&lt;&gt;"","3 - CIM Sent",IF(J18&lt;&gt;"","2 - NDA Signed",IF(I18&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
         <v>4 - IOI Received</v>
       </c>
       <c r="W18" s="39">
-        <f ca="1">IF(COUNT(G18:T18)=0,"-",TODAY()-MAX(G18:T18))</f>
-        <v>83</v>
+        <f>IF(COUNT(G18:T18)=0,"-",Dashboard!$I$6-MAX(G18:T18))</f>
+        <v>87</v>
       </c>
       <c r="X18" s="40" t="s">
-        <v>96</v>
+        <v>813</v>
       </c>
     </row>
     <row r="19" spans="1:24" ht="15" customHeight="1">
@@ -6587,7 +6664,7 @@
         <v>46099</v>
       </c>
       <c r="I19" s="34">
-        <v>46105</v>
+        <v>46095</v>
       </c>
       <c r="J19" s="34">
         <v>46105</v>
@@ -6611,18 +6688,18 @@
       <c r="S19" s="37"/>
       <c r="T19" s="37"/>
       <c r="U19" s="38" t="s">
-        <v>52</v>
+        <v>810</v>
       </c>
       <c r="V19" s="39" t="str">
-        <f>IF(T19&lt;&gt;"","9 - Closed",IF(S19&lt;&gt;"","8 - Definitive Agreement",IF(Q19&lt;&gt;"","7 - Diligence",IF(P19&lt;&gt;"","6 - LOI Signed",IF(O19&lt;&gt;"","5 - Mgmt Meeting",IF(L19&lt;&gt;"","4 - IOI Received",IF(K19&lt;&gt;"","3 - CIM Sent",IF(J19&lt;&gt;"","2 - Teaser Sent",IF(I19&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
+        <f>IF(T19&lt;&gt;"","9 - Closed",IF(S19&lt;&gt;"","8 - Definitive Agreement",IF(Q19&lt;&gt;"","7 - Diligence",IF(P19&lt;&gt;"","6 - LOI Signed",IF(O19&lt;&gt;"","5 - Mgmt Meeting",IF(L19&lt;&gt;"","4 - IOI Received",IF(K19&lt;&gt;"","3 - CIM Sent",IF(J19&lt;&gt;"","2 - NDA Signed",IF(I19&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
         <v>4 - IOI Received</v>
       </c>
       <c r="W19" s="39">
-        <f ca="1">IF(COUNT(G19:T19)=0,"-",TODAY()-MAX(G19:T19))</f>
-        <v>50</v>
+        <f>IF(COUNT(G19:T19)=0,"-",Dashboard!$I$6-MAX(G19:T19))</f>
+        <v>54</v>
       </c>
       <c r="X19" s="40" t="s">
-        <v>96</v>
+        <v>813</v>
       </c>
     </row>
     <row r="20" spans="1:24" ht="15" customHeight="1">
@@ -6651,10 +6728,10 @@
         <v>46090</v>
       </c>
       <c r="I20" s="34">
+        <v>46087</v>
+      </c>
+      <c r="J20" s="34">
         <v>46095</v>
-      </c>
-      <c r="J20" s="34">
-        <v>46097</v>
       </c>
       <c r="K20" s="34">
         <v>46102</v>
@@ -6675,18 +6752,18 @@
       <c r="S20" s="37"/>
       <c r="T20" s="37"/>
       <c r="U20" s="38" t="s">
-        <v>52</v>
+        <v>810</v>
       </c>
       <c r="V20" s="39" t="str">
-        <f>IF(T20&lt;&gt;"","9 - Closed",IF(S20&lt;&gt;"","8 - Definitive Agreement",IF(Q20&lt;&gt;"","7 - Diligence",IF(P20&lt;&gt;"","6 - LOI Signed",IF(O20&lt;&gt;"","5 - Mgmt Meeting",IF(L20&lt;&gt;"","4 - IOI Received",IF(K20&lt;&gt;"","3 - CIM Sent",IF(J20&lt;&gt;"","2 - Teaser Sent",IF(I20&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
+        <f>IF(T20&lt;&gt;"","9 - Closed",IF(S20&lt;&gt;"","8 - Definitive Agreement",IF(Q20&lt;&gt;"","7 - Diligence",IF(P20&lt;&gt;"","6 - LOI Signed",IF(O20&lt;&gt;"","5 - Mgmt Meeting",IF(L20&lt;&gt;"","4 - IOI Received",IF(K20&lt;&gt;"","3 - CIM Sent",IF(J20&lt;&gt;"","2 - NDA Signed",IF(I20&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
         <v>4 - IOI Received</v>
       </c>
       <c r="W20" s="39">
-        <f ca="1">IF(COUNT(G20:T20)=0,"-",TODAY()-MAX(G20:T20))</f>
-        <v>86</v>
+        <f>IF(COUNT(G20:T20)=0,"-",Dashboard!$I$6-MAX(G20:T20))</f>
+        <v>90</v>
       </c>
       <c r="X20" s="40" t="s">
-        <v>96</v>
+        <v>813</v>
       </c>
     </row>
     <row r="21" spans="1:24" ht="15" customHeight="1">
@@ -6715,10 +6792,10 @@
         <v>46096</v>
       </c>
       <c r="I21" s="34">
+        <v>46095</v>
+      </c>
+      <c r="J21" s="34">
         <v>46108</v>
-      </c>
-      <c r="J21" s="34">
-        <v>46110</v>
       </c>
       <c r="K21" s="34">
         <v>46112</v>
@@ -6742,12 +6819,12 @@
         <v>102</v>
       </c>
       <c r="V21" s="39" t="str">
-        <f>IF(T21&lt;&gt;"","9 - Closed",IF(S21&lt;&gt;"","8 - Definitive Agreement",IF(Q21&lt;&gt;"","7 - Diligence",IF(P21&lt;&gt;"","6 - LOI Signed",IF(O21&lt;&gt;"","5 - Mgmt Meeting",IF(L21&lt;&gt;"","4 - IOI Received",IF(K21&lt;&gt;"","3 - CIM Sent",IF(J21&lt;&gt;"","2 - Teaser Sent",IF(I21&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
+        <f>IF(T21&lt;&gt;"","9 - Closed",IF(S21&lt;&gt;"","8 - Definitive Agreement",IF(Q21&lt;&gt;"","7 - Diligence",IF(P21&lt;&gt;"","6 - LOI Signed",IF(O21&lt;&gt;"","5 - Mgmt Meeting",IF(L21&lt;&gt;"","4 - IOI Received",IF(K21&lt;&gt;"","3 - CIM Sent",IF(J21&lt;&gt;"","2 - NDA Signed",IF(I21&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
         <v>4 - IOI Received</v>
       </c>
       <c r="W21" s="39">
-        <f ca="1">IF(COUNT(G21:T21)=0,"-",TODAY()-MAX(G21:T21))</f>
-        <v>89</v>
+        <f>IF(COUNT(G21:T21)=0,"-",Dashboard!$I$6-MAX(G21:T21))</f>
+        <v>93</v>
       </c>
       <c r="X21" s="40" t="s">
         <v>103</v>
@@ -6779,10 +6856,10 @@
         <v>46087</v>
       </c>
       <c r="I22" s="34">
+        <v>46085</v>
+      </c>
+      <c r="J22" s="34">
         <v>46090</v>
-      </c>
-      <c r="J22" s="34">
-        <v>46091</v>
       </c>
       <c r="K22" s="34">
         <v>46098</v>
@@ -6806,12 +6883,12 @@
         <v>102</v>
       </c>
       <c r="V22" s="39" t="str">
-        <f>IF(T22&lt;&gt;"","9 - Closed",IF(S22&lt;&gt;"","8 - Definitive Agreement",IF(Q22&lt;&gt;"","7 - Diligence",IF(P22&lt;&gt;"","6 - LOI Signed",IF(O22&lt;&gt;"","5 - Mgmt Meeting",IF(L22&lt;&gt;"","4 - IOI Received",IF(K22&lt;&gt;"","3 - CIM Sent",IF(J22&lt;&gt;"","2 - Teaser Sent",IF(I22&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
+        <f>IF(T22&lt;&gt;"","9 - Closed",IF(S22&lt;&gt;"","8 - Definitive Agreement",IF(Q22&lt;&gt;"","7 - Diligence",IF(P22&lt;&gt;"","6 - LOI Signed",IF(O22&lt;&gt;"","5 - Mgmt Meeting",IF(L22&lt;&gt;"","4 - IOI Received",IF(K22&lt;&gt;"","3 - CIM Sent",IF(J22&lt;&gt;"","2 - NDA Signed",IF(I22&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
         <v>4 - IOI Received</v>
       </c>
       <c r="W22" s="39">
-        <f ca="1">IF(COUNT(G22:T22)=0,"-",TODAY()-MAX(G22:T22))</f>
-        <v>69</v>
+        <f>IF(COUNT(G22:T22)=0,"-",Dashboard!$I$6-MAX(G22:T22))</f>
+        <v>73</v>
       </c>
       <c r="X22" s="40" t="s">
         <v>103</v>
@@ -6843,10 +6920,10 @@
         <v>46100</v>
       </c>
       <c r="I23" s="34">
+        <v>46097</v>
+      </c>
+      <c r="J23" s="34">
         <v>46110</v>
-      </c>
-      <c r="J23" s="34">
-        <v>46112</v>
       </c>
       <c r="K23" s="34">
         <v>46118</v>
@@ -6867,18 +6944,18 @@
       <c r="S23" s="37"/>
       <c r="T23" s="37"/>
       <c r="U23" s="38" t="s">
-        <v>52</v>
+        <v>810</v>
       </c>
       <c r="V23" s="39" t="str">
-        <f>IF(T23&lt;&gt;"","9 - Closed",IF(S23&lt;&gt;"","8 - Definitive Agreement",IF(Q23&lt;&gt;"","7 - Diligence",IF(P23&lt;&gt;"","6 - LOI Signed",IF(O23&lt;&gt;"","5 - Mgmt Meeting",IF(L23&lt;&gt;"","4 - IOI Received",IF(K23&lt;&gt;"","3 - CIM Sent",IF(J23&lt;&gt;"","2 - Teaser Sent",IF(I23&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
+        <f>IF(T23&lt;&gt;"","9 - Closed",IF(S23&lt;&gt;"","8 - Definitive Agreement",IF(Q23&lt;&gt;"","7 - Diligence",IF(P23&lt;&gt;"","6 - LOI Signed",IF(O23&lt;&gt;"","5 - Mgmt Meeting",IF(L23&lt;&gt;"","4 - IOI Received",IF(K23&lt;&gt;"","3 - CIM Sent",IF(J23&lt;&gt;"","2 - NDA Signed",IF(I23&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
         <v>4 - IOI Received</v>
       </c>
       <c r="W23" s="39">
-        <f ca="1">IF(COUNT(G23:T23)=0,"-",TODAY()-MAX(G23:T23))</f>
-        <v>49</v>
+        <f>IF(COUNT(G23:T23)=0,"-",Dashboard!$I$6-MAX(G23:T23))</f>
+        <v>53</v>
       </c>
       <c r="X23" s="40" t="s">
-        <v>96</v>
+        <v>813</v>
       </c>
     </row>
     <row r="24" spans="1:24" ht="15" customHeight="1">
@@ -6907,7 +6984,7 @@
         <v>46096</v>
       </c>
       <c r="I24" s="34">
-        <v>46103</v>
+        <v>46093</v>
       </c>
       <c r="J24" s="34">
         <v>46103</v>
@@ -6931,18 +7008,18 @@
       <c r="S24" s="37"/>
       <c r="T24" s="37"/>
       <c r="U24" s="38" t="s">
-        <v>52</v>
+        <v>810</v>
       </c>
       <c r="V24" s="39" t="str">
-        <f>IF(T24&lt;&gt;"","9 - Closed",IF(S24&lt;&gt;"","8 - Definitive Agreement",IF(Q24&lt;&gt;"","7 - Diligence",IF(P24&lt;&gt;"","6 - LOI Signed",IF(O24&lt;&gt;"","5 - Mgmt Meeting",IF(L24&lt;&gt;"","4 - IOI Received",IF(K24&lt;&gt;"","3 - CIM Sent",IF(J24&lt;&gt;"","2 - Teaser Sent",IF(I24&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
+        <f>IF(T24&lt;&gt;"","9 - Closed",IF(S24&lt;&gt;"","8 - Definitive Agreement",IF(Q24&lt;&gt;"","7 - Diligence",IF(P24&lt;&gt;"","6 - LOI Signed",IF(O24&lt;&gt;"","5 - Mgmt Meeting",IF(L24&lt;&gt;"","4 - IOI Received",IF(K24&lt;&gt;"","3 - CIM Sent",IF(J24&lt;&gt;"","2 - NDA Signed",IF(I24&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
         <v>4 - IOI Received</v>
       </c>
       <c r="W24" s="39">
-        <f ca="1">IF(COUNT(G24:T24)=0,"-",TODAY()-MAX(G24:T24))</f>
-        <v>104</v>
+        <f>IF(COUNT(G24:T24)=0,"-",Dashboard!$I$6-MAX(G24:T24))</f>
+        <v>108</v>
       </c>
       <c r="X24" s="40" t="s">
-        <v>96</v>
+        <v>813</v>
       </c>
     </row>
     <row r="25" spans="1:24" ht="15" customHeight="1">
@@ -6971,10 +7048,10 @@
         <v>46111</v>
       </c>
       <c r="I25" s="34">
+        <v>46107</v>
+      </c>
+      <c r="J25" s="34">
         <v>46121</v>
-      </c>
-      <c r="J25" s="34">
-        <v>46122</v>
       </c>
       <c r="K25" s="34">
         <v>46125</v>
@@ -6998,12 +7075,12 @@
         <v>102</v>
       </c>
       <c r="V25" s="39" t="str">
-        <f>IF(T25&lt;&gt;"","9 - Closed",IF(S25&lt;&gt;"","8 - Definitive Agreement",IF(Q25&lt;&gt;"","7 - Diligence",IF(P25&lt;&gt;"","6 - LOI Signed",IF(O25&lt;&gt;"","5 - Mgmt Meeting",IF(L25&lt;&gt;"","4 - IOI Received",IF(K25&lt;&gt;"","3 - CIM Sent",IF(J25&lt;&gt;"","2 - Teaser Sent",IF(I25&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
+        <f>IF(T25&lt;&gt;"","9 - Closed",IF(S25&lt;&gt;"","8 - Definitive Agreement",IF(Q25&lt;&gt;"","7 - Diligence",IF(P25&lt;&gt;"","6 - LOI Signed",IF(O25&lt;&gt;"","5 - Mgmt Meeting",IF(L25&lt;&gt;"","4 - IOI Received",IF(K25&lt;&gt;"","3 - CIM Sent",IF(J25&lt;&gt;"","2 - NDA Signed",IF(I25&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
         <v>4 - IOI Received</v>
       </c>
       <c r="W25" s="39">
-        <f ca="1">IF(COUNT(G25:T25)=0,"-",TODAY()-MAX(G25:T25))</f>
-        <v>70</v>
+        <f>IF(COUNT(G25:T25)=0,"-",Dashboard!$I$6-MAX(G25:T25))</f>
+        <v>74</v>
       </c>
       <c r="X25" s="40" t="s">
         <v>103</v>
@@ -7035,10 +7112,10 @@
         <v>46099</v>
       </c>
       <c r="I26" s="34">
+        <v>46096</v>
+      </c>
+      <c r="J26" s="34">
         <v>46110</v>
-      </c>
-      <c r="J26" s="34">
-        <v>46111</v>
       </c>
       <c r="K26" s="34">
         <v>46118</v>
@@ -7059,18 +7136,18 @@
       <c r="S26" s="37"/>
       <c r="T26" s="37"/>
       <c r="U26" s="38" t="s">
-        <v>52</v>
+        <v>810</v>
       </c>
       <c r="V26" s="39" t="str">
-        <f>IF(T26&lt;&gt;"","9 - Closed",IF(S26&lt;&gt;"","8 - Definitive Agreement",IF(Q26&lt;&gt;"","7 - Diligence",IF(P26&lt;&gt;"","6 - LOI Signed",IF(O26&lt;&gt;"","5 - Mgmt Meeting",IF(L26&lt;&gt;"","4 - IOI Received",IF(K26&lt;&gt;"","3 - CIM Sent",IF(J26&lt;&gt;"","2 - Teaser Sent",IF(I26&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
+        <f>IF(T26&lt;&gt;"","9 - Closed",IF(S26&lt;&gt;"","8 - Definitive Agreement",IF(Q26&lt;&gt;"","7 - Diligence",IF(P26&lt;&gt;"","6 - LOI Signed",IF(O26&lt;&gt;"","5 - Mgmt Meeting",IF(L26&lt;&gt;"","4 - IOI Received",IF(K26&lt;&gt;"","3 - CIM Sent",IF(J26&lt;&gt;"","2 - NDA Signed",IF(I26&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
         <v>4 - IOI Received</v>
       </c>
       <c r="W26" s="39">
-        <f ca="1">IF(COUNT(G26:T26)=0,"-",TODAY()-MAX(G26:T26))</f>
-        <v>96</v>
+        <f>IF(COUNT(G26:T26)=0,"-",Dashboard!$I$6-MAX(G26:T26))</f>
+        <v>100</v>
       </c>
       <c r="X26" s="40" t="s">
-        <v>96</v>
+        <v>813</v>
       </c>
     </row>
     <row r="27" spans="1:24" ht="15" customHeight="1">
@@ -7099,7 +7176,7 @@
         <v>46086</v>
       </c>
       <c r="I27" s="34">
-        <v>46097</v>
+        <v>46083</v>
       </c>
       <c r="J27" s="34">
         <v>46097</v>
@@ -7117,18 +7194,18 @@
       <c r="S27" s="37"/>
       <c r="T27" s="37"/>
       <c r="U27" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V27" s="39" t="str">
-        <f>IF(T27&lt;&gt;"","9 - Closed",IF(S27&lt;&gt;"","8 - Definitive Agreement",IF(Q27&lt;&gt;"","7 - Diligence",IF(P27&lt;&gt;"","6 - LOI Signed",IF(O27&lt;&gt;"","5 - Mgmt Meeting",IF(L27&lt;&gt;"","4 - IOI Received",IF(K27&lt;&gt;"","3 - CIM Sent",IF(J27&lt;&gt;"","2 - Teaser Sent",IF(I27&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
+        <f>IF(T27&lt;&gt;"","9 - Closed",IF(S27&lt;&gt;"","8 - Definitive Agreement",IF(Q27&lt;&gt;"","7 - Diligence",IF(P27&lt;&gt;"","6 - LOI Signed",IF(O27&lt;&gt;"","5 - Mgmt Meeting",IF(L27&lt;&gt;"","4 - IOI Received",IF(K27&lt;&gt;"","3 - CIM Sent",IF(J27&lt;&gt;"","2 - NDA Signed",IF(I27&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
         <v>3 - CIM Sent</v>
       </c>
       <c r="W27" s="39">
-        <f ca="1">IF(COUNT(G27:T27)=0,"-",TODAY()-MAX(G27:T27))</f>
-        <v>140</v>
+        <f>IF(COUNT(G27:T27)=0,"-",Dashboard!$I$6-MAX(G27:T27))</f>
+        <v>144</v>
       </c>
       <c r="X27" s="40" t="s">
-        <v>96</v>
+        <v>814</v>
       </c>
     </row>
     <row r="28" spans="1:24" ht="15" customHeight="1">
@@ -7157,10 +7234,10 @@
         <v>46098</v>
       </c>
       <c r="I28" s="34">
+        <v>46094</v>
+      </c>
+      <c r="J28" s="34">
         <v>46104</v>
-      </c>
-      <c r="J28" s="34">
-        <v>46106</v>
       </c>
       <c r="K28" s="34">
         <v>46114</v>
@@ -7178,15 +7255,15 @@
         <v>190</v>
       </c>
       <c r="V28" s="39" t="str">
-        <f>IF(T28&lt;&gt;"","9 - Closed",IF(S28&lt;&gt;"","8 - Definitive Agreement",IF(Q28&lt;&gt;"","7 - Diligence",IF(P28&lt;&gt;"","6 - LOI Signed",IF(O28&lt;&gt;"","5 - Mgmt Meeting",IF(L28&lt;&gt;"","4 - IOI Received",IF(K28&lt;&gt;"","3 - CIM Sent",IF(J28&lt;&gt;"","2 - Teaser Sent",IF(I28&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
+        <f>IF(T28&lt;&gt;"","9 - Closed",IF(S28&lt;&gt;"","8 - Definitive Agreement",IF(Q28&lt;&gt;"","7 - Diligence",IF(P28&lt;&gt;"","6 - LOI Signed",IF(O28&lt;&gt;"","5 - Mgmt Meeting",IF(L28&lt;&gt;"","4 - IOI Received",IF(K28&lt;&gt;"","3 - CIM Sent",IF(J28&lt;&gt;"","2 - NDA Signed",IF(I28&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
         <v>3 - CIM Sent</v>
       </c>
       <c r="W28" s="39">
-        <f ca="1">IF(COUNT(G28:T28)=0,"-",TODAY()-MAX(G28:T28))</f>
-        <v>126</v>
+        <f>IF(COUNT(G28:T28)=0,"-",Dashboard!$I$6-MAX(G28:T28))</f>
+        <v>130</v>
       </c>
       <c r="X28" s="40" t="s">
-        <v>191</v>
+        <v>815</v>
       </c>
     </row>
     <row r="29" spans="1:24" ht="15" customHeight="1">
@@ -7215,10 +7292,10 @@
         <v>46104</v>
       </c>
       <c r="I29" s="34">
+        <v>46103</v>
+      </c>
+      <c r="J29" s="34">
         <v>46106</v>
-      </c>
-      <c r="J29" s="34">
-        <v>46107</v>
       </c>
       <c r="K29" s="34">
         <v>46116</v>
@@ -7236,15 +7313,15 @@
         <v>190</v>
       </c>
       <c r="V29" s="39" t="str">
-        <f>IF(T29&lt;&gt;"","9 - Closed",IF(S29&lt;&gt;"","8 - Definitive Agreement",IF(Q29&lt;&gt;"","7 - Diligence",IF(P29&lt;&gt;"","6 - LOI Signed",IF(O29&lt;&gt;"","5 - Mgmt Meeting",IF(L29&lt;&gt;"","4 - IOI Received",IF(K29&lt;&gt;"","3 - CIM Sent",IF(J29&lt;&gt;"","2 - Teaser Sent",IF(I29&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
+        <f>IF(T29&lt;&gt;"","9 - Closed",IF(S29&lt;&gt;"","8 - Definitive Agreement",IF(Q29&lt;&gt;"","7 - Diligence",IF(P29&lt;&gt;"","6 - LOI Signed",IF(O29&lt;&gt;"","5 - Mgmt Meeting",IF(L29&lt;&gt;"","4 - IOI Received",IF(K29&lt;&gt;"","3 - CIM Sent",IF(J29&lt;&gt;"","2 - NDA Signed",IF(I29&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
         <v>3 - CIM Sent</v>
       </c>
       <c r="W29" s="39">
-        <f ca="1">IF(COUNT(G29:T29)=0,"-",TODAY()-MAX(G29:T29))</f>
-        <v>124</v>
+        <f>IF(COUNT(G29:T29)=0,"-",Dashboard!$I$6-MAX(G29:T29))</f>
+        <v>128</v>
       </c>
       <c r="X29" s="40" t="s">
-        <v>191</v>
+        <v>815</v>
       </c>
     </row>
     <row r="30" spans="1:24" ht="15" customHeight="1">
@@ -7273,7 +7350,7 @@
         <v>46092</v>
       </c>
       <c r="I30" s="34">
-        <v>46102</v>
+        <v>46090</v>
       </c>
       <c r="J30" s="34">
         <v>46102</v>
@@ -7294,15 +7371,15 @@
         <v>190</v>
       </c>
       <c r="V30" s="39" t="str">
-        <f>IF(T30&lt;&gt;"","9 - Closed",IF(S30&lt;&gt;"","8 - Definitive Agreement",IF(Q30&lt;&gt;"","7 - Diligence",IF(P30&lt;&gt;"","6 - LOI Signed",IF(O30&lt;&gt;"","5 - Mgmt Meeting",IF(L30&lt;&gt;"","4 - IOI Received",IF(K30&lt;&gt;"","3 - CIM Sent",IF(J30&lt;&gt;"","2 - Teaser Sent",IF(I30&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
+        <f>IF(T30&lt;&gt;"","9 - Closed",IF(S30&lt;&gt;"","8 - Definitive Agreement",IF(Q30&lt;&gt;"","7 - Diligence",IF(P30&lt;&gt;"","6 - LOI Signed",IF(O30&lt;&gt;"","5 - Mgmt Meeting",IF(L30&lt;&gt;"","4 - IOI Received",IF(K30&lt;&gt;"","3 - CIM Sent",IF(J30&lt;&gt;"","2 - NDA Signed",IF(I30&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
         <v>3 - CIM Sent</v>
       </c>
       <c r="W30" s="39">
-        <f ca="1">IF(COUNT(G30:T30)=0,"-",TODAY()-MAX(G30:T30))</f>
-        <v>130</v>
+        <f>IF(COUNT(G30:T30)=0,"-",Dashboard!$I$6-MAX(G30:T30))</f>
+        <v>134</v>
       </c>
       <c r="X30" s="40" t="s">
-        <v>191</v>
+        <v>815</v>
       </c>
     </row>
     <row r="31" spans="1:24" ht="15" customHeight="1">
@@ -7331,10 +7408,10 @@
         <v>46091</v>
       </c>
       <c r="I31" s="34">
+        <v>46087</v>
+      </c>
+      <c r="J31" s="34">
         <v>46102</v>
-      </c>
-      <c r="J31" s="34">
-        <v>46104</v>
       </c>
       <c r="K31" s="34">
         <v>46108</v>
@@ -7349,18 +7426,18 @@
       <c r="S31" s="37"/>
       <c r="T31" s="37"/>
       <c r="U31" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V31" s="39" t="str">
-        <f>IF(T31&lt;&gt;"","9 - Closed",IF(S31&lt;&gt;"","8 - Definitive Agreement",IF(Q31&lt;&gt;"","7 - Diligence",IF(P31&lt;&gt;"","6 - LOI Signed",IF(O31&lt;&gt;"","5 - Mgmt Meeting",IF(L31&lt;&gt;"","4 - IOI Received",IF(K31&lt;&gt;"","3 - CIM Sent",IF(J31&lt;&gt;"","2 - Teaser Sent",IF(I31&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
+        <f>IF(T31&lt;&gt;"","9 - Closed",IF(S31&lt;&gt;"","8 - Definitive Agreement",IF(Q31&lt;&gt;"","7 - Diligence",IF(P31&lt;&gt;"","6 - LOI Signed",IF(O31&lt;&gt;"","5 - Mgmt Meeting",IF(L31&lt;&gt;"","4 - IOI Received",IF(K31&lt;&gt;"","3 - CIM Sent",IF(J31&lt;&gt;"","2 - NDA Signed",IF(I31&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
         <v>3 - CIM Sent</v>
       </c>
       <c r="W31" s="39">
-        <f ca="1">IF(COUNT(G31:T31)=0,"-",TODAY()-MAX(G31:T31))</f>
-        <v>132</v>
+        <f>IF(COUNT(G31:T31)=0,"-",Dashboard!$I$6-MAX(G31:T31))</f>
+        <v>136</v>
       </c>
       <c r="X31" s="40" t="s">
-        <v>96</v>
+        <v>814</v>
       </c>
     </row>
     <row r="32" spans="1:24" ht="15" customHeight="1">
@@ -7389,10 +7466,10 @@
         <v>46087</v>
       </c>
       <c r="I32" s="34">
+        <v>46086</v>
+      </c>
+      <c r="J32" s="34">
         <v>46096</v>
-      </c>
-      <c r="J32" s="34">
-        <v>46098</v>
       </c>
       <c r="K32" s="34">
         <v>46106</v>
@@ -7407,18 +7484,18 @@
       <c r="S32" s="37"/>
       <c r="T32" s="37"/>
       <c r="U32" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V32" s="39" t="str">
-        <f>IF(T32&lt;&gt;"","9 - Closed",IF(S32&lt;&gt;"","8 - Definitive Agreement",IF(Q32&lt;&gt;"","7 - Diligence",IF(P32&lt;&gt;"","6 - LOI Signed",IF(O32&lt;&gt;"","5 - Mgmt Meeting",IF(L32&lt;&gt;"","4 - IOI Received",IF(K32&lt;&gt;"","3 - CIM Sent",IF(J32&lt;&gt;"","2 - Teaser Sent",IF(I32&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
+        <f>IF(T32&lt;&gt;"","9 - Closed",IF(S32&lt;&gt;"","8 - Definitive Agreement",IF(Q32&lt;&gt;"","7 - Diligence",IF(P32&lt;&gt;"","6 - LOI Signed",IF(O32&lt;&gt;"","5 - Mgmt Meeting",IF(L32&lt;&gt;"","4 - IOI Received",IF(K32&lt;&gt;"","3 - CIM Sent",IF(J32&lt;&gt;"","2 - NDA Signed",IF(I32&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
         <v>3 - CIM Sent</v>
       </c>
       <c r="W32" s="39">
-        <f ca="1">IF(COUNT(G32:T32)=0,"-",TODAY()-MAX(G32:T32))</f>
-        <v>134</v>
+        <f>IF(COUNT(G32:T32)=0,"-",Dashboard!$I$6-MAX(G32:T32))</f>
+        <v>138</v>
       </c>
       <c r="X32" s="40" t="s">
-        <v>96</v>
+        <v>814</v>
       </c>
     </row>
     <row r="33" spans="1:24" ht="15" customHeight="1">
@@ -7447,10 +7524,10 @@
         <v>46094</v>
       </c>
       <c r="I33" s="34">
+        <v>46091</v>
+      </c>
+      <c r="J33" s="34">
         <v>46096</v>
-      </c>
-      <c r="J33" s="34">
-        <v>46098</v>
       </c>
       <c r="K33" s="34">
         <v>46105</v>
@@ -7468,15 +7545,15 @@
         <v>190</v>
       </c>
       <c r="V33" s="39" t="str">
-        <f>IF(T33&lt;&gt;"","9 - Closed",IF(S33&lt;&gt;"","8 - Definitive Agreement",IF(Q33&lt;&gt;"","7 - Diligence",IF(P33&lt;&gt;"","6 - LOI Signed",IF(O33&lt;&gt;"","5 - Mgmt Meeting",IF(L33&lt;&gt;"","4 - IOI Received",IF(K33&lt;&gt;"","3 - CIM Sent",IF(J33&lt;&gt;"","2 - Teaser Sent",IF(I33&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
+        <f>IF(T33&lt;&gt;"","9 - Closed",IF(S33&lt;&gt;"","8 - Definitive Agreement",IF(Q33&lt;&gt;"","7 - Diligence",IF(P33&lt;&gt;"","6 - LOI Signed",IF(O33&lt;&gt;"","5 - Mgmt Meeting",IF(L33&lt;&gt;"","4 - IOI Received",IF(K33&lt;&gt;"","3 - CIM Sent",IF(J33&lt;&gt;"","2 - NDA Signed",IF(I33&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
         <v>3 - CIM Sent</v>
       </c>
       <c r="W33" s="39">
-        <f ca="1">IF(COUNT(G33:T33)=0,"-",TODAY()-MAX(G33:T33))</f>
-        <v>135</v>
+        <f>IF(COUNT(G33:T33)=0,"-",Dashboard!$I$6-MAX(G33:T33))</f>
+        <v>139</v>
       </c>
       <c r="X33" s="40" t="s">
-        <v>191</v>
+        <v>815</v>
       </c>
     </row>
     <row r="34" spans="1:24" ht="15" customHeight="1">
@@ -7505,10 +7582,10 @@
         <v>46106</v>
       </c>
       <c r="I34" s="34">
+        <v>46102</v>
+      </c>
+      <c r="J34" s="34">
         <v>46111</v>
-      </c>
-      <c r="J34" s="34">
-        <v>46112</v>
       </c>
       <c r="K34" s="34">
         <v>46115</v>
@@ -7523,18 +7600,18 @@
       <c r="S34" s="37"/>
       <c r="T34" s="37"/>
       <c r="U34" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V34" s="39" t="str">
-        <f>IF(T34&lt;&gt;"","9 - Closed",IF(S34&lt;&gt;"","8 - Definitive Agreement",IF(Q34&lt;&gt;"","7 - Diligence",IF(P34&lt;&gt;"","6 - LOI Signed",IF(O34&lt;&gt;"","5 - Mgmt Meeting",IF(L34&lt;&gt;"","4 - IOI Received",IF(K34&lt;&gt;"","3 - CIM Sent",IF(J34&lt;&gt;"","2 - Teaser Sent",IF(I34&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
+        <f>IF(T34&lt;&gt;"","9 - Closed",IF(S34&lt;&gt;"","8 - Definitive Agreement",IF(Q34&lt;&gt;"","7 - Diligence",IF(P34&lt;&gt;"","6 - LOI Signed",IF(O34&lt;&gt;"","5 - Mgmt Meeting",IF(L34&lt;&gt;"","4 - IOI Received",IF(K34&lt;&gt;"","3 - CIM Sent",IF(J34&lt;&gt;"","2 - NDA Signed",IF(I34&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
         <v>3 - CIM Sent</v>
       </c>
       <c r="W34" s="39">
-        <f ca="1">IF(COUNT(G34:T34)=0,"-",TODAY()-MAX(G34:T34))</f>
-        <v>125</v>
+        <f>IF(COUNT(G34:T34)=0,"-",Dashboard!$I$6-MAX(G34:T34))</f>
+        <v>129</v>
       </c>
       <c r="X34" s="40" t="s">
-        <v>96</v>
+        <v>814</v>
       </c>
     </row>
     <row r="35" spans="1:24" ht="15" customHeight="1">
@@ -7563,10 +7640,10 @@
         <v>46091</v>
       </c>
       <c r="I35" s="34">
+        <v>46088</v>
+      </c>
+      <c r="J35" s="34">
         <v>46101</v>
-      </c>
-      <c r="J35" s="34">
-        <v>46103</v>
       </c>
       <c r="K35" s="34">
         <v>46110</v>
@@ -7584,15 +7661,15 @@
         <v>190</v>
       </c>
       <c r="V35" s="39" t="str">
-        <f>IF(T35&lt;&gt;"","9 - Closed",IF(S35&lt;&gt;"","8 - Definitive Agreement",IF(Q35&lt;&gt;"","7 - Diligence",IF(P35&lt;&gt;"","6 - LOI Signed",IF(O35&lt;&gt;"","5 - Mgmt Meeting",IF(L35&lt;&gt;"","4 - IOI Received",IF(K35&lt;&gt;"","3 - CIM Sent",IF(J35&lt;&gt;"","2 - Teaser Sent",IF(I35&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
+        <f>IF(T35&lt;&gt;"","9 - Closed",IF(S35&lt;&gt;"","8 - Definitive Agreement",IF(Q35&lt;&gt;"","7 - Diligence",IF(P35&lt;&gt;"","6 - LOI Signed",IF(O35&lt;&gt;"","5 - Mgmt Meeting",IF(L35&lt;&gt;"","4 - IOI Received",IF(K35&lt;&gt;"","3 - CIM Sent",IF(J35&lt;&gt;"","2 - NDA Signed",IF(I35&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
         <v>3 - CIM Sent</v>
       </c>
       <c r="W35" s="39">
-        <f ca="1">IF(COUNT(G35:T35)=0,"-",TODAY()-MAX(G35:T35))</f>
-        <v>130</v>
+        <f>IF(COUNT(G35:T35)=0,"-",Dashboard!$I$6-MAX(G35:T35))</f>
+        <v>134</v>
       </c>
       <c r="X35" s="40" t="s">
-        <v>191</v>
+        <v>815</v>
       </c>
     </row>
     <row r="36" spans="1:24" ht="15" customHeight="1">
@@ -7621,7 +7698,7 @@
         <v>46095</v>
       </c>
       <c r="I36" s="34">
-        <v>46100</v>
+        <v>46092</v>
       </c>
       <c r="J36" s="34">
         <v>46100</v>
@@ -7642,15 +7719,15 @@
         <v>190</v>
       </c>
       <c r="V36" s="39" t="str">
-        <f>IF(T36&lt;&gt;"","9 - Closed",IF(S36&lt;&gt;"","8 - Definitive Agreement",IF(Q36&lt;&gt;"","7 - Diligence",IF(P36&lt;&gt;"","6 - LOI Signed",IF(O36&lt;&gt;"","5 - Mgmt Meeting",IF(L36&lt;&gt;"","4 - IOI Received",IF(K36&lt;&gt;"","3 - CIM Sent",IF(J36&lt;&gt;"","2 - Teaser Sent",IF(I36&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
+        <f>IF(T36&lt;&gt;"","9 - Closed",IF(S36&lt;&gt;"","8 - Definitive Agreement",IF(Q36&lt;&gt;"","7 - Diligence",IF(P36&lt;&gt;"","6 - LOI Signed",IF(O36&lt;&gt;"","5 - Mgmt Meeting",IF(L36&lt;&gt;"","4 - IOI Received",IF(K36&lt;&gt;"","3 - CIM Sent",IF(J36&lt;&gt;"","2 - NDA Signed",IF(I36&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
         <v>3 - CIM Sent</v>
       </c>
       <c r="W36" s="39">
-        <f ca="1">IF(COUNT(G36:T36)=0,"-",TODAY()-MAX(G36:T36))</f>
-        <v>131</v>
+        <f>IF(COUNT(G36:T36)=0,"-",Dashboard!$I$6-MAX(G36:T36))</f>
+        <v>135</v>
       </c>
       <c r="X36" s="40" t="s">
-        <v>191</v>
+        <v>815</v>
       </c>
     </row>
     <row r="37" spans="1:24" ht="15" customHeight="1">
@@ -7679,10 +7756,10 @@
         <v>46097</v>
       </c>
       <c r="I37" s="34">
+        <v>46095</v>
+      </c>
+      <c r="J37" s="34">
         <v>46109</v>
-      </c>
-      <c r="J37" s="34">
-        <v>46111</v>
       </c>
       <c r="K37" s="34">
         <v>46113</v>
@@ -7700,15 +7777,15 @@
         <v>190</v>
       </c>
       <c r="V37" s="39" t="str">
-        <f>IF(T37&lt;&gt;"","9 - Closed",IF(S37&lt;&gt;"","8 - Definitive Agreement",IF(Q37&lt;&gt;"","7 - Diligence",IF(P37&lt;&gt;"","6 - LOI Signed",IF(O37&lt;&gt;"","5 - Mgmt Meeting",IF(L37&lt;&gt;"","4 - IOI Received",IF(K37&lt;&gt;"","3 - CIM Sent",IF(J37&lt;&gt;"","2 - Teaser Sent",IF(I37&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
+        <f>IF(T37&lt;&gt;"","9 - Closed",IF(S37&lt;&gt;"","8 - Definitive Agreement",IF(Q37&lt;&gt;"","7 - Diligence",IF(P37&lt;&gt;"","6 - LOI Signed",IF(O37&lt;&gt;"","5 - Mgmt Meeting",IF(L37&lt;&gt;"","4 - IOI Received",IF(K37&lt;&gt;"","3 - CIM Sent",IF(J37&lt;&gt;"","2 - NDA Signed",IF(I37&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
         <v>3 - CIM Sent</v>
       </c>
       <c r="W37" s="39">
-        <f ca="1">IF(COUNT(G37:T37)=0,"-",TODAY()-MAX(G37:T37))</f>
-        <v>127</v>
+        <f>IF(COUNT(G37:T37)=0,"-",Dashboard!$I$6-MAX(G37:T37))</f>
+        <v>131</v>
       </c>
       <c r="X37" s="40" t="s">
-        <v>191</v>
+        <v>815</v>
       </c>
     </row>
     <row r="38" spans="1:24" ht="15" customHeight="1">
@@ -7737,7 +7814,7 @@
         <v>46104</v>
       </c>
       <c r="I38" s="34">
-        <v>46109</v>
+        <v>46101</v>
       </c>
       <c r="J38" s="34">
         <v>46109</v>
@@ -7758,15 +7835,15 @@
         <v>190</v>
       </c>
       <c r="V38" s="39" t="str">
-        <f>IF(T38&lt;&gt;"","9 - Closed",IF(S38&lt;&gt;"","8 - Definitive Agreement",IF(Q38&lt;&gt;"","7 - Diligence",IF(P38&lt;&gt;"","6 - LOI Signed",IF(O38&lt;&gt;"","5 - Mgmt Meeting",IF(L38&lt;&gt;"","4 - IOI Received",IF(K38&lt;&gt;"","3 - CIM Sent",IF(J38&lt;&gt;"","2 - Teaser Sent",IF(I38&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
+        <f>IF(T38&lt;&gt;"","9 - Closed",IF(S38&lt;&gt;"","8 - Definitive Agreement",IF(Q38&lt;&gt;"","7 - Diligence",IF(P38&lt;&gt;"","6 - LOI Signed",IF(O38&lt;&gt;"","5 - Mgmt Meeting",IF(L38&lt;&gt;"","4 - IOI Received",IF(K38&lt;&gt;"","3 - CIM Sent",IF(J38&lt;&gt;"","2 - NDA Signed",IF(I38&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
         <v>3 - CIM Sent</v>
       </c>
       <c r="W38" s="39">
-        <f ca="1">IF(COUNT(G38:T38)=0,"-",TODAY()-MAX(G38:T38))</f>
-        <v>126</v>
+        <f>IF(COUNT(G38:T38)=0,"-",Dashboard!$I$6-MAX(G38:T38))</f>
+        <v>130</v>
       </c>
       <c r="X38" s="40" t="s">
-        <v>191</v>
+        <v>815</v>
       </c>
     </row>
     <row r="39" spans="1:24" ht="15" customHeight="1">
@@ -7795,7 +7872,7 @@
         <v>46088</v>
       </c>
       <c r="I39" s="34">
-        <v>46099</v>
+        <v>46086</v>
       </c>
       <c r="J39" s="34">
         <v>46099</v>
@@ -7816,15 +7893,15 @@
         <v>190</v>
       </c>
       <c r="V39" s="39" t="str">
-        <f>IF(T39&lt;&gt;"","9 - Closed",IF(S39&lt;&gt;"","8 - Definitive Agreement",IF(Q39&lt;&gt;"","7 - Diligence",IF(P39&lt;&gt;"","6 - LOI Signed",IF(O39&lt;&gt;"","5 - Mgmt Meeting",IF(L39&lt;&gt;"","4 - IOI Received",IF(K39&lt;&gt;"","3 - CIM Sent",IF(J39&lt;&gt;"","2 - Teaser Sent",IF(I39&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
+        <f>IF(T39&lt;&gt;"","9 - Closed",IF(S39&lt;&gt;"","8 - Definitive Agreement",IF(Q39&lt;&gt;"","7 - Diligence",IF(P39&lt;&gt;"","6 - LOI Signed",IF(O39&lt;&gt;"","5 - Mgmt Meeting",IF(L39&lt;&gt;"","4 - IOI Received",IF(K39&lt;&gt;"","3 - CIM Sent",IF(J39&lt;&gt;"","2 - NDA Signed",IF(I39&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
         <v>3 - CIM Sent</v>
       </c>
       <c r="W39" s="39">
-        <f ca="1">IF(COUNT(G39:T39)=0,"-",TODAY()-MAX(G39:T39))</f>
-        <v>136</v>
+        <f>IF(COUNT(G39:T39)=0,"-",Dashboard!$I$6-MAX(G39:T39))</f>
+        <v>140</v>
       </c>
       <c r="X39" s="40" t="s">
-        <v>191</v>
+        <v>815</v>
       </c>
     </row>
     <row r="40" spans="1:24" ht="15" customHeight="1">
@@ -7853,7 +7930,7 @@
         <v>46106</v>
       </c>
       <c r="I40" s="34">
-        <v>46117</v>
+        <v>46104</v>
       </c>
       <c r="J40" s="34">
         <v>46117</v>
@@ -7871,18 +7948,18 @@
       <c r="S40" s="37"/>
       <c r="T40" s="37"/>
       <c r="U40" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V40" s="39" t="str">
-        <f>IF(T40&lt;&gt;"","9 - Closed",IF(S40&lt;&gt;"","8 - Definitive Agreement",IF(Q40&lt;&gt;"","7 - Diligence",IF(P40&lt;&gt;"","6 - LOI Signed",IF(O40&lt;&gt;"","5 - Mgmt Meeting",IF(L40&lt;&gt;"","4 - IOI Received",IF(K40&lt;&gt;"","3 - CIM Sent",IF(J40&lt;&gt;"","2 - Teaser Sent",IF(I40&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
+        <f>IF(T40&lt;&gt;"","9 - Closed",IF(S40&lt;&gt;"","8 - Definitive Agreement",IF(Q40&lt;&gt;"","7 - Diligence",IF(P40&lt;&gt;"","6 - LOI Signed",IF(O40&lt;&gt;"","5 - Mgmt Meeting",IF(L40&lt;&gt;"","4 - IOI Received",IF(K40&lt;&gt;"","3 - CIM Sent",IF(J40&lt;&gt;"","2 - NDA Signed",IF(I40&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
         <v>3 - CIM Sent</v>
       </c>
       <c r="W40" s="39">
-        <f ca="1">IF(COUNT(G40:T40)=0,"-",TODAY()-MAX(G40:T40))</f>
-        <v>117</v>
+        <f>IF(COUNT(G40:T40)=0,"-",Dashboard!$I$6-MAX(G40:T40))</f>
+        <v>121</v>
       </c>
       <c r="X40" s="40" t="s">
-        <v>96</v>
+        <v>814</v>
       </c>
     </row>
     <row r="41" spans="1:24" ht="15" customHeight="1">
@@ -7911,10 +7988,10 @@
         <v>46103</v>
       </c>
       <c r="I41" s="34">
+        <v>46101</v>
+      </c>
+      <c r="J41" s="34">
         <v>46107</v>
-      </c>
-      <c r="J41" s="34">
-        <v>46109</v>
       </c>
       <c r="K41" s="34">
         <v>46115</v>
@@ -7929,18 +8006,18 @@
       <c r="S41" s="37"/>
       <c r="T41" s="37"/>
       <c r="U41" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V41" s="39" t="str">
-        <f>IF(T41&lt;&gt;"","9 - Closed",IF(S41&lt;&gt;"","8 - Definitive Agreement",IF(Q41&lt;&gt;"","7 - Diligence",IF(P41&lt;&gt;"","6 - LOI Signed",IF(O41&lt;&gt;"","5 - Mgmt Meeting",IF(L41&lt;&gt;"","4 - IOI Received",IF(K41&lt;&gt;"","3 - CIM Sent",IF(J41&lt;&gt;"","2 - Teaser Sent",IF(I41&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
+        <f>IF(T41&lt;&gt;"","9 - Closed",IF(S41&lt;&gt;"","8 - Definitive Agreement",IF(Q41&lt;&gt;"","7 - Diligence",IF(P41&lt;&gt;"","6 - LOI Signed",IF(O41&lt;&gt;"","5 - Mgmt Meeting",IF(L41&lt;&gt;"","4 - IOI Received",IF(K41&lt;&gt;"","3 - CIM Sent",IF(J41&lt;&gt;"","2 - NDA Signed",IF(I41&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
         <v>3 - CIM Sent</v>
       </c>
       <c r="W41" s="39">
-        <f ca="1">IF(COUNT(G41:T41)=0,"-",TODAY()-MAX(G41:T41))</f>
-        <v>125</v>
+        <f>IF(COUNT(G41:T41)=0,"-",Dashboard!$I$6-MAX(G41:T41))</f>
+        <v>129</v>
       </c>
       <c r="X41" s="40" t="s">
-        <v>96</v>
+        <v>814</v>
       </c>
     </row>
     <row r="42" spans="1:24" ht="15" customHeight="1">
@@ -7969,7 +8046,7 @@
         <v>46097</v>
       </c>
       <c r="I42" s="34">
-        <v>46109</v>
+        <v>46096</v>
       </c>
       <c r="J42" s="34">
         <v>46109</v>
@@ -7990,15 +8067,15 @@
         <v>190</v>
       </c>
       <c r="V42" s="39" t="str">
-        <f>IF(T42&lt;&gt;"","9 - Closed",IF(S42&lt;&gt;"","8 - Definitive Agreement",IF(Q42&lt;&gt;"","7 - Diligence",IF(P42&lt;&gt;"","6 - LOI Signed",IF(O42&lt;&gt;"","5 - Mgmt Meeting",IF(L42&lt;&gt;"","4 - IOI Received",IF(K42&lt;&gt;"","3 - CIM Sent",IF(J42&lt;&gt;"","2 - Teaser Sent",IF(I42&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
+        <f>IF(T42&lt;&gt;"","9 - Closed",IF(S42&lt;&gt;"","8 - Definitive Agreement",IF(Q42&lt;&gt;"","7 - Diligence",IF(P42&lt;&gt;"","6 - LOI Signed",IF(O42&lt;&gt;"","5 - Mgmt Meeting",IF(L42&lt;&gt;"","4 - IOI Received",IF(K42&lt;&gt;"","3 - CIM Sent",IF(J42&lt;&gt;"","2 - NDA Signed",IF(I42&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
         <v>3 - CIM Sent</v>
       </c>
       <c r="W42" s="39">
-        <f ca="1">IF(COUNT(G42:T42)=0,"-",TODAY()-MAX(G42:T42))</f>
-        <v>127</v>
+        <f>IF(COUNT(G42:T42)=0,"-",Dashboard!$I$6-MAX(G42:T42))</f>
+        <v>131</v>
       </c>
       <c r="X42" s="40" t="s">
-        <v>191</v>
+        <v>815</v>
       </c>
     </row>
     <row r="43" spans="1:24" ht="15" customHeight="1">
@@ -8027,10 +8104,10 @@
         <v>46105</v>
       </c>
       <c r="I43" s="34">
+        <v>46103</v>
+      </c>
+      <c r="J43" s="34">
         <v>46116</v>
-      </c>
-      <c r="J43" s="34">
-        <v>46117</v>
       </c>
       <c r="K43" s="34">
         <v>46119</v>
@@ -8048,15 +8125,15 @@
         <v>190</v>
       </c>
       <c r="V43" s="39" t="str">
-        <f>IF(T43&lt;&gt;"","9 - Closed",IF(S43&lt;&gt;"","8 - Definitive Agreement",IF(Q43&lt;&gt;"","7 - Diligence",IF(P43&lt;&gt;"","6 - LOI Signed",IF(O43&lt;&gt;"","5 - Mgmt Meeting",IF(L43&lt;&gt;"","4 - IOI Received",IF(K43&lt;&gt;"","3 - CIM Sent",IF(J43&lt;&gt;"","2 - Teaser Sent",IF(I43&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
+        <f>IF(T43&lt;&gt;"","9 - Closed",IF(S43&lt;&gt;"","8 - Definitive Agreement",IF(Q43&lt;&gt;"","7 - Diligence",IF(P43&lt;&gt;"","6 - LOI Signed",IF(O43&lt;&gt;"","5 - Mgmt Meeting",IF(L43&lt;&gt;"","4 - IOI Received",IF(K43&lt;&gt;"","3 - CIM Sent",IF(J43&lt;&gt;"","2 - NDA Signed",IF(I43&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
         <v>3 - CIM Sent</v>
       </c>
       <c r="W43" s="39">
-        <f ca="1">IF(COUNT(G43:T43)=0,"-",TODAY()-MAX(G43:T43))</f>
-        <v>121</v>
+        <f>IF(COUNT(G43:T43)=0,"-",Dashboard!$I$6-MAX(G43:T43))</f>
+        <v>125</v>
       </c>
       <c r="X43" s="40" t="s">
-        <v>191</v>
+        <v>815</v>
       </c>
     </row>
     <row r="44" spans="1:24" ht="15" customHeight="1">
@@ -8085,10 +8162,10 @@
         <v>46099</v>
       </c>
       <c r="I44" s="34">
+        <v>46098</v>
+      </c>
+      <c r="J44" s="34">
         <v>46103</v>
-      </c>
-      <c r="J44" s="34">
-        <v>46105</v>
       </c>
       <c r="K44" s="34">
         <v>46113</v>
@@ -8103,18 +8180,18 @@
       <c r="S44" s="37"/>
       <c r="T44" s="37"/>
       <c r="U44" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V44" s="39" t="str">
-        <f>IF(T44&lt;&gt;"","9 - Closed",IF(S44&lt;&gt;"","8 - Definitive Agreement",IF(Q44&lt;&gt;"","7 - Diligence",IF(P44&lt;&gt;"","6 - LOI Signed",IF(O44&lt;&gt;"","5 - Mgmt Meeting",IF(L44&lt;&gt;"","4 - IOI Received",IF(K44&lt;&gt;"","3 - CIM Sent",IF(J44&lt;&gt;"","2 - Teaser Sent",IF(I44&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
+        <f>IF(T44&lt;&gt;"","9 - Closed",IF(S44&lt;&gt;"","8 - Definitive Agreement",IF(Q44&lt;&gt;"","7 - Diligence",IF(P44&lt;&gt;"","6 - LOI Signed",IF(O44&lt;&gt;"","5 - Mgmt Meeting",IF(L44&lt;&gt;"","4 - IOI Received",IF(K44&lt;&gt;"","3 - CIM Sent",IF(J44&lt;&gt;"","2 - NDA Signed",IF(I44&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
         <v>3 - CIM Sent</v>
       </c>
       <c r="W44" s="39">
-        <f ca="1">IF(COUNT(G44:T44)=0,"-",TODAY()-MAX(G44:T44))</f>
-        <v>127</v>
+        <f>IF(COUNT(G44:T44)=0,"-",Dashboard!$I$6-MAX(G44:T44))</f>
+        <v>131</v>
       </c>
       <c r="X44" s="40" t="s">
-        <v>96</v>
+        <v>814</v>
       </c>
     </row>
     <row r="45" spans="1:24" ht="15" customHeight="1">
@@ -8143,10 +8220,10 @@
         <v>46104</v>
       </c>
       <c r="I45" s="34">
+        <v>46103</v>
+      </c>
+      <c r="J45" s="34">
         <v>46113</v>
-      </c>
-      <c r="J45" s="34">
-        <v>46114</v>
       </c>
       <c r="K45" s="34">
         <v>46121</v>
@@ -8161,18 +8238,18 @@
       <c r="S45" s="37"/>
       <c r="T45" s="37"/>
       <c r="U45" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V45" s="39" t="str">
-        <f>IF(T45&lt;&gt;"","9 - Closed",IF(S45&lt;&gt;"","8 - Definitive Agreement",IF(Q45&lt;&gt;"","7 - Diligence",IF(P45&lt;&gt;"","6 - LOI Signed",IF(O45&lt;&gt;"","5 - Mgmt Meeting",IF(L45&lt;&gt;"","4 - IOI Received",IF(K45&lt;&gt;"","3 - CIM Sent",IF(J45&lt;&gt;"","2 - Teaser Sent",IF(I45&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
+        <f>IF(T45&lt;&gt;"","9 - Closed",IF(S45&lt;&gt;"","8 - Definitive Agreement",IF(Q45&lt;&gt;"","7 - Diligence",IF(P45&lt;&gt;"","6 - LOI Signed",IF(O45&lt;&gt;"","5 - Mgmt Meeting",IF(L45&lt;&gt;"","4 - IOI Received",IF(K45&lt;&gt;"","3 - CIM Sent",IF(J45&lt;&gt;"","2 - NDA Signed",IF(I45&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
         <v>3 - CIM Sent</v>
       </c>
       <c r="W45" s="39">
-        <f ca="1">IF(COUNT(G45:T45)=0,"-",TODAY()-MAX(G45:T45))</f>
-        <v>119</v>
+        <f>IF(COUNT(G45:T45)=0,"-",Dashboard!$I$6-MAX(G45:T45))</f>
+        <v>123</v>
       </c>
       <c r="X45" s="40" t="s">
-        <v>96</v>
+        <v>814</v>
       </c>
     </row>
     <row r="46" spans="1:24" ht="15" customHeight="1">
@@ -8201,10 +8278,10 @@
         <v>46088</v>
       </c>
       <c r="I46" s="34">
+        <v>46087</v>
+      </c>
+      <c r="J46" s="34">
         <v>46097</v>
-      </c>
-      <c r="J46" s="34">
-        <v>46099</v>
       </c>
       <c r="K46" s="34">
         <v>46104</v>
@@ -8219,18 +8296,18 @@
       <c r="S46" s="37"/>
       <c r="T46" s="37"/>
       <c r="U46" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V46" s="39" t="str">
-        <f>IF(T46&lt;&gt;"","9 - Closed",IF(S46&lt;&gt;"","8 - Definitive Agreement",IF(Q46&lt;&gt;"","7 - Diligence",IF(P46&lt;&gt;"","6 - LOI Signed",IF(O46&lt;&gt;"","5 - Mgmt Meeting",IF(L46&lt;&gt;"","4 - IOI Received",IF(K46&lt;&gt;"","3 - CIM Sent",IF(J46&lt;&gt;"","2 - Teaser Sent",IF(I46&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
+        <f>IF(T46&lt;&gt;"","9 - Closed",IF(S46&lt;&gt;"","8 - Definitive Agreement",IF(Q46&lt;&gt;"","7 - Diligence",IF(P46&lt;&gt;"","6 - LOI Signed",IF(O46&lt;&gt;"","5 - Mgmt Meeting",IF(L46&lt;&gt;"","4 - IOI Received",IF(K46&lt;&gt;"","3 - CIM Sent",IF(J46&lt;&gt;"","2 - NDA Signed",IF(I46&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
         <v>3 - CIM Sent</v>
       </c>
       <c r="W46" s="39">
-        <f ca="1">IF(COUNT(G46:T46)=0,"-",TODAY()-MAX(G46:T46))</f>
-        <v>136</v>
+        <f>IF(COUNT(G46:T46)=0,"-",Dashboard!$I$6-MAX(G46:T46))</f>
+        <v>140</v>
       </c>
       <c r="X46" s="40" t="s">
-        <v>96</v>
+        <v>814</v>
       </c>
     </row>
     <row r="47" spans="1:24" ht="15" customHeight="1">
@@ -8259,10 +8336,10 @@
         <v>46104</v>
       </c>
       <c r="I47" s="34">
+        <v>46103</v>
+      </c>
+      <c r="J47" s="34">
         <v>46116</v>
-      </c>
-      <c r="J47" s="34">
-        <v>46118</v>
       </c>
       <c r="K47" s="34">
         <v>46124</v>
@@ -8280,15 +8357,15 @@
         <v>190</v>
       </c>
       <c r="V47" s="39" t="str">
-        <f>IF(T47&lt;&gt;"","9 - Closed",IF(S47&lt;&gt;"","8 - Definitive Agreement",IF(Q47&lt;&gt;"","7 - Diligence",IF(P47&lt;&gt;"","6 - LOI Signed",IF(O47&lt;&gt;"","5 - Mgmt Meeting",IF(L47&lt;&gt;"","4 - IOI Received",IF(K47&lt;&gt;"","3 - CIM Sent",IF(J47&lt;&gt;"","2 - Teaser Sent",IF(I47&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
+        <f>IF(T47&lt;&gt;"","9 - Closed",IF(S47&lt;&gt;"","8 - Definitive Agreement",IF(Q47&lt;&gt;"","7 - Diligence",IF(P47&lt;&gt;"","6 - LOI Signed",IF(O47&lt;&gt;"","5 - Mgmt Meeting",IF(L47&lt;&gt;"","4 - IOI Received",IF(K47&lt;&gt;"","3 - CIM Sent",IF(J47&lt;&gt;"","2 - NDA Signed",IF(I47&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
         <v>3 - CIM Sent</v>
       </c>
       <c r="W47" s="39">
-        <f ca="1">IF(COUNT(G47:T47)=0,"-",TODAY()-MAX(G47:T47))</f>
-        <v>116</v>
+        <f>IF(COUNT(G47:T47)=0,"-",Dashboard!$I$6-MAX(G47:T47))</f>
+        <v>120</v>
       </c>
       <c r="X47" s="40" t="s">
-        <v>191</v>
+        <v>815</v>
       </c>
     </row>
     <row r="48" spans="1:24" ht="15" customHeight="1">
@@ -8317,10 +8394,10 @@
         <v>46101</v>
       </c>
       <c r="I48" s="34">
+        <v>46100</v>
+      </c>
+      <c r="J48" s="34">
         <v>46103</v>
-      </c>
-      <c r="J48" s="34">
-        <v>46104</v>
       </c>
       <c r="K48" s="34">
         <v>46112</v>
@@ -8338,15 +8415,15 @@
         <v>190</v>
       </c>
       <c r="V48" s="39" t="str">
-        <f>IF(T48&lt;&gt;"","9 - Closed",IF(S48&lt;&gt;"","8 - Definitive Agreement",IF(Q48&lt;&gt;"","7 - Diligence",IF(P48&lt;&gt;"","6 - LOI Signed",IF(O48&lt;&gt;"","5 - Mgmt Meeting",IF(L48&lt;&gt;"","4 - IOI Received",IF(K48&lt;&gt;"","3 - CIM Sent",IF(J48&lt;&gt;"","2 - Teaser Sent",IF(I48&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
+        <f>IF(T48&lt;&gt;"","9 - Closed",IF(S48&lt;&gt;"","8 - Definitive Agreement",IF(Q48&lt;&gt;"","7 - Diligence",IF(P48&lt;&gt;"","6 - LOI Signed",IF(O48&lt;&gt;"","5 - Mgmt Meeting",IF(L48&lt;&gt;"","4 - IOI Received",IF(K48&lt;&gt;"","3 - CIM Sent",IF(J48&lt;&gt;"","2 - NDA Signed",IF(I48&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
         <v>3 - CIM Sent</v>
       </c>
       <c r="W48" s="39">
-        <f ca="1">IF(COUNT(G48:T48)=0,"-",TODAY()-MAX(G48:T48))</f>
-        <v>128</v>
+        <f>IF(COUNT(G48:T48)=0,"-",Dashboard!$I$6-MAX(G48:T48))</f>
+        <v>132</v>
       </c>
       <c r="X48" s="40" t="s">
-        <v>191</v>
+        <v>815</v>
       </c>
     </row>
     <row r="49" spans="1:24" ht="15" customHeight="1">
@@ -8375,10 +8452,10 @@
         <v>46107</v>
       </c>
       <c r="I49" s="34">
+        <v>46106</v>
+      </c>
+      <c r="J49" s="34">
         <v>46116</v>
-      </c>
-      <c r="J49" s="34">
-        <v>46118</v>
       </c>
       <c r="K49" s="34">
         <v>46127</v>
@@ -8396,15 +8473,15 @@
         <v>190</v>
       </c>
       <c r="V49" s="39" t="str">
-        <f>IF(T49&lt;&gt;"","9 - Closed",IF(S49&lt;&gt;"","8 - Definitive Agreement",IF(Q49&lt;&gt;"","7 - Diligence",IF(P49&lt;&gt;"","6 - LOI Signed",IF(O49&lt;&gt;"","5 - Mgmt Meeting",IF(L49&lt;&gt;"","4 - IOI Received",IF(K49&lt;&gt;"","3 - CIM Sent",IF(J49&lt;&gt;"","2 - Teaser Sent",IF(I49&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
+        <f>IF(T49&lt;&gt;"","9 - Closed",IF(S49&lt;&gt;"","8 - Definitive Agreement",IF(Q49&lt;&gt;"","7 - Diligence",IF(P49&lt;&gt;"","6 - LOI Signed",IF(O49&lt;&gt;"","5 - Mgmt Meeting",IF(L49&lt;&gt;"","4 - IOI Received",IF(K49&lt;&gt;"","3 - CIM Sent",IF(J49&lt;&gt;"","2 - NDA Signed",IF(I49&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
         <v>3 - CIM Sent</v>
       </c>
       <c r="W49" s="39">
-        <f ca="1">IF(COUNT(G49:T49)=0,"-",TODAY()-MAX(G49:T49))</f>
-        <v>113</v>
+        <f>IF(COUNT(G49:T49)=0,"-",Dashboard!$I$6-MAX(G49:T49))</f>
+        <v>117</v>
       </c>
       <c r="X49" s="40" t="s">
-        <v>191</v>
+        <v>815</v>
       </c>
     </row>
     <row r="50" spans="1:24" ht="15" customHeight="1">
@@ -8433,10 +8510,10 @@
         <v>46091</v>
       </c>
       <c r="I50" s="34">
+        <v>46090</v>
+      </c>
+      <c r="J50" s="34">
         <v>46098</v>
-      </c>
-      <c r="J50" s="34">
-        <v>46100</v>
       </c>
       <c r="K50" s="34">
         <v>46104</v>
@@ -8454,15 +8531,15 @@
         <v>190</v>
       </c>
       <c r="V50" s="39" t="str">
-        <f>IF(T50&lt;&gt;"","9 - Closed",IF(S50&lt;&gt;"","8 - Definitive Agreement",IF(Q50&lt;&gt;"","7 - Diligence",IF(P50&lt;&gt;"","6 - LOI Signed",IF(O50&lt;&gt;"","5 - Mgmt Meeting",IF(L50&lt;&gt;"","4 - IOI Received",IF(K50&lt;&gt;"","3 - CIM Sent",IF(J50&lt;&gt;"","2 - Teaser Sent",IF(I50&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
+        <f>IF(T50&lt;&gt;"","9 - Closed",IF(S50&lt;&gt;"","8 - Definitive Agreement",IF(Q50&lt;&gt;"","7 - Diligence",IF(P50&lt;&gt;"","6 - LOI Signed",IF(O50&lt;&gt;"","5 - Mgmt Meeting",IF(L50&lt;&gt;"","4 - IOI Received",IF(K50&lt;&gt;"","3 - CIM Sent",IF(J50&lt;&gt;"","2 - NDA Signed",IF(I50&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
         <v>3 - CIM Sent</v>
       </c>
       <c r="W50" s="39">
-        <f ca="1">IF(COUNT(G50:T50)=0,"-",TODAY()-MAX(G50:T50))</f>
-        <v>136</v>
+        <f>IF(COUNT(G50:T50)=0,"-",Dashboard!$I$6-MAX(G50:T50))</f>
+        <v>140</v>
       </c>
       <c r="X50" s="40" t="s">
-        <v>191</v>
+        <v>815</v>
       </c>
     </row>
     <row r="51" spans="1:24" ht="15" customHeight="1">
@@ -8491,10 +8568,10 @@
         <v>46100</v>
       </c>
       <c r="I51" s="34">
+        <v>46097</v>
+      </c>
+      <c r="J51" s="34">
         <v>46111</v>
-      </c>
-      <c r="J51" s="34">
-        <v>46113</v>
       </c>
       <c r="K51" s="34">
         <v>46123</v>
@@ -8509,18 +8586,18 @@
       <c r="S51" s="37"/>
       <c r="T51" s="37"/>
       <c r="U51" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V51" s="39" t="str">
-        <f>IF(T51&lt;&gt;"","9 - Closed",IF(S51&lt;&gt;"","8 - Definitive Agreement",IF(Q51&lt;&gt;"","7 - Diligence",IF(P51&lt;&gt;"","6 - LOI Signed",IF(O51&lt;&gt;"","5 - Mgmt Meeting",IF(L51&lt;&gt;"","4 - IOI Received",IF(K51&lt;&gt;"","3 - CIM Sent",IF(J51&lt;&gt;"","2 - Teaser Sent",IF(I51&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
+        <f>IF(T51&lt;&gt;"","9 - Closed",IF(S51&lt;&gt;"","8 - Definitive Agreement",IF(Q51&lt;&gt;"","7 - Diligence",IF(P51&lt;&gt;"","6 - LOI Signed",IF(O51&lt;&gt;"","5 - Mgmt Meeting",IF(L51&lt;&gt;"","4 - IOI Received",IF(K51&lt;&gt;"","3 - CIM Sent",IF(J51&lt;&gt;"","2 - NDA Signed",IF(I51&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
         <v>3 - CIM Sent</v>
       </c>
       <c r="W51" s="39">
-        <f ca="1">IF(COUNT(G51:T51)=0,"-",TODAY()-MAX(G51:T51))</f>
-        <v>117</v>
+        <f>IF(COUNT(G51:T51)=0,"-",Dashboard!$I$6-MAX(G51:T51))</f>
+        <v>121</v>
       </c>
       <c r="X51" s="40" t="s">
-        <v>96</v>
+        <v>814</v>
       </c>
     </row>
     <row r="52" spans="1:24" ht="15" customHeight="1">
@@ -8549,10 +8626,10 @@
         <v>46106</v>
       </c>
       <c r="I52" s="34">
+        <v>46102</v>
+      </c>
+      <c r="J52" s="34">
         <v>46117</v>
-      </c>
-      <c r="J52" s="34">
-        <v>46119</v>
       </c>
       <c r="K52" s="34">
         <v>46125</v>
@@ -8570,15 +8647,15 @@
         <v>190</v>
       </c>
       <c r="V52" s="39" t="str">
-        <f>IF(T52&lt;&gt;"","9 - Closed",IF(S52&lt;&gt;"","8 - Definitive Agreement",IF(Q52&lt;&gt;"","7 - Diligence",IF(P52&lt;&gt;"","6 - LOI Signed",IF(O52&lt;&gt;"","5 - Mgmt Meeting",IF(L52&lt;&gt;"","4 - IOI Received",IF(K52&lt;&gt;"","3 - CIM Sent",IF(J52&lt;&gt;"","2 - Teaser Sent",IF(I52&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
+        <f>IF(T52&lt;&gt;"","9 - Closed",IF(S52&lt;&gt;"","8 - Definitive Agreement",IF(Q52&lt;&gt;"","7 - Diligence",IF(P52&lt;&gt;"","6 - LOI Signed",IF(O52&lt;&gt;"","5 - Mgmt Meeting",IF(L52&lt;&gt;"","4 - IOI Received",IF(K52&lt;&gt;"","3 - CIM Sent",IF(J52&lt;&gt;"","2 - NDA Signed",IF(I52&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
         <v>3 - CIM Sent</v>
       </c>
       <c r="W52" s="39">
-        <f ca="1">IF(COUNT(G52:T52)=0,"-",TODAY()-MAX(G52:T52))</f>
-        <v>115</v>
+        <f>IF(COUNT(G52:T52)=0,"-",Dashboard!$I$6-MAX(G52:T52))</f>
+        <v>119</v>
       </c>
       <c r="X52" s="40" t="s">
-        <v>191</v>
+        <v>815</v>
       </c>
     </row>
     <row r="53" spans="1:24" ht="15" customHeight="1">
@@ -8607,10 +8684,10 @@
         <v>46102</v>
       </c>
       <c r="I53" s="34">
+        <v>46098</v>
+      </c>
+      <c r="J53" s="34">
         <v>46105</v>
-      </c>
-      <c r="J53" s="34">
-        <v>46107</v>
       </c>
       <c r="K53" s="34">
         <v>46110</v>
@@ -8625,18 +8702,18 @@
       <c r="S53" s="37"/>
       <c r="T53" s="37"/>
       <c r="U53" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V53" s="39" t="str">
-        <f>IF(T53&lt;&gt;"","9 - Closed",IF(S53&lt;&gt;"","8 - Definitive Agreement",IF(Q53&lt;&gt;"","7 - Diligence",IF(P53&lt;&gt;"","6 - LOI Signed",IF(O53&lt;&gt;"","5 - Mgmt Meeting",IF(L53&lt;&gt;"","4 - IOI Received",IF(K53&lt;&gt;"","3 - CIM Sent",IF(J53&lt;&gt;"","2 - Teaser Sent",IF(I53&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
+        <f>IF(T53&lt;&gt;"","9 - Closed",IF(S53&lt;&gt;"","8 - Definitive Agreement",IF(Q53&lt;&gt;"","7 - Diligence",IF(P53&lt;&gt;"","6 - LOI Signed",IF(O53&lt;&gt;"","5 - Mgmt Meeting",IF(L53&lt;&gt;"","4 - IOI Received",IF(K53&lt;&gt;"","3 - CIM Sent",IF(J53&lt;&gt;"","2 - NDA Signed",IF(I53&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
         <v>3 - CIM Sent</v>
       </c>
       <c r="W53" s="39">
-        <f ca="1">IF(COUNT(G53:T53)=0,"-",TODAY()-MAX(G53:T53))</f>
-        <v>130</v>
+        <f>IF(COUNT(G53:T53)=0,"-",Dashboard!$I$6-MAX(G53:T53))</f>
+        <v>134</v>
       </c>
       <c r="X53" s="40" t="s">
-        <v>96</v>
+        <v>814</v>
       </c>
     </row>
     <row r="54" spans="1:24" ht="15" customHeight="1">
@@ -8665,12 +8742,14 @@
         <v>46091</v>
       </c>
       <c r="I54" s="34">
+        <v>46089</v>
+      </c>
+      <c r="J54" s="34">
         <v>46099</v>
       </c>
-      <c r="J54" s="34">
+      <c r="K54" s="34">
         <v>46100</v>
       </c>
-      <c r="K54" s="37"/>
       <c r="L54" s="37"/>
       <c r="M54" s="33"/>
       <c r="N54" s="33"/>
@@ -8681,18 +8760,18 @@
       <c r="S54" s="37"/>
       <c r="T54" s="37"/>
       <c r="U54" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V54" s="39" t="str">
-        <f>IF(T54&lt;&gt;"","9 - Closed",IF(S54&lt;&gt;"","8 - Definitive Agreement",IF(Q54&lt;&gt;"","7 - Diligence",IF(P54&lt;&gt;"","6 - LOI Signed",IF(O54&lt;&gt;"","5 - Mgmt Meeting",IF(L54&lt;&gt;"","4 - IOI Received",IF(K54&lt;&gt;"","3 - CIM Sent",IF(J54&lt;&gt;"","2 - Teaser Sent",IF(I54&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>2 - Teaser Sent</v>
+        <f>IF(T54&lt;&gt;"","9 - Closed",IF(S54&lt;&gt;"","8 - Definitive Agreement",IF(Q54&lt;&gt;"","7 - Diligence",IF(P54&lt;&gt;"","6 - LOI Signed",IF(O54&lt;&gt;"","5 - Mgmt Meeting",IF(L54&lt;&gt;"","4 - IOI Received",IF(K54&lt;&gt;"","3 - CIM Sent",IF(J54&lt;&gt;"","2 - NDA Signed",IF(I54&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>3 - CIM Sent</v>
       </c>
       <c r="W54" s="39">
-        <f ca="1">IF(COUNT(G54:T54)=0,"-",TODAY()-MAX(G54:T54))</f>
-        <v>140</v>
+        <f>IF(COUNT(G54:T54)=0,"-",Dashboard!$I$6-MAX(G54:T54))</f>
+        <v>144</v>
       </c>
       <c r="X54" s="40" t="s">
-        <v>96</v>
+        <v>814</v>
       </c>
     </row>
     <row r="55" spans="1:24" ht="15" customHeight="1">
@@ -8721,12 +8800,14 @@
         <v>46093</v>
       </c>
       <c r="I55" s="34">
+        <v>46091</v>
+      </c>
+      <c r="J55" s="34">
         <v>46101</v>
       </c>
-      <c r="J55" s="34">
+      <c r="K55" s="34">
         <v>46102</v>
       </c>
-      <c r="K55" s="37"/>
       <c r="L55" s="37"/>
       <c r="M55" s="33"/>
       <c r="N55" s="33"/>
@@ -8737,18 +8818,18 @@
       <c r="S55" s="37"/>
       <c r="T55" s="37"/>
       <c r="U55" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V55" s="39" t="str">
-        <f>IF(T55&lt;&gt;"","9 - Closed",IF(S55&lt;&gt;"","8 - Definitive Agreement",IF(Q55&lt;&gt;"","7 - Diligence",IF(P55&lt;&gt;"","6 - LOI Signed",IF(O55&lt;&gt;"","5 - Mgmt Meeting",IF(L55&lt;&gt;"","4 - IOI Received",IF(K55&lt;&gt;"","3 - CIM Sent",IF(J55&lt;&gt;"","2 - Teaser Sent",IF(I55&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>2 - Teaser Sent</v>
+        <f>IF(T55&lt;&gt;"","9 - Closed",IF(S55&lt;&gt;"","8 - Definitive Agreement",IF(Q55&lt;&gt;"","7 - Diligence",IF(P55&lt;&gt;"","6 - LOI Signed",IF(O55&lt;&gt;"","5 - Mgmt Meeting",IF(L55&lt;&gt;"","4 - IOI Received",IF(K55&lt;&gt;"","3 - CIM Sent",IF(J55&lt;&gt;"","2 - NDA Signed",IF(I55&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>3 - CIM Sent</v>
       </c>
       <c r="W55" s="39">
-        <f ca="1">IF(COUNT(G55:T55)=0,"-",TODAY()-MAX(G55:T55))</f>
-        <v>138</v>
+        <f>IF(COUNT(G55:T55)=0,"-",Dashboard!$I$6-MAX(G55:T55))</f>
+        <v>142</v>
       </c>
       <c r="X55" s="40" t="s">
-        <v>96</v>
+        <v>814</v>
       </c>
     </row>
     <row r="56" spans="1:24" ht="15" customHeight="1">
@@ -8777,12 +8858,14 @@
         <v>46095</v>
       </c>
       <c r="I56" s="34">
+        <v>46091</v>
+      </c>
+      <c r="J56" s="34">
         <v>46103</v>
       </c>
-      <c r="J56" s="34">
+      <c r="K56" s="34">
         <v>46104</v>
       </c>
-      <c r="K56" s="37"/>
       <c r="L56" s="37"/>
       <c r="M56" s="33"/>
       <c r="N56" s="33"/>
@@ -8793,18 +8876,18 @@
       <c r="S56" s="37"/>
       <c r="T56" s="37"/>
       <c r="U56" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V56" s="39" t="str">
-        <f>IF(T56&lt;&gt;"","9 - Closed",IF(S56&lt;&gt;"","8 - Definitive Agreement",IF(Q56&lt;&gt;"","7 - Diligence",IF(P56&lt;&gt;"","6 - LOI Signed",IF(O56&lt;&gt;"","5 - Mgmt Meeting",IF(L56&lt;&gt;"","4 - IOI Received",IF(K56&lt;&gt;"","3 - CIM Sent",IF(J56&lt;&gt;"","2 - Teaser Sent",IF(I56&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>2 - Teaser Sent</v>
+        <f>IF(T56&lt;&gt;"","9 - Closed",IF(S56&lt;&gt;"","8 - Definitive Agreement",IF(Q56&lt;&gt;"","7 - Diligence",IF(P56&lt;&gt;"","6 - LOI Signed",IF(O56&lt;&gt;"","5 - Mgmt Meeting",IF(L56&lt;&gt;"","4 - IOI Received",IF(K56&lt;&gt;"","3 - CIM Sent",IF(J56&lt;&gt;"","2 - NDA Signed",IF(I56&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>3 - CIM Sent</v>
       </c>
       <c r="W56" s="39">
-        <f ca="1">IF(COUNT(G56:T56)=0,"-",TODAY()-MAX(G56:T56))</f>
-        <v>136</v>
+        <f>IF(COUNT(G56:T56)=0,"-",Dashboard!$I$6-MAX(G56:T56))</f>
+        <v>140</v>
       </c>
       <c r="X56" s="40" t="s">
-        <v>96</v>
+        <v>814</v>
       </c>
     </row>
     <row r="57" spans="1:24" ht="15" customHeight="1">
@@ -8833,12 +8916,14 @@
         <v>46090</v>
       </c>
       <c r="I57" s="34">
+        <v>46089</v>
+      </c>
+      <c r="J57" s="34">
         <v>46097</v>
       </c>
-      <c r="J57" s="34">
+      <c r="K57" s="34">
         <v>46098</v>
       </c>
-      <c r="K57" s="37"/>
       <c r="L57" s="37"/>
       <c r="M57" s="33"/>
       <c r="N57" s="33"/>
@@ -8849,18 +8934,18 @@
       <c r="S57" s="37"/>
       <c r="T57" s="37"/>
       <c r="U57" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V57" s="39" t="str">
-        <f>IF(T57&lt;&gt;"","9 - Closed",IF(S57&lt;&gt;"","8 - Definitive Agreement",IF(Q57&lt;&gt;"","7 - Diligence",IF(P57&lt;&gt;"","6 - LOI Signed",IF(O57&lt;&gt;"","5 - Mgmt Meeting",IF(L57&lt;&gt;"","4 - IOI Received",IF(K57&lt;&gt;"","3 - CIM Sent",IF(J57&lt;&gt;"","2 - Teaser Sent",IF(I57&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>2 - Teaser Sent</v>
+        <f>IF(T57&lt;&gt;"","9 - Closed",IF(S57&lt;&gt;"","8 - Definitive Agreement",IF(Q57&lt;&gt;"","7 - Diligence",IF(P57&lt;&gt;"","6 - LOI Signed",IF(O57&lt;&gt;"","5 - Mgmt Meeting",IF(L57&lt;&gt;"","4 - IOI Received",IF(K57&lt;&gt;"","3 - CIM Sent",IF(J57&lt;&gt;"","2 - NDA Signed",IF(I57&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>3 - CIM Sent</v>
       </c>
       <c r="W57" s="39">
-        <f ca="1">IF(COUNT(G57:T57)=0,"-",TODAY()-MAX(G57:T57))</f>
-        <v>142</v>
+        <f>IF(COUNT(G57:T57)=0,"-",Dashboard!$I$6-MAX(G57:T57))</f>
+        <v>146</v>
       </c>
       <c r="X57" s="40" t="s">
-        <v>96</v>
+        <v>814</v>
       </c>
     </row>
     <row r="58" spans="1:24" ht="15" customHeight="1">
@@ -8889,12 +8974,14 @@
         <v>46101</v>
       </c>
       <c r="I58" s="34">
+        <v>46098</v>
+      </c>
+      <c r="J58" s="34">
         <v>46113</v>
       </c>
-      <c r="J58" s="34">
+      <c r="K58" s="34">
         <v>46114</v>
       </c>
-      <c r="K58" s="37"/>
       <c r="L58" s="37"/>
       <c r="M58" s="33"/>
       <c r="N58" s="33"/>
@@ -8905,18 +8992,18 @@
       <c r="S58" s="37"/>
       <c r="T58" s="37"/>
       <c r="U58" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V58" s="39" t="str">
-        <f>IF(T58&lt;&gt;"","9 - Closed",IF(S58&lt;&gt;"","8 - Definitive Agreement",IF(Q58&lt;&gt;"","7 - Diligence",IF(P58&lt;&gt;"","6 - LOI Signed",IF(O58&lt;&gt;"","5 - Mgmt Meeting",IF(L58&lt;&gt;"","4 - IOI Received",IF(K58&lt;&gt;"","3 - CIM Sent",IF(J58&lt;&gt;"","2 - Teaser Sent",IF(I58&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>2 - Teaser Sent</v>
+        <f>IF(T58&lt;&gt;"","9 - Closed",IF(S58&lt;&gt;"","8 - Definitive Agreement",IF(Q58&lt;&gt;"","7 - Diligence",IF(P58&lt;&gt;"","6 - LOI Signed",IF(O58&lt;&gt;"","5 - Mgmt Meeting",IF(L58&lt;&gt;"","4 - IOI Received",IF(K58&lt;&gt;"","3 - CIM Sent",IF(J58&lt;&gt;"","2 - NDA Signed",IF(I58&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>3 - CIM Sent</v>
       </c>
       <c r="W58" s="39">
-        <f ca="1">IF(COUNT(G58:T58)=0,"-",TODAY()-MAX(G58:T58))</f>
-        <v>126</v>
+        <f>IF(COUNT(G58:T58)=0,"-",Dashboard!$I$6-MAX(G58:T58))</f>
+        <v>130</v>
       </c>
       <c r="X58" s="40" t="s">
-        <v>96</v>
+        <v>814</v>
       </c>
     </row>
     <row r="59" spans="1:24" ht="15" customHeight="1">
@@ -8945,12 +9032,14 @@
         <v>46101</v>
       </c>
       <c r="I59" s="34">
+        <v>46098</v>
+      </c>
+      <c r="J59" s="34">
         <v>46105</v>
       </c>
-      <c r="J59" s="34">
+      <c r="K59" s="34">
         <v>46107</v>
       </c>
-      <c r="K59" s="37"/>
       <c r="L59" s="37"/>
       <c r="M59" s="33"/>
       <c r="N59" s="33"/>
@@ -8961,18 +9050,18 @@
       <c r="S59" s="37"/>
       <c r="T59" s="37"/>
       <c r="U59" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V59" s="39" t="str">
-        <f>IF(T59&lt;&gt;"","9 - Closed",IF(S59&lt;&gt;"","8 - Definitive Agreement",IF(Q59&lt;&gt;"","7 - Diligence",IF(P59&lt;&gt;"","6 - LOI Signed",IF(O59&lt;&gt;"","5 - Mgmt Meeting",IF(L59&lt;&gt;"","4 - IOI Received",IF(K59&lt;&gt;"","3 - CIM Sent",IF(J59&lt;&gt;"","2 - Teaser Sent",IF(I59&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>2 - Teaser Sent</v>
+        <f>IF(T59&lt;&gt;"","9 - Closed",IF(S59&lt;&gt;"","8 - Definitive Agreement",IF(Q59&lt;&gt;"","7 - Diligence",IF(P59&lt;&gt;"","6 - LOI Signed",IF(O59&lt;&gt;"","5 - Mgmt Meeting",IF(L59&lt;&gt;"","4 - IOI Received",IF(K59&lt;&gt;"","3 - CIM Sent",IF(J59&lt;&gt;"","2 - NDA Signed",IF(I59&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>3 - CIM Sent</v>
       </c>
       <c r="W59" s="39">
-        <f ca="1">IF(COUNT(G59:T59)=0,"-",TODAY()-MAX(G59:T59))</f>
-        <v>133</v>
+        <f>IF(COUNT(G59:T59)=0,"-",Dashboard!$I$6-MAX(G59:T59))</f>
+        <v>137</v>
       </c>
       <c r="X59" s="40" t="s">
-        <v>96</v>
+        <v>814</v>
       </c>
     </row>
     <row r="60" spans="1:24" ht="15" customHeight="1">
@@ -9001,12 +9090,14 @@
         <v>46112</v>
       </c>
       <c r="I60" s="34">
-        <v>46115</v>
+        <v>46108</v>
       </c>
       <c r="J60" s="34">
         <v>46115</v>
       </c>
-      <c r="K60" s="37"/>
+      <c r="K60" s="34">
+        <v>46115</v>
+      </c>
       <c r="L60" s="37"/>
       <c r="M60" s="33"/>
       <c r="N60" s="33"/>
@@ -9017,18 +9108,18 @@
       <c r="S60" s="37"/>
       <c r="T60" s="37"/>
       <c r="U60" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V60" s="39" t="str">
-        <f>IF(T60&lt;&gt;"","9 - Closed",IF(S60&lt;&gt;"","8 - Definitive Agreement",IF(Q60&lt;&gt;"","7 - Diligence",IF(P60&lt;&gt;"","6 - LOI Signed",IF(O60&lt;&gt;"","5 - Mgmt Meeting",IF(L60&lt;&gt;"","4 - IOI Received",IF(K60&lt;&gt;"","3 - CIM Sent",IF(J60&lt;&gt;"","2 - Teaser Sent",IF(I60&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>2 - Teaser Sent</v>
+        <f>IF(T60&lt;&gt;"","9 - Closed",IF(S60&lt;&gt;"","8 - Definitive Agreement",IF(Q60&lt;&gt;"","7 - Diligence",IF(P60&lt;&gt;"","6 - LOI Signed",IF(O60&lt;&gt;"","5 - Mgmt Meeting",IF(L60&lt;&gt;"","4 - IOI Received",IF(K60&lt;&gt;"","3 - CIM Sent",IF(J60&lt;&gt;"","2 - NDA Signed",IF(I60&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>3 - CIM Sent</v>
       </c>
       <c r="W60" s="39">
-        <f ca="1">IF(COUNT(G60:T60)=0,"-",TODAY()-MAX(G60:T60))</f>
-        <v>125</v>
+        <f>IF(COUNT(G60:T60)=0,"-",Dashboard!$I$6-MAX(G60:T60))</f>
+        <v>129</v>
       </c>
       <c r="X60" s="40" t="s">
-        <v>96</v>
+        <v>814</v>
       </c>
     </row>
     <row r="61" spans="1:24" ht="15" customHeight="1">
@@ -9057,12 +9148,14 @@
         <v>46096</v>
       </c>
       <c r="I61" s="34">
+        <v>46095</v>
+      </c>
+      <c r="J61" s="34">
         <v>46099</v>
       </c>
-      <c r="J61" s="34">
+      <c r="K61" s="34">
         <v>46100</v>
       </c>
-      <c r="K61" s="37"/>
       <c r="L61" s="37"/>
       <c r="M61" s="33"/>
       <c r="N61" s="33"/>
@@ -9073,18 +9166,18 @@
       <c r="S61" s="37"/>
       <c r="T61" s="37"/>
       <c r="U61" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V61" s="39" t="str">
-        <f>IF(T61&lt;&gt;"","9 - Closed",IF(S61&lt;&gt;"","8 - Definitive Agreement",IF(Q61&lt;&gt;"","7 - Diligence",IF(P61&lt;&gt;"","6 - LOI Signed",IF(O61&lt;&gt;"","5 - Mgmt Meeting",IF(L61&lt;&gt;"","4 - IOI Received",IF(K61&lt;&gt;"","3 - CIM Sent",IF(J61&lt;&gt;"","2 - Teaser Sent",IF(I61&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>2 - Teaser Sent</v>
+        <f>IF(T61&lt;&gt;"","9 - Closed",IF(S61&lt;&gt;"","8 - Definitive Agreement",IF(Q61&lt;&gt;"","7 - Diligence",IF(P61&lt;&gt;"","6 - LOI Signed",IF(O61&lt;&gt;"","5 - Mgmt Meeting",IF(L61&lt;&gt;"","4 - IOI Received",IF(K61&lt;&gt;"","3 - CIM Sent",IF(J61&lt;&gt;"","2 - NDA Signed",IF(I61&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>3 - CIM Sent</v>
       </c>
       <c r="W61" s="39">
-        <f ca="1">IF(COUNT(G61:T61)=0,"-",TODAY()-MAX(G61:T61))</f>
-        <v>140</v>
+        <f>IF(COUNT(G61:T61)=0,"-",Dashboard!$I$6-MAX(G61:T61))</f>
+        <v>144</v>
       </c>
       <c r="X61" s="40" t="s">
-        <v>96</v>
+        <v>814</v>
       </c>
     </row>
     <row r="62" spans="1:24" ht="15" customHeight="1">
@@ -9113,12 +9206,14 @@
         <v>46102</v>
       </c>
       <c r="I62" s="34">
-        <v>46109</v>
+        <v>46101</v>
       </c>
       <c r="J62" s="34">
         <v>46109</v>
       </c>
-      <c r="K62" s="37"/>
+      <c r="K62" s="34">
+        <v>46109</v>
+      </c>
       <c r="L62" s="37"/>
       <c r="M62" s="33"/>
       <c r="N62" s="33"/>
@@ -9129,18 +9224,18 @@
       <c r="S62" s="37"/>
       <c r="T62" s="37"/>
       <c r="U62" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V62" s="39" t="str">
-        <f>IF(T62&lt;&gt;"","9 - Closed",IF(S62&lt;&gt;"","8 - Definitive Agreement",IF(Q62&lt;&gt;"","7 - Diligence",IF(P62&lt;&gt;"","6 - LOI Signed",IF(O62&lt;&gt;"","5 - Mgmt Meeting",IF(L62&lt;&gt;"","4 - IOI Received",IF(K62&lt;&gt;"","3 - CIM Sent",IF(J62&lt;&gt;"","2 - Teaser Sent",IF(I62&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>2 - Teaser Sent</v>
+        <f>IF(T62&lt;&gt;"","9 - Closed",IF(S62&lt;&gt;"","8 - Definitive Agreement",IF(Q62&lt;&gt;"","7 - Diligence",IF(P62&lt;&gt;"","6 - LOI Signed",IF(O62&lt;&gt;"","5 - Mgmt Meeting",IF(L62&lt;&gt;"","4 - IOI Received",IF(K62&lt;&gt;"","3 - CIM Sent",IF(J62&lt;&gt;"","2 - NDA Signed",IF(I62&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>3 - CIM Sent</v>
       </c>
       <c r="W62" s="39">
-        <f ca="1">IF(COUNT(G62:T62)=0,"-",TODAY()-MAX(G62:T62))</f>
-        <v>131</v>
+        <f>IF(COUNT(G62:T62)=0,"-",Dashboard!$I$6-MAX(G62:T62))</f>
+        <v>135</v>
       </c>
       <c r="X62" s="40" t="s">
-        <v>96</v>
+        <v>814</v>
       </c>
     </row>
     <row r="63" spans="1:24" ht="15" customHeight="1">
@@ -9169,12 +9264,14 @@
         <v>46095</v>
       </c>
       <c r="I63" s="34">
+        <v>46094</v>
+      </c>
+      <c r="J63" s="34">
         <v>46106</v>
       </c>
-      <c r="J63" s="34">
+      <c r="K63" s="34">
         <v>46108</v>
       </c>
-      <c r="K63" s="37"/>
       <c r="L63" s="37"/>
       <c r="M63" s="33"/>
       <c r="N63" s="33"/>
@@ -9185,18 +9282,18 @@
       <c r="S63" s="37"/>
       <c r="T63" s="37"/>
       <c r="U63" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V63" s="39" t="str">
-        <f>IF(T63&lt;&gt;"","9 - Closed",IF(S63&lt;&gt;"","8 - Definitive Agreement",IF(Q63&lt;&gt;"","7 - Diligence",IF(P63&lt;&gt;"","6 - LOI Signed",IF(O63&lt;&gt;"","5 - Mgmt Meeting",IF(L63&lt;&gt;"","4 - IOI Received",IF(K63&lt;&gt;"","3 - CIM Sent",IF(J63&lt;&gt;"","2 - Teaser Sent",IF(I63&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>2 - Teaser Sent</v>
+        <f>IF(T63&lt;&gt;"","9 - Closed",IF(S63&lt;&gt;"","8 - Definitive Agreement",IF(Q63&lt;&gt;"","7 - Diligence",IF(P63&lt;&gt;"","6 - LOI Signed",IF(O63&lt;&gt;"","5 - Mgmt Meeting",IF(L63&lt;&gt;"","4 - IOI Received",IF(K63&lt;&gt;"","3 - CIM Sent",IF(J63&lt;&gt;"","2 - NDA Signed",IF(I63&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>3 - CIM Sent</v>
       </c>
       <c r="W63" s="39">
-        <f ca="1">IF(COUNT(G63:T63)=0,"-",TODAY()-MAX(G63:T63))</f>
-        <v>132</v>
+        <f>IF(COUNT(G63:T63)=0,"-",Dashboard!$I$6-MAX(G63:T63))</f>
+        <v>136</v>
       </c>
       <c r="X63" s="40" t="s">
-        <v>96</v>
+        <v>814</v>
       </c>
     </row>
     <row r="64" spans="1:24" ht="15" customHeight="1">
@@ -9225,12 +9322,14 @@
         <v>46097</v>
       </c>
       <c r="I64" s="34">
-        <v>46109</v>
+        <v>46094</v>
       </c>
       <c r="J64" s="34">
         <v>46109</v>
       </c>
-      <c r="K64" s="37"/>
+      <c r="K64" s="34">
+        <v>46109</v>
+      </c>
       <c r="L64" s="37"/>
       <c r="M64" s="33"/>
       <c r="N64" s="33"/>
@@ -9241,18 +9340,18 @@
       <c r="S64" s="37"/>
       <c r="T64" s="37"/>
       <c r="U64" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V64" s="39" t="str">
-        <f>IF(T64&lt;&gt;"","9 - Closed",IF(S64&lt;&gt;"","8 - Definitive Agreement",IF(Q64&lt;&gt;"","7 - Diligence",IF(P64&lt;&gt;"","6 - LOI Signed",IF(O64&lt;&gt;"","5 - Mgmt Meeting",IF(L64&lt;&gt;"","4 - IOI Received",IF(K64&lt;&gt;"","3 - CIM Sent",IF(J64&lt;&gt;"","2 - Teaser Sent",IF(I64&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>2 - Teaser Sent</v>
+        <f>IF(T64&lt;&gt;"","9 - Closed",IF(S64&lt;&gt;"","8 - Definitive Agreement",IF(Q64&lt;&gt;"","7 - Diligence",IF(P64&lt;&gt;"","6 - LOI Signed",IF(O64&lt;&gt;"","5 - Mgmt Meeting",IF(L64&lt;&gt;"","4 - IOI Received",IF(K64&lt;&gt;"","3 - CIM Sent",IF(J64&lt;&gt;"","2 - NDA Signed",IF(I64&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>3 - CIM Sent</v>
       </c>
       <c r="W64" s="39">
-        <f ca="1">IF(COUNT(G64:T64)=0,"-",TODAY()-MAX(G64:T64))</f>
-        <v>131</v>
+        <f>IF(COUNT(G64:T64)=0,"-",Dashboard!$I$6-MAX(G64:T64))</f>
+        <v>135</v>
       </c>
       <c r="X64" s="40" t="s">
-        <v>96</v>
+        <v>814</v>
       </c>
     </row>
     <row r="65" spans="1:24" ht="15" customHeight="1">
@@ -9281,12 +9380,14 @@
         <v>46095</v>
       </c>
       <c r="I65" s="34">
+        <v>46091</v>
+      </c>
+      <c r="J65" s="34">
         <v>46102</v>
       </c>
-      <c r="J65" s="34">
+      <c r="K65" s="34">
         <v>46104</v>
       </c>
-      <c r="K65" s="37"/>
       <c r="L65" s="37"/>
       <c r="M65" s="33"/>
       <c r="N65" s="33"/>
@@ -9297,18 +9398,18 @@
       <c r="S65" s="37"/>
       <c r="T65" s="37"/>
       <c r="U65" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V65" s="39" t="str">
-        <f>IF(T65&lt;&gt;"","9 - Closed",IF(S65&lt;&gt;"","8 - Definitive Agreement",IF(Q65&lt;&gt;"","7 - Diligence",IF(P65&lt;&gt;"","6 - LOI Signed",IF(O65&lt;&gt;"","5 - Mgmt Meeting",IF(L65&lt;&gt;"","4 - IOI Received",IF(K65&lt;&gt;"","3 - CIM Sent",IF(J65&lt;&gt;"","2 - Teaser Sent",IF(I65&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>2 - Teaser Sent</v>
+        <f>IF(T65&lt;&gt;"","9 - Closed",IF(S65&lt;&gt;"","8 - Definitive Agreement",IF(Q65&lt;&gt;"","7 - Diligence",IF(P65&lt;&gt;"","6 - LOI Signed",IF(O65&lt;&gt;"","5 - Mgmt Meeting",IF(L65&lt;&gt;"","4 - IOI Received",IF(K65&lt;&gt;"","3 - CIM Sent",IF(J65&lt;&gt;"","2 - NDA Signed",IF(I65&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>3 - CIM Sent</v>
       </c>
       <c r="W65" s="39">
-        <f ca="1">IF(COUNT(G65:T65)=0,"-",TODAY()-MAX(G65:T65))</f>
-        <v>136</v>
+        <f>IF(COUNT(G65:T65)=0,"-",Dashboard!$I$6-MAX(G65:T65))</f>
+        <v>140</v>
       </c>
       <c r="X65" s="40" t="s">
-        <v>96</v>
+        <v>814</v>
       </c>
     </row>
     <row r="66" spans="1:24" ht="15" customHeight="1">
@@ -9337,12 +9438,14 @@
         <v>46097</v>
       </c>
       <c r="I66" s="34">
+        <v>46093</v>
+      </c>
+      <c r="J66" s="34">
         <v>46099</v>
       </c>
-      <c r="J66" s="34">
+      <c r="K66" s="34">
         <v>46100</v>
       </c>
-      <c r="K66" s="37"/>
       <c r="L66" s="37"/>
       <c r="M66" s="33"/>
       <c r="N66" s="33"/>
@@ -9353,18 +9456,18 @@
       <c r="S66" s="37"/>
       <c r="T66" s="37"/>
       <c r="U66" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V66" s="39" t="str">
-        <f>IF(T66&lt;&gt;"","9 - Closed",IF(S66&lt;&gt;"","8 - Definitive Agreement",IF(Q66&lt;&gt;"","7 - Diligence",IF(P66&lt;&gt;"","6 - LOI Signed",IF(O66&lt;&gt;"","5 - Mgmt Meeting",IF(L66&lt;&gt;"","4 - IOI Received",IF(K66&lt;&gt;"","3 - CIM Sent",IF(J66&lt;&gt;"","2 - Teaser Sent",IF(I66&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>2 - Teaser Sent</v>
+        <f>IF(T66&lt;&gt;"","9 - Closed",IF(S66&lt;&gt;"","8 - Definitive Agreement",IF(Q66&lt;&gt;"","7 - Diligence",IF(P66&lt;&gt;"","6 - LOI Signed",IF(O66&lt;&gt;"","5 - Mgmt Meeting",IF(L66&lt;&gt;"","4 - IOI Received",IF(K66&lt;&gt;"","3 - CIM Sent",IF(J66&lt;&gt;"","2 - NDA Signed",IF(I66&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>3 - CIM Sent</v>
       </c>
       <c r="W66" s="39">
-        <f ca="1">IF(COUNT(G66:T66)=0,"-",TODAY()-MAX(G66:T66))</f>
-        <v>140</v>
+        <f>IF(COUNT(G66:T66)=0,"-",Dashboard!$I$6-MAX(G66:T66))</f>
+        <v>144</v>
       </c>
       <c r="X66" s="40" t="s">
-        <v>96</v>
+        <v>814</v>
       </c>
     </row>
     <row r="67" spans="1:24" ht="15" customHeight="1">
@@ -9393,12 +9496,14 @@
         <v>46110</v>
       </c>
       <c r="I67" s="34">
-        <v>46117</v>
+        <v>46107</v>
       </c>
       <c r="J67" s="34">
         <v>46117</v>
       </c>
-      <c r="K67" s="37"/>
+      <c r="K67" s="34">
+        <v>46117</v>
+      </c>
       <c r="L67" s="37"/>
       <c r="M67" s="33"/>
       <c r="N67" s="33"/>
@@ -9409,18 +9514,18 @@
       <c r="S67" s="37"/>
       <c r="T67" s="37"/>
       <c r="U67" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V67" s="39" t="str">
-        <f>IF(T67&lt;&gt;"","9 - Closed",IF(S67&lt;&gt;"","8 - Definitive Agreement",IF(Q67&lt;&gt;"","7 - Diligence",IF(P67&lt;&gt;"","6 - LOI Signed",IF(O67&lt;&gt;"","5 - Mgmt Meeting",IF(L67&lt;&gt;"","4 - IOI Received",IF(K67&lt;&gt;"","3 - CIM Sent",IF(J67&lt;&gt;"","2 - Teaser Sent",IF(I67&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>2 - Teaser Sent</v>
+        <f>IF(T67&lt;&gt;"","9 - Closed",IF(S67&lt;&gt;"","8 - Definitive Agreement",IF(Q67&lt;&gt;"","7 - Diligence",IF(P67&lt;&gt;"","6 - LOI Signed",IF(O67&lt;&gt;"","5 - Mgmt Meeting",IF(L67&lt;&gt;"","4 - IOI Received",IF(K67&lt;&gt;"","3 - CIM Sent",IF(J67&lt;&gt;"","2 - NDA Signed",IF(I67&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>3 - CIM Sent</v>
       </c>
       <c r="W67" s="39">
-        <f ca="1">IF(COUNT(G67:T67)=0,"-",TODAY()-MAX(G67:T67))</f>
-        <v>123</v>
+        <f>IF(COUNT(G67:T67)=0,"-",Dashboard!$I$6-MAX(G67:T67))</f>
+        <v>127</v>
       </c>
       <c r="X67" s="40" t="s">
-        <v>96</v>
+        <v>814</v>
       </c>
     </row>
     <row r="68" spans="1:24" ht="15" customHeight="1">
@@ -9449,12 +9554,14 @@
         <v>46108</v>
       </c>
       <c r="I68" s="34">
+        <v>46106</v>
+      </c>
+      <c r="J68" s="34">
         <v>46112</v>
       </c>
-      <c r="J68" s="34">
+      <c r="K68" s="34">
         <v>46114</v>
       </c>
-      <c r="K68" s="37"/>
       <c r="L68" s="37"/>
       <c r="M68" s="33"/>
       <c r="N68" s="33"/>
@@ -9465,18 +9572,18 @@
       <c r="S68" s="37"/>
       <c r="T68" s="37"/>
       <c r="U68" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V68" s="39" t="str">
-        <f>IF(T68&lt;&gt;"","9 - Closed",IF(S68&lt;&gt;"","8 - Definitive Agreement",IF(Q68&lt;&gt;"","7 - Diligence",IF(P68&lt;&gt;"","6 - LOI Signed",IF(O68&lt;&gt;"","5 - Mgmt Meeting",IF(L68&lt;&gt;"","4 - IOI Received",IF(K68&lt;&gt;"","3 - CIM Sent",IF(J68&lt;&gt;"","2 - Teaser Sent",IF(I68&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>2 - Teaser Sent</v>
+        <f>IF(T68&lt;&gt;"","9 - Closed",IF(S68&lt;&gt;"","8 - Definitive Agreement",IF(Q68&lt;&gt;"","7 - Diligence",IF(P68&lt;&gt;"","6 - LOI Signed",IF(O68&lt;&gt;"","5 - Mgmt Meeting",IF(L68&lt;&gt;"","4 - IOI Received",IF(K68&lt;&gt;"","3 - CIM Sent",IF(J68&lt;&gt;"","2 - NDA Signed",IF(I68&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>3 - CIM Sent</v>
       </c>
       <c r="W68" s="39">
-        <f ca="1">IF(COUNT(G68:T68)=0,"-",TODAY()-MAX(G68:T68))</f>
-        <v>126</v>
+        <f>IF(COUNT(G68:T68)=0,"-",Dashboard!$I$6-MAX(G68:T68))</f>
+        <v>130</v>
       </c>
       <c r="X68" s="40" t="s">
-        <v>96</v>
+        <v>814</v>
       </c>
     </row>
     <row r="69" spans="1:24" ht="15" customHeight="1">
@@ -9505,12 +9612,14 @@
         <v>46111</v>
       </c>
       <c r="I69" s="34">
-        <v>46116</v>
+        <v>46107</v>
       </c>
       <c r="J69" s="34">
         <v>46116</v>
       </c>
-      <c r="K69" s="37"/>
+      <c r="K69" s="34">
+        <v>46116</v>
+      </c>
       <c r="L69" s="37"/>
       <c r="M69" s="33"/>
       <c r="N69" s="33"/>
@@ -9521,18 +9630,18 @@
       <c r="S69" s="37"/>
       <c r="T69" s="37"/>
       <c r="U69" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V69" s="39" t="str">
-        <f>IF(T69&lt;&gt;"","9 - Closed",IF(S69&lt;&gt;"","8 - Definitive Agreement",IF(Q69&lt;&gt;"","7 - Diligence",IF(P69&lt;&gt;"","6 - LOI Signed",IF(O69&lt;&gt;"","5 - Mgmt Meeting",IF(L69&lt;&gt;"","4 - IOI Received",IF(K69&lt;&gt;"","3 - CIM Sent",IF(J69&lt;&gt;"","2 - Teaser Sent",IF(I69&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>2 - Teaser Sent</v>
+        <f>IF(T69&lt;&gt;"","9 - Closed",IF(S69&lt;&gt;"","8 - Definitive Agreement",IF(Q69&lt;&gt;"","7 - Diligence",IF(P69&lt;&gt;"","6 - LOI Signed",IF(O69&lt;&gt;"","5 - Mgmt Meeting",IF(L69&lt;&gt;"","4 - IOI Received",IF(K69&lt;&gt;"","3 - CIM Sent",IF(J69&lt;&gt;"","2 - NDA Signed",IF(I69&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>3 - CIM Sent</v>
       </c>
       <c r="W69" s="39">
-        <f ca="1">IF(COUNT(G69:T69)=0,"-",TODAY()-MAX(G69:T69))</f>
-        <v>124</v>
+        <f>IF(COUNT(G69:T69)=0,"-",Dashboard!$I$6-MAX(G69:T69))</f>
+        <v>128</v>
       </c>
       <c r="X69" s="40" t="s">
-        <v>96</v>
+        <v>814</v>
       </c>
     </row>
     <row r="70" spans="1:24" ht="15" customHeight="1">
@@ -9561,10 +9670,14 @@
         <v>46089</v>
       </c>
       <c r="I70" s="34">
+        <v>46086</v>
+      </c>
+      <c r="J70" s="34">
         <v>46099</v>
       </c>
-      <c r="J70" s="37"/>
-      <c r="K70" s="37"/>
+      <c r="K70" s="34">
+        <v>46101</v>
+      </c>
       <c r="L70" s="37"/>
       <c r="M70" s="33"/>
       <c r="N70" s="33"/>
@@ -9575,18 +9688,18 @@
       <c r="S70" s="37"/>
       <c r="T70" s="37"/>
       <c r="U70" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V70" s="39" t="str">
-        <f>IF(T70&lt;&gt;"","9 - Closed",IF(S70&lt;&gt;"","8 - Definitive Agreement",IF(Q70&lt;&gt;"","7 - Diligence",IF(P70&lt;&gt;"","6 - LOI Signed",IF(O70&lt;&gt;"","5 - Mgmt Meeting",IF(L70&lt;&gt;"","4 - IOI Received",IF(K70&lt;&gt;"","3 - CIM Sent",IF(J70&lt;&gt;"","2 - Teaser Sent",IF(I70&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>1 - NDA Signed</v>
+        <f>IF(T70&lt;&gt;"","9 - Closed",IF(S70&lt;&gt;"","8 - Definitive Agreement",IF(Q70&lt;&gt;"","7 - Diligence",IF(P70&lt;&gt;"","6 - LOI Signed",IF(O70&lt;&gt;"","5 - Mgmt Meeting",IF(L70&lt;&gt;"","4 - IOI Received",IF(K70&lt;&gt;"","3 - CIM Sent",IF(J70&lt;&gt;"","2 - NDA Signed",IF(I70&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>3 - CIM Sent</v>
       </c>
       <c r="W70" s="39">
-        <f ca="1">IF(COUNT(G70:T70)=0,"-",TODAY()-MAX(G70:T70))</f>
-        <v>141</v>
+        <f>IF(COUNT(G70:T70)=0,"-",Dashboard!$I$6-MAX(G70:T70))</f>
+        <v>143</v>
       </c>
       <c r="X70" s="40" t="s">
-        <v>96</v>
+        <v>814</v>
       </c>
     </row>
     <row r="71" spans="1:24" ht="15" customHeight="1">
@@ -9615,10 +9728,14 @@
         <v>46097</v>
       </c>
       <c r="I71" s="34">
+        <v>46094</v>
+      </c>
+      <c r="J71" s="34">
         <v>46100</v>
       </c>
-      <c r="J71" s="37"/>
-      <c r="K71" s="37"/>
+      <c r="K71" s="34">
+        <v>46102</v>
+      </c>
       <c r="L71" s="37"/>
       <c r="M71" s="33"/>
       <c r="N71" s="33"/>
@@ -9629,18 +9746,18 @@
       <c r="S71" s="37"/>
       <c r="T71" s="37"/>
       <c r="U71" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V71" s="39" t="str">
-        <f>IF(T71&lt;&gt;"","9 - Closed",IF(S71&lt;&gt;"","8 - Definitive Agreement",IF(Q71&lt;&gt;"","7 - Diligence",IF(P71&lt;&gt;"","6 - LOI Signed",IF(O71&lt;&gt;"","5 - Mgmt Meeting",IF(L71&lt;&gt;"","4 - IOI Received",IF(K71&lt;&gt;"","3 - CIM Sent",IF(J71&lt;&gt;"","2 - Teaser Sent",IF(I71&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>1 - NDA Signed</v>
+        <f>IF(T71&lt;&gt;"","9 - Closed",IF(S71&lt;&gt;"","8 - Definitive Agreement",IF(Q71&lt;&gt;"","7 - Diligence",IF(P71&lt;&gt;"","6 - LOI Signed",IF(O71&lt;&gt;"","5 - Mgmt Meeting",IF(L71&lt;&gt;"","4 - IOI Received",IF(K71&lt;&gt;"","3 - CIM Sent",IF(J71&lt;&gt;"","2 - NDA Signed",IF(I71&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>3 - CIM Sent</v>
       </c>
       <c r="W71" s="39">
-        <f ca="1">IF(COUNT(G71:T71)=0,"-",TODAY()-MAX(G71:T71))</f>
-        <v>140</v>
+        <f>IF(COUNT(G71:T71)=0,"-",Dashboard!$I$6-MAX(G71:T71))</f>
+        <v>142</v>
       </c>
       <c r="X71" s="40" t="s">
-        <v>96</v>
+        <v>814</v>
       </c>
     </row>
     <row r="72" spans="1:24" ht="15" customHeight="1">
@@ -9669,10 +9786,14 @@
         <v>46103</v>
       </c>
       <c r="I72" s="34">
+        <v>46100</v>
+      </c>
+      <c r="J72" s="34">
         <v>46114</v>
       </c>
-      <c r="J72" s="37"/>
-      <c r="K72" s="37"/>
+      <c r="K72" s="34">
+        <v>46116</v>
+      </c>
       <c r="L72" s="37"/>
       <c r="M72" s="33"/>
       <c r="N72" s="33"/>
@@ -9683,18 +9804,18 @@
       <c r="S72" s="37"/>
       <c r="T72" s="37"/>
       <c r="U72" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V72" s="39" t="str">
-        <f>IF(T72&lt;&gt;"","9 - Closed",IF(S72&lt;&gt;"","8 - Definitive Agreement",IF(Q72&lt;&gt;"","7 - Diligence",IF(P72&lt;&gt;"","6 - LOI Signed",IF(O72&lt;&gt;"","5 - Mgmt Meeting",IF(L72&lt;&gt;"","4 - IOI Received",IF(K72&lt;&gt;"","3 - CIM Sent",IF(J72&lt;&gt;"","2 - Teaser Sent",IF(I72&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>1 - NDA Signed</v>
+        <f>IF(T72&lt;&gt;"","9 - Closed",IF(S72&lt;&gt;"","8 - Definitive Agreement",IF(Q72&lt;&gt;"","7 - Diligence",IF(P72&lt;&gt;"","6 - LOI Signed",IF(O72&lt;&gt;"","5 - Mgmt Meeting",IF(L72&lt;&gt;"","4 - IOI Received",IF(K72&lt;&gt;"","3 - CIM Sent",IF(J72&lt;&gt;"","2 - NDA Signed",IF(I72&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>3 - CIM Sent</v>
       </c>
       <c r="W72" s="39">
-        <f ca="1">IF(COUNT(G72:T72)=0,"-",TODAY()-MAX(G72:T72))</f>
-        <v>126</v>
+        <f>IF(COUNT(G72:T72)=0,"-",Dashboard!$I$6-MAX(G72:T72))</f>
+        <v>128</v>
       </c>
       <c r="X72" s="40" t="s">
-        <v>96</v>
+        <v>814</v>
       </c>
     </row>
     <row r="73" spans="1:24" ht="15" customHeight="1">
@@ -9723,10 +9844,14 @@
         <v>46086</v>
       </c>
       <c r="I73" s="34">
+        <v>46084</v>
+      </c>
+      <c r="J73" s="34">
         <v>46094</v>
       </c>
-      <c r="J73" s="37"/>
-      <c r="K73" s="37"/>
+      <c r="K73" s="34">
+        <v>46096</v>
+      </c>
       <c r="L73" s="37"/>
       <c r="M73" s="33"/>
       <c r="N73" s="33"/>
@@ -9737,18 +9862,18 @@
       <c r="S73" s="37"/>
       <c r="T73" s="37"/>
       <c r="U73" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V73" s="39" t="str">
-        <f>IF(T73&lt;&gt;"","9 - Closed",IF(S73&lt;&gt;"","8 - Definitive Agreement",IF(Q73&lt;&gt;"","7 - Diligence",IF(P73&lt;&gt;"","6 - LOI Signed",IF(O73&lt;&gt;"","5 - Mgmt Meeting",IF(L73&lt;&gt;"","4 - IOI Received",IF(K73&lt;&gt;"","3 - CIM Sent",IF(J73&lt;&gt;"","2 - Teaser Sent",IF(I73&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>1 - NDA Signed</v>
+        <f>IF(T73&lt;&gt;"","9 - Closed",IF(S73&lt;&gt;"","8 - Definitive Agreement",IF(Q73&lt;&gt;"","7 - Diligence",IF(P73&lt;&gt;"","6 - LOI Signed",IF(O73&lt;&gt;"","5 - Mgmt Meeting",IF(L73&lt;&gt;"","4 - IOI Received",IF(K73&lt;&gt;"","3 - CIM Sent",IF(J73&lt;&gt;"","2 - NDA Signed",IF(I73&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>3 - CIM Sent</v>
       </c>
       <c r="W73" s="39">
-        <f ca="1">IF(COUNT(G73:T73)=0,"-",TODAY()-MAX(G73:T73))</f>
-        <v>146</v>
+        <f>IF(COUNT(G73:T73)=0,"-",Dashboard!$I$6-MAX(G73:T73))</f>
+        <v>148</v>
       </c>
       <c r="X73" s="40" t="s">
-        <v>96</v>
+        <v>814</v>
       </c>
     </row>
     <row r="74" spans="1:24" ht="15" customHeight="1">
@@ -9776,7 +9901,9 @@
       <c r="H74" s="34">
         <v>46088</v>
       </c>
-      <c r="I74" s="37"/>
+      <c r="I74" s="34">
+        <v>46087</v>
+      </c>
       <c r="J74" s="37"/>
       <c r="K74" s="37"/>
       <c r="L74" s="37"/>
@@ -9789,18 +9916,18 @@
       <c r="S74" s="37"/>
       <c r="T74" s="37"/>
       <c r="U74" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V74" s="39" t="str">
-        <f>IF(T74&lt;&gt;"","9 - Closed",IF(S74&lt;&gt;"","8 - Definitive Agreement",IF(Q74&lt;&gt;"","7 - Diligence",IF(P74&lt;&gt;"","6 - LOI Signed",IF(O74&lt;&gt;"","5 - Mgmt Meeting",IF(L74&lt;&gt;"","4 - IOI Received",IF(K74&lt;&gt;"","3 - CIM Sent",IF(J74&lt;&gt;"","2 - Teaser Sent",IF(I74&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T74&lt;&gt;"","9 - Closed",IF(S74&lt;&gt;"","8 - Definitive Agreement",IF(Q74&lt;&gt;"","7 - Diligence",IF(P74&lt;&gt;"","6 - LOI Signed",IF(O74&lt;&gt;"","5 - Mgmt Meeting",IF(L74&lt;&gt;"","4 - IOI Received",IF(K74&lt;&gt;"","3 - CIM Sent",IF(J74&lt;&gt;"","2 - NDA Signed",IF(I74&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W74" s="39">
-        <f ca="1">IF(COUNT(G74:T74)=0,"-",TODAY()-MAX(G74:T74))</f>
-        <v>152</v>
+        <f>IF(COUNT(G74:T74)=0,"-",Dashboard!$I$6-MAX(G74:T74))</f>
+        <v>156</v>
       </c>
       <c r="X74" s="40" t="s">
-        <v>96</v>
+        <v>816</v>
       </c>
     </row>
     <row r="75" spans="1:24" ht="15" customHeight="1">
@@ -9828,7 +9955,9 @@
       <c r="H75" s="34">
         <v>46089</v>
       </c>
-      <c r="I75" s="37"/>
+      <c r="I75" s="34">
+        <v>46086</v>
+      </c>
       <c r="J75" s="37"/>
       <c r="K75" s="37"/>
       <c r="L75" s="37"/>
@@ -9844,15 +9973,15 @@
         <v>190</v>
       </c>
       <c r="V75" s="39" t="str">
-        <f>IF(T75&lt;&gt;"","9 - Closed",IF(S75&lt;&gt;"","8 - Definitive Agreement",IF(Q75&lt;&gt;"","7 - Diligence",IF(P75&lt;&gt;"","6 - LOI Signed",IF(O75&lt;&gt;"","5 - Mgmt Meeting",IF(L75&lt;&gt;"","4 - IOI Received",IF(K75&lt;&gt;"","3 - CIM Sent",IF(J75&lt;&gt;"","2 - Teaser Sent",IF(I75&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T75&lt;&gt;"","9 - Closed",IF(S75&lt;&gt;"","8 - Definitive Agreement",IF(Q75&lt;&gt;"","7 - Diligence",IF(P75&lt;&gt;"","6 - LOI Signed",IF(O75&lt;&gt;"","5 - Mgmt Meeting",IF(L75&lt;&gt;"","4 - IOI Received",IF(K75&lt;&gt;"","3 - CIM Sent",IF(J75&lt;&gt;"","2 - NDA Signed",IF(I75&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W75" s="39">
-        <f ca="1">IF(COUNT(G75:T75)=0,"-",TODAY()-MAX(G75:T75))</f>
-        <v>151</v>
+        <f>IF(COUNT(G75:T75)=0,"-",Dashboard!$I$6-MAX(G75:T75))</f>
+        <v>155</v>
       </c>
       <c r="X75" s="40" t="s">
-        <v>191</v>
+        <v>817</v>
       </c>
     </row>
     <row r="76" spans="1:24" ht="15" customHeight="1">
@@ -9880,7 +10009,9 @@
       <c r="H76" s="34">
         <v>46101</v>
       </c>
-      <c r="I76" s="37"/>
+      <c r="I76" s="34">
+        <v>46098</v>
+      </c>
       <c r="J76" s="37"/>
       <c r="K76" s="37"/>
       <c r="L76" s="37"/>
@@ -9893,18 +10024,18 @@
       <c r="S76" s="37"/>
       <c r="T76" s="37"/>
       <c r="U76" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V76" s="39" t="str">
-        <f>IF(T76&lt;&gt;"","9 - Closed",IF(S76&lt;&gt;"","8 - Definitive Agreement",IF(Q76&lt;&gt;"","7 - Diligence",IF(P76&lt;&gt;"","6 - LOI Signed",IF(O76&lt;&gt;"","5 - Mgmt Meeting",IF(L76&lt;&gt;"","4 - IOI Received",IF(K76&lt;&gt;"","3 - CIM Sent",IF(J76&lt;&gt;"","2 - Teaser Sent",IF(I76&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T76&lt;&gt;"","9 - Closed",IF(S76&lt;&gt;"","8 - Definitive Agreement",IF(Q76&lt;&gt;"","7 - Diligence",IF(P76&lt;&gt;"","6 - LOI Signed",IF(O76&lt;&gt;"","5 - Mgmt Meeting",IF(L76&lt;&gt;"","4 - IOI Received",IF(K76&lt;&gt;"","3 - CIM Sent",IF(J76&lt;&gt;"","2 - NDA Signed",IF(I76&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W76" s="39">
-        <f ca="1">IF(COUNT(G76:T76)=0,"-",TODAY()-MAX(G76:T76))</f>
-        <v>139</v>
+        <f>IF(COUNT(G76:T76)=0,"-",Dashboard!$I$6-MAX(G76:T76))</f>
+        <v>143</v>
       </c>
       <c r="X76" s="40" t="s">
-        <v>96</v>
+        <v>816</v>
       </c>
     </row>
     <row r="77" spans="1:24" ht="15" customHeight="1">
@@ -9932,7 +10063,9 @@
       <c r="H77" s="34">
         <v>46087</v>
       </c>
-      <c r="I77" s="37"/>
+      <c r="I77" s="34">
+        <v>46084</v>
+      </c>
       <c r="J77" s="37"/>
       <c r="K77" s="37"/>
       <c r="L77" s="37"/>
@@ -9945,18 +10078,18 @@
       <c r="S77" s="37"/>
       <c r="T77" s="37"/>
       <c r="U77" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V77" s="39" t="str">
-        <f>IF(T77&lt;&gt;"","9 - Closed",IF(S77&lt;&gt;"","8 - Definitive Agreement",IF(Q77&lt;&gt;"","7 - Diligence",IF(P77&lt;&gt;"","6 - LOI Signed",IF(O77&lt;&gt;"","5 - Mgmt Meeting",IF(L77&lt;&gt;"","4 - IOI Received",IF(K77&lt;&gt;"","3 - CIM Sent",IF(J77&lt;&gt;"","2 - Teaser Sent",IF(I77&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T77&lt;&gt;"","9 - Closed",IF(S77&lt;&gt;"","8 - Definitive Agreement",IF(Q77&lt;&gt;"","7 - Diligence",IF(P77&lt;&gt;"","6 - LOI Signed",IF(O77&lt;&gt;"","5 - Mgmt Meeting",IF(L77&lt;&gt;"","4 - IOI Received",IF(K77&lt;&gt;"","3 - CIM Sent",IF(J77&lt;&gt;"","2 - NDA Signed",IF(I77&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W77" s="39">
-        <f ca="1">IF(COUNT(G77:T77)=0,"-",TODAY()-MAX(G77:T77))</f>
-        <v>153</v>
+        <f>IF(COUNT(G77:T77)=0,"-",Dashboard!$I$6-MAX(G77:T77))</f>
+        <v>157</v>
       </c>
       <c r="X77" s="40" t="s">
-        <v>96</v>
+        <v>816</v>
       </c>
     </row>
     <row r="78" spans="1:24" ht="15" customHeight="1">
@@ -9984,7 +10117,9 @@
       <c r="H78" s="34">
         <v>46088</v>
       </c>
-      <c r="I78" s="37"/>
+      <c r="I78" s="34">
+        <v>46085</v>
+      </c>
       <c r="J78" s="37"/>
       <c r="K78" s="37"/>
       <c r="L78" s="37"/>
@@ -10000,15 +10135,15 @@
         <v>190</v>
       </c>
       <c r="V78" s="39" t="str">
-        <f>IF(T78&lt;&gt;"","9 - Closed",IF(S78&lt;&gt;"","8 - Definitive Agreement",IF(Q78&lt;&gt;"","7 - Diligence",IF(P78&lt;&gt;"","6 - LOI Signed",IF(O78&lt;&gt;"","5 - Mgmt Meeting",IF(L78&lt;&gt;"","4 - IOI Received",IF(K78&lt;&gt;"","3 - CIM Sent",IF(J78&lt;&gt;"","2 - Teaser Sent",IF(I78&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T78&lt;&gt;"","9 - Closed",IF(S78&lt;&gt;"","8 - Definitive Agreement",IF(Q78&lt;&gt;"","7 - Diligence",IF(P78&lt;&gt;"","6 - LOI Signed",IF(O78&lt;&gt;"","5 - Mgmt Meeting",IF(L78&lt;&gt;"","4 - IOI Received",IF(K78&lt;&gt;"","3 - CIM Sent",IF(J78&lt;&gt;"","2 - NDA Signed",IF(I78&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W78" s="39">
-        <f ca="1">IF(COUNT(G78:T78)=0,"-",TODAY()-MAX(G78:T78))</f>
-        <v>152</v>
+        <f>IF(COUNT(G78:T78)=0,"-",Dashboard!$I$6-MAX(G78:T78))</f>
+        <v>156</v>
       </c>
       <c r="X78" s="40" t="s">
-        <v>191</v>
+        <v>817</v>
       </c>
     </row>
     <row r="79" spans="1:24" ht="15" customHeight="1">
@@ -10036,7 +10171,9 @@
       <c r="H79" s="34">
         <v>46105</v>
       </c>
-      <c r="I79" s="37"/>
+      <c r="I79" s="34">
+        <v>46103</v>
+      </c>
       <c r="J79" s="37"/>
       <c r="K79" s="37"/>
       <c r="L79" s="37"/>
@@ -10049,18 +10186,18 @@
       <c r="S79" s="37"/>
       <c r="T79" s="37"/>
       <c r="U79" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V79" s="39" t="str">
-        <f>IF(T79&lt;&gt;"","9 - Closed",IF(S79&lt;&gt;"","8 - Definitive Agreement",IF(Q79&lt;&gt;"","7 - Diligence",IF(P79&lt;&gt;"","6 - LOI Signed",IF(O79&lt;&gt;"","5 - Mgmt Meeting",IF(L79&lt;&gt;"","4 - IOI Received",IF(K79&lt;&gt;"","3 - CIM Sent",IF(J79&lt;&gt;"","2 - Teaser Sent",IF(I79&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T79&lt;&gt;"","9 - Closed",IF(S79&lt;&gt;"","8 - Definitive Agreement",IF(Q79&lt;&gt;"","7 - Diligence",IF(P79&lt;&gt;"","6 - LOI Signed",IF(O79&lt;&gt;"","5 - Mgmt Meeting",IF(L79&lt;&gt;"","4 - IOI Received",IF(K79&lt;&gt;"","3 - CIM Sent",IF(J79&lt;&gt;"","2 - NDA Signed",IF(I79&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W79" s="39">
-        <f ca="1">IF(COUNT(G79:T79)=0,"-",TODAY()-MAX(G79:T79))</f>
-        <v>135</v>
+        <f>IF(COUNT(G79:T79)=0,"-",Dashboard!$I$6-MAX(G79:T79))</f>
+        <v>139</v>
       </c>
       <c r="X79" s="40" t="s">
-        <v>96</v>
+        <v>816</v>
       </c>
     </row>
     <row r="80" spans="1:24" ht="15" customHeight="1">
@@ -10088,7 +10225,9 @@
       <c r="H80" s="34">
         <v>46112</v>
       </c>
-      <c r="I80" s="37"/>
+      <c r="I80" s="34">
+        <v>46108</v>
+      </c>
       <c r="J80" s="37"/>
       <c r="K80" s="37"/>
       <c r="L80" s="37"/>
@@ -10104,15 +10243,15 @@
         <v>190</v>
       </c>
       <c r="V80" s="39" t="str">
-        <f>IF(T80&lt;&gt;"","9 - Closed",IF(S80&lt;&gt;"","8 - Definitive Agreement",IF(Q80&lt;&gt;"","7 - Diligence",IF(P80&lt;&gt;"","6 - LOI Signed",IF(O80&lt;&gt;"","5 - Mgmt Meeting",IF(L80&lt;&gt;"","4 - IOI Received",IF(K80&lt;&gt;"","3 - CIM Sent",IF(J80&lt;&gt;"","2 - Teaser Sent",IF(I80&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T80&lt;&gt;"","9 - Closed",IF(S80&lt;&gt;"","8 - Definitive Agreement",IF(Q80&lt;&gt;"","7 - Diligence",IF(P80&lt;&gt;"","6 - LOI Signed",IF(O80&lt;&gt;"","5 - Mgmt Meeting",IF(L80&lt;&gt;"","4 - IOI Received",IF(K80&lt;&gt;"","3 - CIM Sent",IF(J80&lt;&gt;"","2 - NDA Signed",IF(I80&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W80" s="39">
-        <f ca="1">IF(COUNT(G80:T80)=0,"-",TODAY()-MAX(G80:T80))</f>
-        <v>128</v>
+        <f>IF(COUNT(G80:T80)=0,"-",Dashboard!$I$6-MAX(G80:T80))</f>
+        <v>132</v>
       </c>
       <c r="X80" s="40" t="s">
-        <v>191</v>
+        <v>817</v>
       </c>
     </row>
     <row r="81" spans="1:24" ht="15" customHeight="1">
@@ -10140,7 +10279,9 @@
       <c r="H81" s="34">
         <v>46091</v>
       </c>
-      <c r="I81" s="37"/>
+      <c r="I81" s="34">
+        <v>46090</v>
+      </c>
       <c r="J81" s="37"/>
       <c r="K81" s="37"/>
       <c r="L81" s="37"/>
@@ -10156,15 +10297,15 @@
         <v>190</v>
       </c>
       <c r="V81" s="39" t="str">
-        <f>IF(T81&lt;&gt;"","9 - Closed",IF(S81&lt;&gt;"","8 - Definitive Agreement",IF(Q81&lt;&gt;"","7 - Diligence",IF(P81&lt;&gt;"","6 - LOI Signed",IF(O81&lt;&gt;"","5 - Mgmt Meeting",IF(L81&lt;&gt;"","4 - IOI Received",IF(K81&lt;&gt;"","3 - CIM Sent",IF(J81&lt;&gt;"","2 - Teaser Sent",IF(I81&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T81&lt;&gt;"","9 - Closed",IF(S81&lt;&gt;"","8 - Definitive Agreement",IF(Q81&lt;&gt;"","7 - Diligence",IF(P81&lt;&gt;"","6 - LOI Signed",IF(O81&lt;&gt;"","5 - Mgmt Meeting",IF(L81&lt;&gt;"","4 - IOI Received",IF(K81&lt;&gt;"","3 - CIM Sent",IF(J81&lt;&gt;"","2 - NDA Signed",IF(I81&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W81" s="39">
-        <f ca="1">IF(COUNT(G81:T81)=0,"-",TODAY()-MAX(G81:T81))</f>
-        <v>149</v>
+        <f>IF(COUNT(G81:T81)=0,"-",Dashboard!$I$6-MAX(G81:T81))</f>
+        <v>153</v>
       </c>
       <c r="X81" s="40" t="s">
-        <v>191</v>
+        <v>817</v>
       </c>
     </row>
     <row r="82" spans="1:24" ht="15" customHeight="1">
@@ -10190,7 +10331,9 @@
         <v>46102</v>
       </c>
       <c r="H82" s="37"/>
-      <c r="I82" s="37"/>
+      <c r="I82" s="34">
+        <v>46102</v>
+      </c>
       <c r="J82" s="37"/>
       <c r="K82" s="37"/>
       <c r="L82" s="37"/>
@@ -10206,15 +10349,15 @@
         <v>89</v>
       </c>
       <c r="V82" s="39" t="str">
-        <f>IF(T82&lt;&gt;"","9 - Closed",IF(S82&lt;&gt;"","8 - Definitive Agreement",IF(Q82&lt;&gt;"","7 - Diligence",IF(P82&lt;&gt;"","6 - LOI Signed",IF(O82&lt;&gt;"","5 - Mgmt Meeting",IF(L82&lt;&gt;"","4 - IOI Received",IF(K82&lt;&gt;"","3 - CIM Sent",IF(J82&lt;&gt;"","2 - Teaser Sent",IF(I82&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T82&lt;&gt;"","9 - Closed",IF(S82&lt;&gt;"","8 - Definitive Agreement",IF(Q82&lt;&gt;"","7 - Diligence",IF(P82&lt;&gt;"","6 - LOI Signed",IF(O82&lt;&gt;"","5 - Mgmt Meeting",IF(L82&lt;&gt;"","4 - IOI Received",IF(K82&lt;&gt;"","3 - CIM Sent",IF(J82&lt;&gt;"","2 - NDA Signed",IF(I82&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W82" s="39">
-        <f ca="1">IF(COUNT(G82:T82)=0,"-",TODAY()-MAX(G82:T82))</f>
-        <v>138</v>
+        <f>IF(COUNT(G82:T82)=0,"-",Dashboard!$I$6-MAX(G82:T82))</f>
+        <v>142</v>
       </c>
       <c r="X82" s="40" t="s">
-        <v>90</v>
+        <v>818</v>
       </c>
     </row>
     <row r="83" spans="1:24" ht="15" customHeight="1">
@@ -10240,7 +10383,9 @@
         <v>46107</v>
       </c>
       <c r="H83" s="37"/>
-      <c r="I83" s="37"/>
+      <c r="I83" s="34">
+        <v>46107</v>
+      </c>
       <c r="J83" s="37"/>
       <c r="K83" s="37"/>
       <c r="L83" s="37"/>
@@ -10253,18 +10398,18 @@
       <c r="S83" s="37"/>
       <c r="T83" s="37"/>
       <c r="U83" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V83" s="39" t="str">
-        <f>IF(T83&lt;&gt;"","9 - Closed",IF(S83&lt;&gt;"","8 - Definitive Agreement",IF(Q83&lt;&gt;"","7 - Diligence",IF(P83&lt;&gt;"","6 - LOI Signed",IF(O83&lt;&gt;"","5 - Mgmt Meeting",IF(L83&lt;&gt;"","4 - IOI Received",IF(K83&lt;&gt;"","3 - CIM Sent",IF(J83&lt;&gt;"","2 - Teaser Sent",IF(I83&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T83&lt;&gt;"","9 - Closed",IF(S83&lt;&gt;"","8 - Definitive Agreement",IF(Q83&lt;&gt;"","7 - Diligence",IF(P83&lt;&gt;"","6 - LOI Signed",IF(O83&lt;&gt;"","5 - Mgmt Meeting",IF(L83&lt;&gt;"","4 - IOI Received",IF(K83&lt;&gt;"","3 - CIM Sent",IF(J83&lt;&gt;"","2 - NDA Signed",IF(I83&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W83" s="39">
-        <f ca="1">IF(COUNT(G83:T83)=0,"-",TODAY()-MAX(G83:T83))</f>
-        <v>133</v>
+        <f>IF(COUNT(G83:T83)=0,"-",Dashboard!$I$6-MAX(G83:T83))</f>
+        <v>137</v>
       </c>
       <c r="X83" s="40" t="s">
-        <v>96</v>
+        <v>819</v>
       </c>
     </row>
     <row r="84" spans="1:24" ht="15" customHeight="1">
@@ -10290,7 +10435,9 @@
         <v>46097</v>
       </c>
       <c r="H84" s="37"/>
-      <c r="I84" s="37"/>
+      <c r="I84" s="34">
+        <v>46097</v>
+      </c>
       <c r="J84" s="37"/>
       <c r="K84" s="37"/>
       <c r="L84" s="37"/>
@@ -10303,18 +10450,18 @@
       <c r="S84" s="37"/>
       <c r="T84" s="37"/>
       <c r="U84" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V84" s="39" t="str">
-        <f>IF(T84&lt;&gt;"","9 - Closed",IF(S84&lt;&gt;"","8 - Definitive Agreement",IF(Q84&lt;&gt;"","7 - Diligence",IF(P84&lt;&gt;"","6 - LOI Signed",IF(O84&lt;&gt;"","5 - Mgmt Meeting",IF(L84&lt;&gt;"","4 - IOI Received",IF(K84&lt;&gt;"","3 - CIM Sent",IF(J84&lt;&gt;"","2 - Teaser Sent",IF(I84&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T84&lt;&gt;"","9 - Closed",IF(S84&lt;&gt;"","8 - Definitive Agreement",IF(Q84&lt;&gt;"","7 - Diligence",IF(P84&lt;&gt;"","6 - LOI Signed",IF(O84&lt;&gt;"","5 - Mgmt Meeting",IF(L84&lt;&gt;"","4 - IOI Received",IF(K84&lt;&gt;"","3 - CIM Sent",IF(J84&lt;&gt;"","2 - NDA Signed",IF(I84&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W84" s="39">
-        <f ca="1">IF(COUNT(G84:T84)=0,"-",TODAY()-MAX(G84:T84))</f>
-        <v>143</v>
+        <f>IF(COUNT(G84:T84)=0,"-",Dashboard!$I$6-MAX(G84:T84))</f>
+        <v>147</v>
       </c>
       <c r="X84" s="40" t="s">
-        <v>96</v>
+        <v>819</v>
       </c>
     </row>
     <row r="85" spans="1:24" ht="15" customHeight="1">
@@ -10340,7 +10487,9 @@
         <v>46096</v>
       </c>
       <c r="H85" s="37"/>
-      <c r="I85" s="37"/>
+      <c r="I85" s="34">
+        <v>46096</v>
+      </c>
       <c r="J85" s="37"/>
       <c r="K85" s="37"/>
       <c r="L85" s="37"/>
@@ -10353,18 +10502,18 @@
       <c r="S85" s="37"/>
       <c r="T85" s="37"/>
       <c r="U85" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V85" s="39" t="str">
-        <f>IF(T85&lt;&gt;"","9 - Closed",IF(S85&lt;&gt;"","8 - Definitive Agreement",IF(Q85&lt;&gt;"","7 - Diligence",IF(P85&lt;&gt;"","6 - LOI Signed",IF(O85&lt;&gt;"","5 - Mgmt Meeting",IF(L85&lt;&gt;"","4 - IOI Received",IF(K85&lt;&gt;"","3 - CIM Sent",IF(J85&lt;&gt;"","2 - Teaser Sent",IF(I85&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T85&lt;&gt;"","9 - Closed",IF(S85&lt;&gt;"","8 - Definitive Agreement",IF(Q85&lt;&gt;"","7 - Diligence",IF(P85&lt;&gt;"","6 - LOI Signed",IF(O85&lt;&gt;"","5 - Mgmt Meeting",IF(L85&lt;&gt;"","4 - IOI Received",IF(K85&lt;&gt;"","3 - CIM Sent",IF(J85&lt;&gt;"","2 - NDA Signed",IF(I85&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W85" s="39">
-        <f ca="1">IF(COUNT(G85:T85)=0,"-",TODAY()-MAX(G85:T85))</f>
-        <v>144</v>
+        <f>IF(COUNT(G85:T85)=0,"-",Dashboard!$I$6-MAX(G85:T85))</f>
+        <v>148</v>
       </c>
       <c r="X85" s="40" t="s">
-        <v>96</v>
+        <v>819</v>
       </c>
     </row>
     <row r="86" spans="1:24" ht="15" customHeight="1">
@@ -10390,7 +10539,9 @@
         <v>46102</v>
       </c>
       <c r="H86" s="37"/>
-      <c r="I86" s="37"/>
+      <c r="I86" s="34">
+        <v>46102</v>
+      </c>
       <c r="J86" s="37"/>
       <c r="K86" s="37"/>
       <c r="L86" s="37"/>
@@ -10403,18 +10554,18 @@
       <c r="S86" s="37"/>
       <c r="T86" s="37"/>
       <c r="U86" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V86" s="39" t="str">
-        <f>IF(T86&lt;&gt;"","9 - Closed",IF(S86&lt;&gt;"","8 - Definitive Agreement",IF(Q86&lt;&gt;"","7 - Diligence",IF(P86&lt;&gt;"","6 - LOI Signed",IF(O86&lt;&gt;"","5 - Mgmt Meeting",IF(L86&lt;&gt;"","4 - IOI Received",IF(K86&lt;&gt;"","3 - CIM Sent",IF(J86&lt;&gt;"","2 - Teaser Sent",IF(I86&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T86&lt;&gt;"","9 - Closed",IF(S86&lt;&gt;"","8 - Definitive Agreement",IF(Q86&lt;&gt;"","7 - Diligence",IF(P86&lt;&gt;"","6 - LOI Signed",IF(O86&lt;&gt;"","5 - Mgmt Meeting",IF(L86&lt;&gt;"","4 - IOI Received",IF(K86&lt;&gt;"","3 - CIM Sent",IF(J86&lt;&gt;"","2 - NDA Signed",IF(I86&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W86" s="39">
-        <f ca="1">IF(COUNT(G86:T86)=0,"-",TODAY()-MAX(G86:T86))</f>
-        <v>138</v>
+        <f>IF(COUNT(G86:T86)=0,"-",Dashboard!$I$6-MAX(G86:T86))</f>
+        <v>142</v>
       </c>
       <c r="X86" s="40" t="s">
-        <v>96</v>
+        <v>819</v>
       </c>
     </row>
     <row r="87" spans="1:24" ht="15" customHeight="1">
@@ -10440,7 +10591,9 @@
         <v>46089</v>
       </c>
       <c r="H87" s="37"/>
-      <c r="I87" s="37"/>
+      <c r="I87" s="34">
+        <v>46089</v>
+      </c>
       <c r="J87" s="37"/>
       <c r="K87" s="37"/>
       <c r="L87" s="37"/>
@@ -10453,18 +10606,18 @@
       <c r="S87" s="37"/>
       <c r="T87" s="37"/>
       <c r="U87" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V87" s="39" t="str">
-        <f>IF(T87&lt;&gt;"","9 - Closed",IF(S87&lt;&gt;"","8 - Definitive Agreement",IF(Q87&lt;&gt;"","7 - Diligence",IF(P87&lt;&gt;"","6 - LOI Signed",IF(O87&lt;&gt;"","5 - Mgmt Meeting",IF(L87&lt;&gt;"","4 - IOI Received",IF(K87&lt;&gt;"","3 - CIM Sent",IF(J87&lt;&gt;"","2 - Teaser Sent",IF(I87&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T87&lt;&gt;"","9 - Closed",IF(S87&lt;&gt;"","8 - Definitive Agreement",IF(Q87&lt;&gt;"","7 - Diligence",IF(P87&lt;&gt;"","6 - LOI Signed",IF(O87&lt;&gt;"","5 - Mgmt Meeting",IF(L87&lt;&gt;"","4 - IOI Received",IF(K87&lt;&gt;"","3 - CIM Sent",IF(J87&lt;&gt;"","2 - NDA Signed",IF(I87&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W87" s="39">
-        <f ca="1">IF(COUNT(G87:T87)=0,"-",TODAY()-MAX(G87:T87))</f>
-        <v>151</v>
+        <f>IF(COUNT(G87:T87)=0,"-",Dashboard!$I$6-MAX(G87:T87))</f>
+        <v>155</v>
       </c>
       <c r="X87" s="40" t="s">
-        <v>96</v>
+        <v>819</v>
       </c>
     </row>
     <row r="88" spans="1:24" ht="15" customHeight="1">
@@ -10490,7 +10643,9 @@
         <v>46085</v>
       </c>
       <c r="H88" s="37"/>
-      <c r="I88" s="37"/>
+      <c r="I88" s="34">
+        <v>46085</v>
+      </c>
       <c r="J88" s="37"/>
       <c r="K88" s="37"/>
       <c r="L88" s="37"/>
@@ -10506,15 +10661,15 @@
         <v>89</v>
       </c>
       <c r="V88" s="39" t="str">
-        <f>IF(T88&lt;&gt;"","9 - Closed",IF(S88&lt;&gt;"","8 - Definitive Agreement",IF(Q88&lt;&gt;"","7 - Diligence",IF(P88&lt;&gt;"","6 - LOI Signed",IF(O88&lt;&gt;"","5 - Mgmt Meeting",IF(L88&lt;&gt;"","4 - IOI Received",IF(K88&lt;&gt;"","3 - CIM Sent",IF(J88&lt;&gt;"","2 - Teaser Sent",IF(I88&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T88&lt;&gt;"","9 - Closed",IF(S88&lt;&gt;"","8 - Definitive Agreement",IF(Q88&lt;&gt;"","7 - Diligence",IF(P88&lt;&gt;"","6 - LOI Signed",IF(O88&lt;&gt;"","5 - Mgmt Meeting",IF(L88&lt;&gt;"","4 - IOI Received",IF(K88&lt;&gt;"","3 - CIM Sent",IF(J88&lt;&gt;"","2 - NDA Signed",IF(I88&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W88" s="39">
-        <f ca="1">IF(COUNT(G88:T88)=0,"-",TODAY()-MAX(G88:T88))</f>
-        <v>155</v>
+        <f>IF(COUNT(G88:T88)=0,"-",Dashboard!$I$6-MAX(G88:T88))</f>
+        <v>159</v>
       </c>
       <c r="X88" s="40" t="s">
-        <v>90</v>
+        <v>818</v>
       </c>
     </row>
     <row r="89" spans="1:24" ht="15" customHeight="1">
@@ -10540,7 +10695,9 @@
         <v>46085</v>
       </c>
       <c r="H89" s="37"/>
-      <c r="I89" s="37"/>
+      <c r="I89" s="34">
+        <v>46085</v>
+      </c>
       <c r="J89" s="37"/>
       <c r="K89" s="37"/>
       <c r="L89" s="37"/>
@@ -10556,15 +10713,15 @@
         <v>89</v>
       </c>
       <c r="V89" s="39" t="str">
-        <f>IF(T89&lt;&gt;"","9 - Closed",IF(S89&lt;&gt;"","8 - Definitive Agreement",IF(Q89&lt;&gt;"","7 - Diligence",IF(P89&lt;&gt;"","6 - LOI Signed",IF(O89&lt;&gt;"","5 - Mgmt Meeting",IF(L89&lt;&gt;"","4 - IOI Received",IF(K89&lt;&gt;"","3 - CIM Sent",IF(J89&lt;&gt;"","2 - Teaser Sent",IF(I89&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T89&lt;&gt;"","9 - Closed",IF(S89&lt;&gt;"","8 - Definitive Agreement",IF(Q89&lt;&gt;"","7 - Diligence",IF(P89&lt;&gt;"","6 - LOI Signed",IF(O89&lt;&gt;"","5 - Mgmt Meeting",IF(L89&lt;&gt;"","4 - IOI Received",IF(K89&lt;&gt;"","3 - CIM Sent",IF(J89&lt;&gt;"","2 - NDA Signed",IF(I89&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W89" s="39">
-        <f ca="1">IF(COUNT(G89:T89)=0,"-",TODAY()-MAX(G89:T89))</f>
-        <v>155</v>
+        <f>IF(COUNT(G89:T89)=0,"-",Dashboard!$I$6-MAX(G89:T89))</f>
+        <v>159</v>
       </c>
       <c r="X89" s="40" t="s">
-        <v>90</v>
+        <v>818</v>
       </c>
     </row>
     <row r="90" spans="1:24" ht="15" customHeight="1">
@@ -10590,7 +10747,9 @@
         <v>46105</v>
       </c>
       <c r="H90" s="37"/>
-      <c r="I90" s="37"/>
+      <c r="I90" s="34">
+        <v>46105</v>
+      </c>
       <c r="J90" s="37"/>
       <c r="K90" s="37"/>
       <c r="L90" s="37"/>
@@ -10606,15 +10765,15 @@
         <v>89</v>
       </c>
       <c r="V90" s="39" t="str">
-        <f>IF(T90&lt;&gt;"","9 - Closed",IF(S90&lt;&gt;"","8 - Definitive Agreement",IF(Q90&lt;&gt;"","7 - Diligence",IF(P90&lt;&gt;"","6 - LOI Signed",IF(O90&lt;&gt;"","5 - Mgmt Meeting",IF(L90&lt;&gt;"","4 - IOI Received",IF(K90&lt;&gt;"","3 - CIM Sent",IF(J90&lt;&gt;"","2 - Teaser Sent",IF(I90&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T90&lt;&gt;"","9 - Closed",IF(S90&lt;&gt;"","8 - Definitive Agreement",IF(Q90&lt;&gt;"","7 - Diligence",IF(P90&lt;&gt;"","6 - LOI Signed",IF(O90&lt;&gt;"","5 - Mgmt Meeting",IF(L90&lt;&gt;"","4 - IOI Received",IF(K90&lt;&gt;"","3 - CIM Sent",IF(J90&lt;&gt;"","2 - NDA Signed",IF(I90&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W90" s="39">
-        <f ca="1">IF(COUNT(G90:T90)=0,"-",TODAY()-MAX(G90:T90))</f>
-        <v>135</v>
+        <f>IF(COUNT(G90:T90)=0,"-",Dashboard!$I$6-MAX(G90:T90))</f>
+        <v>139</v>
       </c>
       <c r="X90" s="40" t="s">
-        <v>90</v>
+        <v>818</v>
       </c>
     </row>
     <row r="91" spans="1:24" ht="15" customHeight="1">
@@ -10640,7 +10799,9 @@
         <v>46090</v>
       </c>
       <c r="H91" s="37"/>
-      <c r="I91" s="37"/>
+      <c r="I91" s="34">
+        <v>46090</v>
+      </c>
       <c r="J91" s="37"/>
       <c r="K91" s="37"/>
       <c r="L91" s="37"/>
@@ -10653,18 +10814,18 @@
       <c r="S91" s="37"/>
       <c r="T91" s="37"/>
       <c r="U91" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V91" s="39" t="str">
-        <f>IF(T91&lt;&gt;"","9 - Closed",IF(S91&lt;&gt;"","8 - Definitive Agreement",IF(Q91&lt;&gt;"","7 - Diligence",IF(P91&lt;&gt;"","6 - LOI Signed",IF(O91&lt;&gt;"","5 - Mgmt Meeting",IF(L91&lt;&gt;"","4 - IOI Received",IF(K91&lt;&gt;"","3 - CIM Sent",IF(J91&lt;&gt;"","2 - Teaser Sent",IF(I91&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T91&lt;&gt;"","9 - Closed",IF(S91&lt;&gt;"","8 - Definitive Agreement",IF(Q91&lt;&gt;"","7 - Diligence",IF(P91&lt;&gt;"","6 - LOI Signed",IF(O91&lt;&gt;"","5 - Mgmt Meeting",IF(L91&lt;&gt;"","4 - IOI Received",IF(K91&lt;&gt;"","3 - CIM Sent",IF(J91&lt;&gt;"","2 - NDA Signed",IF(I91&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W91" s="39">
-        <f ca="1">IF(COUNT(G91:T91)=0,"-",TODAY()-MAX(G91:T91))</f>
-        <v>150</v>
+        <f>IF(COUNT(G91:T91)=0,"-",Dashboard!$I$6-MAX(G91:T91))</f>
+        <v>154</v>
       </c>
       <c r="X91" s="40" t="s">
-        <v>96</v>
+        <v>819</v>
       </c>
     </row>
     <row r="92" spans="1:24" ht="15" customHeight="1">
@@ -10690,7 +10851,9 @@
         <v>46097</v>
       </c>
       <c r="H92" s="37"/>
-      <c r="I92" s="37"/>
+      <c r="I92" s="34">
+        <v>46097</v>
+      </c>
       <c r="J92" s="37"/>
       <c r="K92" s="37"/>
       <c r="L92" s="37"/>
@@ -10706,15 +10869,15 @@
         <v>89</v>
       </c>
       <c r="V92" s="39" t="str">
-        <f>IF(T92&lt;&gt;"","9 - Closed",IF(S92&lt;&gt;"","8 - Definitive Agreement",IF(Q92&lt;&gt;"","7 - Diligence",IF(P92&lt;&gt;"","6 - LOI Signed",IF(O92&lt;&gt;"","5 - Mgmt Meeting",IF(L92&lt;&gt;"","4 - IOI Received",IF(K92&lt;&gt;"","3 - CIM Sent",IF(J92&lt;&gt;"","2 - Teaser Sent",IF(I92&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T92&lt;&gt;"","9 - Closed",IF(S92&lt;&gt;"","8 - Definitive Agreement",IF(Q92&lt;&gt;"","7 - Diligence",IF(P92&lt;&gt;"","6 - LOI Signed",IF(O92&lt;&gt;"","5 - Mgmt Meeting",IF(L92&lt;&gt;"","4 - IOI Received",IF(K92&lt;&gt;"","3 - CIM Sent",IF(J92&lt;&gt;"","2 - NDA Signed",IF(I92&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W92" s="39">
-        <f ca="1">IF(COUNT(G92:T92)=0,"-",TODAY()-MAX(G92:T92))</f>
-        <v>143</v>
+        <f>IF(COUNT(G92:T92)=0,"-",Dashboard!$I$6-MAX(G92:T92))</f>
+        <v>147</v>
       </c>
       <c r="X92" s="40" t="s">
-        <v>90</v>
+        <v>818</v>
       </c>
     </row>
     <row r="93" spans="1:24" ht="15" customHeight="1">
@@ -10740,7 +10903,9 @@
         <v>46091</v>
       </c>
       <c r="H93" s="37"/>
-      <c r="I93" s="37"/>
+      <c r="I93" s="34">
+        <v>46091</v>
+      </c>
       <c r="J93" s="37"/>
       <c r="K93" s="37"/>
       <c r="L93" s="37"/>
@@ -10753,18 +10918,18 @@
       <c r="S93" s="37"/>
       <c r="T93" s="37"/>
       <c r="U93" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V93" s="39" t="str">
-        <f>IF(T93&lt;&gt;"","9 - Closed",IF(S93&lt;&gt;"","8 - Definitive Agreement",IF(Q93&lt;&gt;"","7 - Diligence",IF(P93&lt;&gt;"","6 - LOI Signed",IF(O93&lt;&gt;"","5 - Mgmt Meeting",IF(L93&lt;&gt;"","4 - IOI Received",IF(K93&lt;&gt;"","3 - CIM Sent",IF(J93&lt;&gt;"","2 - Teaser Sent",IF(I93&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T93&lt;&gt;"","9 - Closed",IF(S93&lt;&gt;"","8 - Definitive Agreement",IF(Q93&lt;&gt;"","7 - Diligence",IF(P93&lt;&gt;"","6 - LOI Signed",IF(O93&lt;&gt;"","5 - Mgmt Meeting",IF(L93&lt;&gt;"","4 - IOI Received",IF(K93&lt;&gt;"","3 - CIM Sent",IF(J93&lt;&gt;"","2 - NDA Signed",IF(I93&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W93" s="39">
-        <f ca="1">IF(COUNT(G93:T93)=0,"-",TODAY()-MAX(G93:T93))</f>
-        <v>149</v>
+        <f>IF(COUNT(G93:T93)=0,"-",Dashboard!$I$6-MAX(G93:T93))</f>
+        <v>153</v>
       </c>
       <c r="X93" s="40" t="s">
-        <v>96</v>
+        <v>819</v>
       </c>
     </row>
     <row r="94" spans="1:24" ht="15" customHeight="1">
@@ -10790,7 +10955,9 @@
         <v>46104</v>
       </c>
       <c r="H94" s="37"/>
-      <c r="I94" s="37"/>
+      <c r="I94" s="34">
+        <v>46104</v>
+      </c>
       <c r="J94" s="37"/>
       <c r="K94" s="37"/>
       <c r="L94" s="37"/>
@@ -10803,18 +10970,18 @@
       <c r="S94" s="37"/>
       <c r="T94" s="37"/>
       <c r="U94" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V94" s="39" t="str">
-        <f>IF(T94&lt;&gt;"","9 - Closed",IF(S94&lt;&gt;"","8 - Definitive Agreement",IF(Q94&lt;&gt;"","7 - Diligence",IF(P94&lt;&gt;"","6 - LOI Signed",IF(O94&lt;&gt;"","5 - Mgmt Meeting",IF(L94&lt;&gt;"","4 - IOI Received",IF(K94&lt;&gt;"","3 - CIM Sent",IF(J94&lt;&gt;"","2 - Teaser Sent",IF(I94&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T94&lt;&gt;"","9 - Closed",IF(S94&lt;&gt;"","8 - Definitive Agreement",IF(Q94&lt;&gt;"","7 - Diligence",IF(P94&lt;&gt;"","6 - LOI Signed",IF(O94&lt;&gt;"","5 - Mgmt Meeting",IF(L94&lt;&gt;"","4 - IOI Received",IF(K94&lt;&gt;"","3 - CIM Sent",IF(J94&lt;&gt;"","2 - NDA Signed",IF(I94&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W94" s="39">
-        <f ca="1">IF(COUNT(G94:T94)=0,"-",TODAY()-MAX(G94:T94))</f>
-        <v>136</v>
+        <f>IF(COUNT(G94:T94)=0,"-",Dashboard!$I$6-MAX(G94:T94))</f>
+        <v>140</v>
       </c>
       <c r="X94" s="40" t="s">
-        <v>96</v>
+        <v>819</v>
       </c>
     </row>
     <row r="95" spans="1:24" ht="15" customHeight="1">
@@ -10840,7 +11007,9 @@
         <v>46100</v>
       </c>
       <c r="H95" s="37"/>
-      <c r="I95" s="37"/>
+      <c r="I95" s="34">
+        <v>46100</v>
+      </c>
       <c r="J95" s="37"/>
       <c r="K95" s="37"/>
       <c r="L95" s="37"/>
@@ -10853,18 +11022,18 @@
       <c r="S95" s="37"/>
       <c r="T95" s="37"/>
       <c r="U95" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V95" s="39" t="str">
-        <f>IF(T95&lt;&gt;"","9 - Closed",IF(S95&lt;&gt;"","8 - Definitive Agreement",IF(Q95&lt;&gt;"","7 - Diligence",IF(P95&lt;&gt;"","6 - LOI Signed",IF(O95&lt;&gt;"","5 - Mgmt Meeting",IF(L95&lt;&gt;"","4 - IOI Received",IF(K95&lt;&gt;"","3 - CIM Sent",IF(J95&lt;&gt;"","2 - Teaser Sent",IF(I95&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T95&lt;&gt;"","9 - Closed",IF(S95&lt;&gt;"","8 - Definitive Agreement",IF(Q95&lt;&gt;"","7 - Diligence",IF(P95&lt;&gt;"","6 - LOI Signed",IF(O95&lt;&gt;"","5 - Mgmt Meeting",IF(L95&lt;&gt;"","4 - IOI Received",IF(K95&lt;&gt;"","3 - CIM Sent",IF(J95&lt;&gt;"","2 - NDA Signed",IF(I95&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W95" s="39">
-        <f ca="1">IF(COUNT(G95:T95)=0,"-",TODAY()-MAX(G95:T95))</f>
-        <v>140</v>
+        <f>IF(COUNT(G95:T95)=0,"-",Dashboard!$I$6-MAX(G95:T95))</f>
+        <v>144</v>
       </c>
       <c r="X95" s="40" t="s">
-        <v>96</v>
+        <v>819</v>
       </c>
     </row>
     <row r="96" spans="1:24" ht="15" customHeight="1">
@@ -10890,7 +11059,9 @@
         <v>46091</v>
       </c>
       <c r="H96" s="37"/>
-      <c r="I96" s="37"/>
+      <c r="I96" s="34">
+        <v>46091</v>
+      </c>
       <c r="J96" s="37"/>
       <c r="K96" s="37"/>
       <c r="L96" s="37"/>
@@ -10903,18 +11074,18 @@
       <c r="S96" s="37"/>
       <c r="T96" s="37"/>
       <c r="U96" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V96" s="39" t="str">
-        <f>IF(T96&lt;&gt;"","9 - Closed",IF(S96&lt;&gt;"","8 - Definitive Agreement",IF(Q96&lt;&gt;"","7 - Diligence",IF(P96&lt;&gt;"","6 - LOI Signed",IF(O96&lt;&gt;"","5 - Mgmt Meeting",IF(L96&lt;&gt;"","4 - IOI Received",IF(K96&lt;&gt;"","3 - CIM Sent",IF(J96&lt;&gt;"","2 - Teaser Sent",IF(I96&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T96&lt;&gt;"","9 - Closed",IF(S96&lt;&gt;"","8 - Definitive Agreement",IF(Q96&lt;&gt;"","7 - Diligence",IF(P96&lt;&gt;"","6 - LOI Signed",IF(O96&lt;&gt;"","5 - Mgmt Meeting",IF(L96&lt;&gt;"","4 - IOI Received",IF(K96&lt;&gt;"","3 - CIM Sent",IF(J96&lt;&gt;"","2 - NDA Signed",IF(I96&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W96" s="39">
-        <f ca="1">IF(COUNT(G96:T96)=0,"-",TODAY()-MAX(G96:T96))</f>
-        <v>149</v>
+        <f>IF(COUNT(G96:T96)=0,"-",Dashboard!$I$6-MAX(G96:T96))</f>
+        <v>153</v>
       </c>
       <c r="X96" s="40" t="s">
-        <v>96</v>
+        <v>819</v>
       </c>
     </row>
     <row r="97" spans="1:24" ht="15" customHeight="1">
@@ -10940,7 +11111,9 @@
         <v>46088</v>
       </c>
       <c r="H97" s="37"/>
-      <c r="I97" s="37"/>
+      <c r="I97" s="34">
+        <v>46088</v>
+      </c>
       <c r="J97" s="37"/>
       <c r="K97" s="37"/>
       <c r="L97" s="37"/>
@@ -10956,15 +11129,15 @@
         <v>89</v>
       </c>
       <c r="V97" s="39" t="str">
-        <f>IF(T97&lt;&gt;"","9 - Closed",IF(S97&lt;&gt;"","8 - Definitive Agreement",IF(Q97&lt;&gt;"","7 - Diligence",IF(P97&lt;&gt;"","6 - LOI Signed",IF(O97&lt;&gt;"","5 - Mgmt Meeting",IF(L97&lt;&gt;"","4 - IOI Received",IF(K97&lt;&gt;"","3 - CIM Sent",IF(J97&lt;&gt;"","2 - Teaser Sent",IF(I97&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T97&lt;&gt;"","9 - Closed",IF(S97&lt;&gt;"","8 - Definitive Agreement",IF(Q97&lt;&gt;"","7 - Diligence",IF(P97&lt;&gt;"","6 - LOI Signed",IF(O97&lt;&gt;"","5 - Mgmt Meeting",IF(L97&lt;&gt;"","4 - IOI Received",IF(K97&lt;&gt;"","3 - CIM Sent",IF(J97&lt;&gt;"","2 - NDA Signed",IF(I97&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W97" s="39">
-        <f ca="1">IF(COUNT(G97:T97)=0,"-",TODAY()-MAX(G97:T97))</f>
-        <v>152</v>
+        <f>IF(COUNT(G97:T97)=0,"-",Dashboard!$I$6-MAX(G97:T97))</f>
+        <v>156</v>
       </c>
       <c r="X97" s="40" t="s">
-        <v>90</v>
+        <v>818</v>
       </c>
     </row>
     <row r="98" spans="1:24" ht="15" customHeight="1">
@@ -10990,7 +11163,9 @@
         <v>46101</v>
       </c>
       <c r="H98" s="37"/>
-      <c r="I98" s="37"/>
+      <c r="I98" s="34">
+        <v>46101</v>
+      </c>
       <c r="J98" s="37"/>
       <c r="K98" s="37"/>
       <c r="L98" s="37"/>
@@ -11003,18 +11178,18 @@
       <c r="S98" s="37"/>
       <c r="T98" s="37"/>
       <c r="U98" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V98" s="39" t="str">
-        <f>IF(T98&lt;&gt;"","9 - Closed",IF(S98&lt;&gt;"","8 - Definitive Agreement",IF(Q98&lt;&gt;"","7 - Diligence",IF(P98&lt;&gt;"","6 - LOI Signed",IF(O98&lt;&gt;"","5 - Mgmt Meeting",IF(L98&lt;&gt;"","4 - IOI Received",IF(K98&lt;&gt;"","3 - CIM Sent",IF(J98&lt;&gt;"","2 - Teaser Sent",IF(I98&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T98&lt;&gt;"","9 - Closed",IF(S98&lt;&gt;"","8 - Definitive Agreement",IF(Q98&lt;&gt;"","7 - Diligence",IF(P98&lt;&gt;"","6 - LOI Signed",IF(O98&lt;&gt;"","5 - Mgmt Meeting",IF(L98&lt;&gt;"","4 - IOI Received",IF(K98&lt;&gt;"","3 - CIM Sent",IF(J98&lt;&gt;"","2 - NDA Signed",IF(I98&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W98" s="39">
-        <f ca="1">IF(COUNT(G98:T98)=0,"-",TODAY()-MAX(G98:T98))</f>
-        <v>139</v>
+        <f>IF(COUNT(G98:T98)=0,"-",Dashboard!$I$6-MAX(G98:T98))</f>
+        <v>143</v>
       </c>
       <c r="X98" s="40" t="s">
-        <v>96</v>
+        <v>819</v>
       </c>
     </row>
     <row r="99" spans="1:24" ht="15" customHeight="1">
@@ -11040,7 +11215,9 @@
         <v>46097</v>
       </c>
       <c r="H99" s="37"/>
-      <c r="I99" s="37"/>
+      <c r="I99" s="34">
+        <v>46097</v>
+      </c>
       <c r="J99" s="37"/>
       <c r="K99" s="37"/>
       <c r="L99" s="37"/>
@@ -11053,18 +11230,18 @@
       <c r="S99" s="37"/>
       <c r="T99" s="37"/>
       <c r="U99" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V99" s="39" t="str">
-        <f>IF(T99&lt;&gt;"","9 - Closed",IF(S99&lt;&gt;"","8 - Definitive Agreement",IF(Q99&lt;&gt;"","7 - Diligence",IF(P99&lt;&gt;"","6 - LOI Signed",IF(O99&lt;&gt;"","5 - Mgmt Meeting",IF(L99&lt;&gt;"","4 - IOI Received",IF(K99&lt;&gt;"","3 - CIM Sent",IF(J99&lt;&gt;"","2 - Teaser Sent",IF(I99&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T99&lt;&gt;"","9 - Closed",IF(S99&lt;&gt;"","8 - Definitive Agreement",IF(Q99&lt;&gt;"","7 - Diligence",IF(P99&lt;&gt;"","6 - LOI Signed",IF(O99&lt;&gt;"","5 - Mgmt Meeting",IF(L99&lt;&gt;"","4 - IOI Received",IF(K99&lt;&gt;"","3 - CIM Sent",IF(J99&lt;&gt;"","2 - NDA Signed",IF(I99&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W99" s="39">
-        <f ca="1">IF(COUNT(G99:T99)=0,"-",TODAY()-MAX(G99:T99))</f>
-        <v>143</v>
+        <f>IF(COUNT(G99:T99)=0,"-",Dashboard!$I$6-MAX(G99:T99))</f>
+        <v>147</v>
       </c>
       <c r="X99" s="40" t="s">
-        <v>96</v>
+        <v>819</v>
       </c>
     </row>
     <row r="100" spans="1:24" ht="15" customHeight="1">
@@ -11090,7 +11267,9 @@
         <v>46091</v>
       </c>
       <c r="H100" s="37"/>
-      <c r="I100" s="37"/>
+      <c r="I100" s="34">
+        <v>46091</v>
+      </c>
       <c r="J100" s="37"/>
       <c r="K100" s="37"/>
       <c r="L100" s="37"/>
@@ -11106,15 +11285,15 @@
         <v>89</v>
       </c>
       <c r="V100" s="39" t="str">
-        <f>IF(T100&lt;&gt;"","9 - Closed",IF(S100&lt;&gt;"","8 - Definitive Agreement",IF(Q100&lt;&gt;"","7 - Diligence",IF(P100&lt;&gt;"","6 - LOI Signed",IF(O100&lt;&gt;"","5 - Mgmt Meeting",IF(L100&lt;&gt;"","4 - IOI Received",IF(K100&lt;&gt;"","3 - CIM Sent",IF(J100&lt;&gt;"","2 - Teaser Sent",IF(I100&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T100&lt;&gt;"","9 - Closed",IF(S100&lt;&gt;"","8 - Definitive Agreement",IF(Q100&lt;&gt;"","7 - Diligence",IF(P100&lt;&gt;"","6 - LOI Signed",IF(O100&lt;&gt;"","5 - Mgmt Meeting",IF(L100&lt;&gt;"","4 - IOI Received",IF(K100&lt;&gt;"","3 - CIM Sent",IF(J100&lt;&gt;"","2 - NDA Signed",IF(I100&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W100" s="39">
-        <f ca="1">IF(COUNT(G100:T100)=0,"-",TODAY()-MAX(G100:T100))</f>
-        <v>149</v>
+        <f>IF(COUNT(G100:T100)=0,"-",Dashboard!$I$6-MAX(G100:T100))</f>
+        <v>153</v>
       </c>
       <c r="X100" s="40" t="s">
-        <v>90</v>
+        <v>818</v>
       </c>
     </row>
     <row r="101" spans="1:24" ht="15" customHeight="1">
@@ -11140,7 +11319,9 @@
         <v>46085</v>
       </c>
       <c r="H101" s="37"/>
-      <c r="I101" s="37"/>
+      <c r="I101" s="34">
+        <v>46085</v>
+      </c>
       <c r="J101" s="37"/>
       <c r="K101" s="37"/>
       <c r="L101" s="37"/>
@@ -11153,18 +11334,18 @@
       <c r="S101" s="37"/>
       <c r="T101" s="37"/>
       <c r="U101" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V101" s="39" t="str">
-        <f>IF(T101&lt;&gt;"","9 - Closed",IF(S101&lt;&gt;"","8 - Definitive Agreement",IF(Q101&lt;&gt;"","7 - Diligence",IF(P101&lt;&gt;"","6 - LOI Signed",IF(O101&lt;&gt;"","5 - Mgmt Meeting",IF(L101&lt;&gt;"","4 - IOI Received",IF(K101&lt;&gt;"","3 - CIM Sent",IF(J101&lt;&gt;"","2 - Teaser Sent",IF(I101&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T101&lt;&gt;"","9 - Closed",IF(S101&lt;&gt;"","8 - Definitive Agreement",IF(Q101&lt;&gt;"","7 - Diligence",IF(P101&lt;&gt;"","6 - LOI Signed",IF(O101&lt;&gt;"","5 - Mgmt Meeting",IF(L101&lt;&gt;"","4 - IOI Received",IF(K101&lt;&gt;"","3 - CIM Sent",IF(J101&lt;&gt;"","2 - NDA Signed",IF(I101&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W101" s="39">
-        <f ca="1">IF(COUNT(G101:T101)=0,"-",TODAY()-MAX(G101:T101))</f>
-        <v>155</v>
+        <f>IF(COUNT(G101:T101)=0,"-",Dashboard!$I$6-MAX(G101:T101))</f>
+        <v>159</v>
       </c>
       <c r="X101" s="40" t="s">
-        <v>96</v>
+        <v>819</v>
       </c>
     </row>
     <row r="102" spans="1:24" ht="15" customHeight="1">
@@ -11190,7 +11371,9 @@
         <v>46106</v>
       </c>
       <c r="H102" s="37"/>
-      <c r="I102" s="37"/>
+      <c r="I102" s="34">
+        <v>46106</v>
+      </c>
       <c r="J102" s="37"/>
       <c r="K102" s="37"/>
       <c r="L102" s="37"/>
@@ -11203,18 +11386,18 @@
       <c r="S102" s="37"/>
       <c r="T102" s="37"/>
       <c r="U102" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V102" s="39" t="str">
-        <f>IF(T102&lt;&gt;"","9 - Closed",IF(S102&lt;&gt;"","8 - Definitive Agreement",IF(Q102&lt;&gt;"","7 - Diligence",IF(P102&lt;&gt;"","6 - LOI Signed",IF(O102&lt;&gt;"","5 - Mgmt Meeting",IF(L102&lt;&gt;"","4 - IOI Received",IF(K102&lt;&gt;"","3 - CIM Sent",IF(J102&lt;&gt;"","2 - Teaser Sent",IF(I102&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T102&lt;&gt;"","9 - Closed",IF(S102&lt;&gt;"","8 - Definitive Agreement",IF(Q102&lt;&gt;"","7 - Diligence",IF(P102&lt;&gt;"","6 - LOI Signed",IF(O102&lt;&gt;"","5 - Mgmt Meeting",IF(L102&lt;&gt;"","4 - IOI Received",IF(K102&lt;&gt;"","3 - CIM Sent",IF(J102&lt;&gt;"","2 - NDA Signed",IF(I102&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W102" s="39">
-        <f ca="1">IF(COUNT(G102:T102)=0,"-",TODAY()-MAX(G102:T102))</f>
-        <v>134</v>
+        <f>IF(COUNT(G102:T102)=0,"-",Dashboard!$I$6-MAX(G102:T102))</f>
+        <v>138</v>
       </c>
       <c r="X102" s="40" t="s">
-        <v>96</v>
+        <v>819</v>
       </c>
     </row>
     <row r="103" spans="1:24" ht="15" customHeight="1">
@@ -11240,7 +11423,9 @@
         <v>46085</v>
       </c>
       <c r="H103" s="37"/>
-      <c r="I103" s="37"/>
+      <c r="I103" s="34">
+        <v>46085</v>
+      </c>
       <c r="J103" s="37"/>
       <c r="K103" s="37"/>
       <c r="L103" s="37"/>
@@ -11256,15 +11441,15 @@
         <v>89</v>
       </c>
       <c r="V103" s="39" t="str">
-        <f>IF(T103&lt;&gt;"","9 - Closed",IF(S103&lt;&gt;"","8 - Definitive Agreement",IF(Q103&lt;&gt;"","7 - Diligence",IF(P103&lt;&gt;"","6 - LOI Signed",IF(O103&lt;&gt;"","5 - Mgmt Meeting",IF(L103&lt;&gt;"","4 - IOI Received",IF(K103&lt;&gt;"","3 - CIM Sent",IF(J103&lt;&gt;"","2 - Teaser Sent",IF(I103&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T103&lt;&gt;"","9 - Closed",IF(S103&lt;&gt;"","8 - Definitive Agreement",IF(Q103&lt;&gt;"","7 - Diligence",IF(P103&lt;&gt;"","6 - LOI Signed",IF(O103&lt;&gt;"","5 - Mgmt Meeting",IF(L103&lt;&gt;"","4 - IOI Received",IF(K103&lt;&gt;"","3 - CIM Sent",IF(J103&lt;&gt;"","2 - NDA Signed",IF(I103&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W103" s="39">
-        <f ca="1">IF(COUNT(G103:T103)=0,"-",TODAY()-MAX(G103:T103))</f>
-        <v>155</v>
+        <f>IF(COUNT(G103:T103)=0,"-",Dashboard!$I$6-MAX(G103:T103))</f>
+        <v>159</v>
       </c>
       <c r="X103" s="40" t="s">
-        <v>90</v>
+        <v>818</v>
       </c>
     </row>
     <row r="104" spans="1:24" ht="15" customHeight="1">
@@ -11290,7 +11475,9 @@
         <v>46101</v>
       </c>
       <c r="H104" s="37"/>
-      <c r="I104" s="37"/>
+      <c r="I104" s="34">
+        <v>46101</v>
+      </c>
       <c r="J104" s="37"/>
       <c r="K104" s="37"/>
       <c r="L104" s="37"/>
@@ -11306,15 +11493,15 @@
         <v>89</v>
       </c>
       <c r="V104" s="39" t="str">
-        <f>IF(T104&lt;&gt;"","9 - Closed",IF(S104&lt;&gt;"","8 - Definitive Agreement",IF(Q104&lt;&gt;"","7 - Diligence",IF(P104&lt;&gt;"","6 - LOI Signed",IF(O104&lt;&gt;"","5 - Mgmt Meeting",IF(L104&lt;&gt;"","4 - IOI Received",IF(K104&lt;&gt;"","3 - CIM Sent",IF(J104&lt;&gt;"","2 - Teaser Sent",IF(I104&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T104&lt;&gt;"","9 - Closed",IF(S104&lt;&gt;"","8 - Definitive Agreement",IF(Q104&lt;&gt;"","7 - Diligence",IF(P104&lt;&gt;"","6 - LOI Signed",IF(O104&lt;&gt;"","5 - Mgmt Meeting",IF(L104&lt;&gt;"","4 - IOI Received",IF(K104&lt;&gt;"","3 - CIM Sent",IF(J104&lt;&gt;"","2 - NDA Signed",IF(I104&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W104" s="39">
-        <f ca="1">IF(COUNT(G104:T104)=0,"-",TODAY()-MAX(G104:T104))</f>
-        <v>139</v>
+        <f>IF(COUNT(G104:T104)=0,"-",Dashboard!$I$6-MAX(G104:T104))</f>
+        <v>143</v>
       </c>
       <c r="X104" s="40" t="s">
-        <v>90</v>
+        <v>818</v>
       </c>
     </row>
     <row r="105" spans="1:24" ht="15" customHeight="1">
@@ -11340,7 +11527,9 @@
         <v>46104</v>
       </c>
       <c r="H105" s="37"/>
-      <c r="I105" s="37"/>
+      <c r="I105" s="34">
+        <v>46104</v>
+      </c>
       <c r="J105" s="37"/>
       <c r="K105" s="37"/>
       <c r="L105" s="37"/>
@@ -11356,15 +11545,15 @@
         <v>89</v>
       </c>
       <c r="V105" s="39" t="str">
-        <f>IF(T105&lt;&gt;"","9 - Closed",IF(S105&lt;&gt;"","8 - Definitive Agreement",IF(Q105&lt;&gt;"","7 - Diligence",IF(P105&lt;&gt;"","6 - LOI Signed",IF(O105&lt;&gt;"","5 - Mgmt Meeting",IF(L105&lt;&gt;"","4 - IOI Received",IF(K105&lt;&gt;"","3 - CIM Sent",IF(J105&lt;&gt;"","2 - Teaser Sent",IF(I105&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T105&lt;&gt;"","9 - Closed",IF(S105&lt;&gt;"","8 - Definitive Agreement",IF(Q105&lt;&gt;"","7 - Diligence",IF(P105&lt;&gt;"","6 - LOI Signed",IF(O105&lt;&gt;"","5 - Mgmt Meeting",IF(L105&lt;&gt;"","4 - IOI Received",IF(K105&lt;&gt;"","3 - CIM Sent",IF(J105&lt;&gt;"","2 - NDA Signed",IF(I105&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W105" s="39">
-        <f ca="1">IF(COUNT(G105:T105)=0,"-",TODAY()-MAX(G105:T105))</f>
-        <v>136</v>
+        <f>IF(COUNT(G105:T105)=0,"-",Dashboard!$I$6-MAX(G105:T105))</f>
+        <v>140</v>
       </c>
       <c r="X105" s="40" t="s">
-        <v>90</v>
+        <v>818</v>
       </c>
     </row>
     <row r="106" spans="1:24" ht="15" customHeight="1">
@@ -11390,7 +11579,9 @@
         <v>46107</v>
       </c>
       <c r="H106" s="37"/>
-      <c r="I106" s="37"/>
+      <c r="I106" s="34">
+        <v>46107</v>
+      </c>
       <c r="J106" s="37"/>
       <c r="K106" s="37"/>
       <c r="L106" s="37"/>
@@ -11403,18 +11594,18 @@
       <c r="S106" s="37"/>
       <c r="T106" s="37"/>
       <c r="U106" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V106" s="39" t="str">
-        <f>IF(T106&lt;&gt;"","9 - Closed",IF(S106&lt;&gt;"","8 - Definitive Agreement",IF(Q106&lt;&gt;"","7 - Diligence",IF(P106&lt;&gt;"","6 - LOI Signed",IF(O106&lt;&gt;"","5 - Mgmt Meeting",IF(L106&lt;&gt;"","4 - IOI Received",IF(K106&lt;&gt;"","3 - CIM Sent",IF(J106&lt;&gt;"","2 - Teaser Sent",IF(I106&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T106&lt;&gt;"","9 - Closed",IF(S106&lt;&gt;"","8 - Definitive Agreement",IF(Q106&lt;&gt;"","7 - Diligence",IF(P106&lt;&gt;"","6 - LOI Signed",IF(O106&lt;&gt;"","5 - Mgmt Meeting",IF(L106&lt;&gt;"","4 - IOI Received",IF(K106&lt;&gt;"","3 - CIM Sent",IF(J106&lt;&gt;"","2 - NDA Signed",IF(I106&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W106" s="39">
-        <f ca="1">IF(COUNT(G106:T106)=0,"-",TODAY()-MAX(G106:T106))</f>
-        <v>133</v>
+        <f>IF(COUNT(G106:T106)=0,"-",Dashboard!$I$6-MAX(G106:T106))</f>
+        <v>137</v>
       </c>
       <c r="X106" s="40" t="s">
-        <v>96</v>
+        <v>819</v>
       </c>
     </row>
     <row r="107" spans="1:24" ht="15" customHeight="1">
@@ -11440,7 +11631,9 @@
         <v>46103</v>
       </c>
       <c r="H107" s="37"/>
-      <c r="I107" s="37"/>
+      <c r="I107" s="34">
+        <v>46103</v>
+      </c>
       <c r="J107" s="37"/>
       <c r="K107" s="37"/>
       <c r="L107" s="37"/>
@@ -11453,18 +11646,18 @@
       <c r="S107" s="37"/>
       <c r="T107" s="37"/>
       <c r="U107" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V107" s="39" t="str">
-        <f>IF(T107&lt;&gt;"","9 - Closed",IF(S107&lt;&gt;"","8 - Definitive Agreement",IF(Q107&lt;&gt;"","7 - Diligence",IF(P107&lt;&gt;"","6 - LOI Signed",IF(O107&lt;&gt;"","5 - Mgmt Meeting",IF(L107&lt;&gt;"","4 - IOI Received",IF(K107&lt;&gt;"","3 - CIM Sent",IF(J107&lt;&gt;"","2 - Teaser Sent",IF(I107&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T107&lt;&gt;"","9 - Closed",IF(S107&lt;&gt;"","8 - Definitive Agreement",IF(Q107&lt;&gt;"","7 - Diligence",IF(P107&lt;&gt;"","6 - LOI Signed",IF(O107&lt;&gt;"","5 - Mgmt Meeting",IF(L107&lt;&gt;"","4 - IOI Received",IF(K107&lt;&gt;"","3 - CIM Sent",IF(J107&lt;&gt;"","2 - NDA Signed",IF(I107&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W107" s="39">
-        <f ca="1">IF(COUNT(G107:T107)=0,"-",TODAY()-MAX(G107:T107))</f>
-        <v>137</v>
+        <f>IF(COUNT(G107:T107)=0,"-",Dashboard!$I$6-MAX(G107:T107))</f>
+        <v>141</v>
       </c>
       <c r="X107" s="40" t="s">
-        <v>96</v>
+        <v>819</v>
       </c>
     </row>
     <row r="108" spans="1:24" ht="15" customHeight="1">
@@ -11490,7 +11683,9 @@
         <v>46101</v>
       </c>
       <c r="H108" s="37"/>
-      <c r="I108" s="37"/>
+      <c r="I108" s="34">
+        <v>46101</v>
+      </c>
       <c r="J108" s="37"/>
       <c r="K108" s="37"/>
       <c r="L108" s="37"/>
@@ -11506,15 +11701,15 @@
         <v>89</v>
       </c>
       <c r="V108" s="39" t="str">
-        <f>IF(T108&lt;&gt;"","9 - Closed",IF(S108&lt;&gt;"","8 - Definitive Agreement",IF(Q108&lt;&gt;"","7 - Diligence",IF(P108&lt;&gt;"","6 - LOI Signed",IF(O108&lt;&gt;"","5 - Mgmt Meeting",IF(L108&lt;&gt;"","4 - IOI Received",IF(K108&lt;&gt;"","3 - CIM Sent",IF(J108&lt;&gt;"","2 - Teaser Sent",IF(I108&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T108&lt;&gt;"","9 - Closed",IF(S108&lt;&gt;"","8 - Definitive Agreement",IF(Q108&lt;&gt;"","7 - Diligence",IF(P108&lt;&gt;"","6 - LOI Signed",IF(O108&lt;&gt;"","5 - Mgmt Meeting",IF(L108&lt;&gt;"","4 - IOI Received",IF(K108&lt;&gt;"","3 - CIM Sent",IF(J108&lt;&gt;"","2 - NDA Signed",IF(I108&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W108" s="39">
-        <f ca="1">IF(COUNT(G108:T108)=0,"-",TODAY()-MAX(G108:T108))</f>
-        <v>139</v>
+        <f>IF(COUNT(G108:T108)=0,"-",Dashboard!$I$6-MAX(G108:T108))</f>
+        <v>143</v>
       </c>
       <c r="X108" s="40" t="s">
-        <v>90</v>
+        <v>818</v>
       </c>
     </row>
     <row r="109" spans="1:24" ht="15" customHeight="1">
@@ -11540,7 +11735,9 @@
         <v>46085</v>
       </c>
       <c r="H109" s="37"/>
-      <c r="I109" s="37"/>
+      <c r="I109" s="34">
+        <v>46085</v>
+      </c>
       <c r="J109" s="37"/>
       <c r="K109" s="37"/>
       <c r="L109" s="37"/>
@@ -11553,18 +11750,18 @@
       <c r="S109" s="37"/>
       <c r="T109" s="37"/>
       <c r="U109" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V109" s="39" t="str">
-        <f>IF(T109&lt;&gt;"","9 - Closed",IF(S109&lt;&gt;"","8 - Definitive Agreement",IF(Q109&lt;&gt;"","7 - Diligence",IF(P109&lt;&gt;"","6 - LOI Signed",IF(O109&lt;&gt;"","5 - Mgmt Meeting",IF(L109&lt;&gt;"","4 - IOI Received",IF(K109&lt;&gt;"","3 - CIM Sent",IF(J109&lt;&gt;"","2 - Teaser Sent",IF(I109&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T109&lt;&gt;"","9 - Closed",IF(S109&lt;&gt;"","8 - Definitive Agreement",IF(Q109&lt;&gt;"","7 - Diligence",IF(P109&lt;&gt;"","6 - LOI Signed",IF(O109&lt;&gt;"","5 - Mgmt Meeting",IF(L109&lt;&gt;"","4 - IOI Received",IF(K109&lt;&gt;"","3 - CIM Sent",IF(J109&lt;&gt;"","2 - NDA Signed",IF(I109&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W109" s="39">
-        <f ca="1">IF(COUNT(G109:T109)=0,"-",TODAY()-MAX(G109:T109))</f>
-        <v>155</v>
+        <f>IF(COUNT(G109:T109)=0,"-",Dashboard!$I$6-MAX(G109:T109))</f>
+        <v>159</v>
       </c>
       <c r="X109" s="40" t="s">
-        <v>96</v>
+        <v>819</v>
       </c>
     </row>
     <row r="110" spans="1:24" ht="15" customHeight="1">
@@ -11590,7 +11787,9 @@
         <v>46093</v>
       </c>
       <c r="H110" s="37"/>
-      <c r="I110" s="37"/>
+      <c r="I110" s="34">
+        <v>46093</v>
+      </c>
       <c r="J110" s="37"/>
       <c r="K110" s="37"/>
       <c r="L110" s="37"/>
@@ -11603,18 +11802,18 @@
       <c r="S110" s="37"/>
       <c r="T110" s="37"/>
       <c r="U110" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V110" s="39" t="str">
-        <f>IF(T110&lt;&gt;"","9 - Closed",IF(S110&lt;&gt;"","8 - Definitive Agreement",IF(Q110&lt;&gt;"","7 - Diligence",IF(P110&lt;&gt;"","6 - LOI Signed",IF(O110&lt;&gt;"","5 - Mgmt Meeting",IF(L110&lt;&gt;"","4 - IOI Received",IF(K110&lt;&gt;"","3 - CIM Sent",IF(J110&lt;&gt;"","2 - Teaser Sent",IF(I110&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T110&lt;&gt;"","9 - Closed",IF(S110&lt;&gt;"","8 - Definitive Agreement",IF(Q110&lt;&gt;"","7 - Diligence",IF(P110&lt;&gt;"","6 - LOI Signed",IF(O110&lt;&gt;"","5 - Mgmt Meeting",IF(L110&lt;&gt;"","4 - IOI Received",IF(K110&lt;&gt;"","3 - CIM Sent",IF(J110&lt;&gt;"","2 - NDA Signed",IF(I110&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W110" s="39">
-        <f ca="1">IF(COUNT(G110:T110)=0,"-",TODAY()-MAX(G110:T110))</f>
-        <v>147</v>
+        <f>IF(COUNT(G110:T110)=0,"-",Dashboard!$I$6-MAX(G110:T110))</f>
+        <v>151</v>
       </c>
       <c r="X110" s="40" t="s">
-        <v>96</v>
+        <v>819</v>
       </c>
     </row>
     <row r="111" spans="1:24" ht="15" customHeight="1">
@@ -11640,7 +11839,9 @@
         <v>46093</v>
       </c>
       <c r="H111" s="37"/>
-      <c r="I111" s="37"/>
+      <c r="I111" s="34">
+        <v>46093</v>
+      </c>
       <c r="J111" s="37"/>
       <c r="K111" s="37"/>
       <c r="L111" s="37"/>
@@ -11656,15 +11857,15 @@
         <v>89</v>
       </c>
       <c r="V111" s="39" t="str">
-        <f>IF(T111&lt;&gt;"","9 - Closed",IF(S111&lt;&gt;"","8 - Definitive Agreement",IF(Q111&lt;&gt;"","7 - Diligence",IF(P111&lt;&gt;"","6 - LOI Signed",IF(O111&lt;&gt;"","5 - Mgmt Meeting",IF(L111&lt;&gt;"","4 - IOI Received",IF(K111&lt;&gt;"","3 - CIM Sent",IF(J111&lt;&gt;"","2 - Teaser Sent",IF(I111&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T111&lt;&gt;"","9 - Closed",IF(S111&lt;&gt;"","8 - Definitive Agreement",IF(Q111&lt;&gt;"","7 - Diligence",IF(P111&lt;&gt;"","6 - LOI Signed",IF(O111&lt;&gt;"","5 - Mgmt Meeting",IF(L111&lt;&gt;"","4 - IOI Received",IF(K111&lt;&gt;"","3 - CIM Sent",IF(J111&lt;&gt;"","2 - NDA Signed",IF(I111&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W111" s="39">
-        <f ca="1">IF(COUNT(G111:T111)=0,"-",TODAY()-MAX(G111:T111))</f>
-        <v>147</v>
+        <f>IF(COUNT(G111:T111)=0,"-",Dashboard!$I$6-MAX(G111:T111))</f>
+        <v>151</v>
       </c>
       <c r="X111" s="40" t="s">
-        <v>90</v>
+        <v>818</v>
       </c>
     </row>
     <row r="112" spans="1:24" ht="15" customHeight="1">
@@ -11690,7 +11891,9 @@
         <v>46104</v>
       </c>
       <c r="H112" s="37"/>
-      <c r="I112" s="37"/>
+      <c r="I112" s="34">
+        <v>46104</v>
+      </c>
       <c r="J112" s="37"/>
       <c r="K112" s="37"/>
       <c r="L112" s="37"/>
@@ -11706,15 +11909,15 @@
         <v>89</v>
       </c>
       <c r="V112" s="39" t="str">
-        <f>IF(T112&lt;&gt;"","9 - Closed",IF(S112&lt;&gt;"","8 - Definitive Agreement",IF(Q112&lt;&gt;"","7 - Diligence",IF(P112&lt;&gt;"","6 - LOI Signed",IF(O112&lt;&gt;"","5 - Mgmt Meeting",IF(L112&lt;&gt;"","4 - IOI Received",IF(K112&lt;&gt;"","3 - CIM Sent",IF(J112&lt;&gt;"","2 - Teaser Sent",IF(I112&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T112&lt;&gt;"","9 - Closed",IF(S112&lt;&gt;"","8 - Definitive Agreement",IF(Q112&lt;&gt;"","7 - Diligence",IF(P112&lt;&gt;"","6 - LOI Signed",IF(O112&lt;&gt;"","5 - Mgmt Meeting",IF(L112&lt;&gt;"","4 - IOI Received",IF(K112&lt;&gt;"","3 - CIM Sent",IF(J112&lt;&gt;"","2 - NDA Signed",IF(I112&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W112" s="39">
-        <f ca="1">IF(COUNT(G112:T112)=0,"-",TODAY()-MAX(G112:T112))</f>
-        <v>136</v>
+        <f>IF(COUNT(G112:T112)=0,"-",Dashboard!$I$6-MAX(G112:T112))</f>
+        <v>140</v>
       </c>
       <c r="X112" s="40" t="s">
-        <v>90</v>
+        <v>818</v>
       </c>
     </row>
     <row r="113" spans="1:24" ht="15" customHeight="1">
@@ -11740,7 +11943,9 @@
         <v>46084</v>
       </c>
       <c r="H113" s="37"/>
-      <c r="I113" s="37"/>
+      <c r="I113" s="34">
+        <v>46084</v>
+      </c>
       <c r="J113" s="37"/>
       <c r="K113" s="37"/>
       <c r="L113" s="37"/>
@@ -11756,15 +11961,15 @@
         <v>89</v>
       </c>
       <c r="V113" s="39" t="str">
-        <f>IF(T113&lt;&gt;"","9 - Closed",IF(S113&lt;&gt;"","8 - Definitive Agreement",IF(Q113&lt;&gt;"","7 - Diligence",IF(P113&lt;&gt;"","6 - LOI Signed",IF(O113&lt;&gt;"","5 - Mgmt Meeting",IF(L113&lt;&gt;"","4 - IOI Received",IF(K113&lt;&gt;"","3 - CIM Sent",IF(J113&lt;&gt;"","2 - Teaser Sent",IF(I113&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T113&lt;&gt;"","9 - Closed",IF(S113&lt;&gt;"","8 - Definitive Agreement",IF(Q113&lt;&gt;"","7 - Diligence",IF(P113&lt;&gt;"","6 - LOI Signed",IF(O113&lt;&gt;"","5 - Mgmt Meeting",IF(L113&lt;&gt;"","4 - IOI Received",IF(K113&lt;&gt;"","3 - CIM Sent",IF(J113&lt;&gt;"","2 - NDA Signed",IF(I113&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W113" s="39">
-        <f ca="1">IF(COUNT(G113:T113)=0,"-",TODAY()-MAX(G113:T113))</f>
-        <v>156</v>
+        <f>IF(COUNT(G113:T113)=0,"-",Dashboard!$I$6-MAX(G113:T113))</f>
+        <v>160</v>
       </c>
       <c r="X113" s="40" t="s">
-        <v>90</v>
+        <v>818</v>
       </c>
     </row>
     <row r="114" spans="1:24" ht="15" customHeight="1">
@@ -11790,7 +11995,9 @@
         <v>46093</v>
       </c>
       <c r="H114" s="37"/>
-      <c r="I114" s="37"/>
+      <c r="I114" s="34">
+        <v>46093</v>
+      </c>
       <c r="J114" s="37"/>
       <c r="K114" s="37"/>
       <c r="L114" s="37"/>
@@ -11803,18 +12010,18 @@
       <c r="S114" s="37"/>
       <c r="T114" s="37"/>
       <c r="U114" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V114" s="39" t="str">
-        <f>IF(T114&lt;&gt;"","9 - Closed",IF(S114&lt;&gt;"","8 - Definitive Agreement",IF(Q114&lt;&gt;"","7 - Diligence",IF(P114&lt;&gt;"","6 - LOI Signed",IF(O114&lt;&gt;"","5 - Mgmt Meeting",IF(L114&lt;&gt;"","4 - IOI Received",IF(K114&lt;&gt;"","3 - CIM Sent",IF(J114&lt;&gt;"","2 - Teaser Sent",IF(I114&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T114&lt;&gt;"","9 - Closed",IF(S114&lt;&gt;"","8 - Definitive Agreement",IF(Q114&lt;&gt;"","7 - Diligence",IF(P114&lt;&gt;"","6 - LOI Signed",IF(O114&lt;&gt;"","5 - Mgmt Meeting",IF(L114&lt;&gt;"","4 - IOI Received",IF(K114&lt;&gt;"","3 - CIM Sent",IF(J114&lt;&gt;"","2 - NDA Signed",IF(I114&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W114" s="39">
-        <f ca="1">IF(COUNT(G114:T114)=0,"-",TODAY()-MAX(G114:T114))</f>
-        <v>147</v>
+        <f>IF(COUNT(G114:T114)=0,"-",Dashboard!$I$6-MAX(G114:T114))</f>
+        <v>151</v>
       </c>
       <c r="X114" s="40" t="s">
-        <v>96</v>
+        <v>819</v>
       </c>
     </row>
     <row r="115" spans="1:24" ht="15" customHeight="1">
@@ -11840,7 +12047,9 @@
         <v>46099</v>
       </c>
       <c r="H115" s="37"/>
-      <c r="I115" s="37"/>
+      <c r="I115" s="34">
+        <v>46099</v>
+      </c>
       <c r="J115" s="37"/>
       <c r="K115" s="37"/>
       <c r="L115" s="37"/>
@@ -11853,18 +12062,18 @@
       <c r="S115" s="37"/>
       <c r="T115" s="37"/>
       <c r="U115" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V115" s="39" t="str">
-        <f>IF(T115&lt;&gt;"","9 - Closed",IF(S115&lt;&gt;"","8 - Definitive Agreement",IF(Q115&lt;&gt;"","7 - Diligence",IF(P115&lt;&gt;"","6 - LOI Signed",IF(O115&lt;&gt;"","5 - Mgmt Meeting",IF(L115&lt;&gt;"","4 - IOI Received",IF(K115&lt;&gt;"","3 - CIM Sent",IF(J115&lt;&gt;"","2 - Teaser Sent",IF(I115&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T115&lt;&gt;"","9 - Closed",IF(S115&lt;&gt;"","8 - Definitive Agreement",IF(Q115&lt;&gt;"","7 - Diligence",IF(P115&lt;&gt;"","6 - LOI Signed",IF(O115&lt;&gt;"","5 - Mgmt Meeting",IF(L115&lt;&gt;"","4 - IOI Received",IF(K115&lt;&gt;"","3 - CIM Sent",IF(J115&lt;&gt;"","2 - NDA Signed",IF(I115&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W115" s="39">
-        <f ca="1">IF(COUNT(G115:T115)=0,"-",TODAY()-MAX(G115:T115))</f>
-        <v>141</v>
+        <f>IF(COUNT(G115:T115)=0,"-",Dashboard!$I$6-MAX(G115:T115))</f>
+        <v>145</v>
       </c>
       <c r="X115" s="40" t="s">
-        <v>96</v>
+        <v>819</v>
       </c>
     </row>
     <row r="116" spans="1:24" ht="15" customHeight="1">
@@ -11890,7 +12099,9 @@
         <v>46100</v>
       </c>
       <c r="H116" s="37"/>
-      <c r="I116" s="37"/>
+      <c r="I116" s="34">
+        <v>46100</v>
+      </c>
       <c r="J116" s="37"/>
       <c r="K116" s="37"/>
       <c r="L116" s="37"/>
@@ -11903,18 +12114,18 @@
       <c r="S116" s="37"/>
       <c r="T116" s="37"/>
       <c r="U116" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V116" s="39" t="str">
-        <f>IF(T116&lt;&gt;"","9 - Closed",IF(S116&lt;&gt;"","8 - Definitive Agreement",IF(Q116&lt;&gt;"","7 - Diligence",IF(P116&lt;&gt;"","6 - LOI Signed",IF(O116&lt;&gt;"","5 - Mgmt Meeting",IF(L116&lt;&gt;"","4 - IOI Received",IF(K116&lt;&gt;"","3 - CIM Sent",IF(J116&lt;&gt;"","2 - Teaser Sent",IF(I116&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T116&lt;&gt;"","9 - Closed",IF(S116&lt;&gt;"","8 - Definitive Agreement",IF(Q116&lt;&gt;"","7 - Diligence",IF(P116&lt;&gt;"","6 - LOI Signed",IF(O116&lt;&gt;"","5 - Mgmt Meeting",IF(L116&lt;&gt;"","4 - IOI Received",IF(K116&lt;&gt;"","3 - CIM Sent",IF(J116&lt;&gt;"","2 - NDA Signed",IF(I116&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W116" s="39">
-        <f ca="1">IF(COUNT(G116:T116)=0,"-",TODAY()-MAX(G116:T116))</f>
-        <v>140</v>
+        <f>IF(COUNT(G116:T116)=0,"-",Dashboard!$I$6-MAX(G116:T116))</f>
+        <v>144</v>
       </c>
       <c r="X116" s="40" t="s">
-        <v>96</v>
+        <v>819</v>
       </c>
     </row>
     <row r="117" spans="1:24" ht="15" customHeight="1">
@@ -11940,7 +12151,9 @@
         <v>46099</v>
       </c>
       <c r="H117" s="37"/>
-      <c r="I117" s="37"/>
+      <c r="I117" s="34">
+        <v>46099</v>
+      </c>
       <c r="J117" s="37"/>
       <c r="K117" s="37"/>
       <c r="L117" s="37"/>
@@ -11953,18 +12166,18 @@
       <c r="S117" s="37"/>
       <c r="T117" s="37"/>
       <c r="U117" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V117" s="39" t="str">
-        <f>IF(T117&lt;&gt;"","9 - Closed",IF(S117&lt;&gt;"","8 - Definitive Agreement",IF(Q117&lt;&gt;"","7 - Diligence",IF(P117&lt;&gt;"","6 - LOI Signed",IF(O117&lt;&gt;"","5 - Mgmt Meeting",IF(L117&lt;&gt;"","4 - IOI Received",IF(K117&lt;&gt;"","3 - CIM Sent",IF(J117&lt;&gt;"","2 - Teaser Sent",IF(I117&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T117&lt;&gt;"","9 - Closed",IF(S117&lt;&gt;"","8 - Definitive Agreement",IF(Q117&lt;&gt;"","7 - Diligence",IF(P117&lt;&gt;"","6 - LOI Signed",IF(O117&lt;&gt;"","5 - Mgmt Meeting",IF(L117&lt;&gt;"","4 - IOI Received",IF(K117&lt;&gt;"","3 - CIM Sent",IF(J117&lt;&gt;"","2 - NDA Signed",IF(I117&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W117" s="39">
-        <f ca="1">IF(COUNT(G117:T117)=0,"-",TODAY()-MAX(G117:T117))</f>
-        <v>141</v>
+        <f>IF(COUNT(G117:T117)=0,"-",Dashboard!$I$6-MAX(G117:T117))</f>
+        <v>145</v>
       </c>
       <c r="X117" s="40" t="s">
-        <v>96</v>
+        <v>819</v>
       </c>
     </row>
     <row r="118" spans="1:24" ht="15" customHeight="1">
@@ -11990,7 +12203,9 @@
         <v>46103</v>
       </c>
       <c r="H118" s="37"/>
-      <c r="I118" s="37"/>
+      <c r="I118" s="34">
+        <v>46103</v>
+      </c>
       <c r="J118" s="37"/>
       <c r="K118" s="37"/>
       <c r="L118" s="37"/>
@@ -12003,18 +12218,18 @@
       <c r="S118" s="37"/>
       <c r="T118" s="37"/>
       <c r="U118" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V118" s="39" t="str">
-        <f>IF(T118&lt;&gt;"","9 - Closed",IF(S118&lt;&gt;"","8 - Definitive Agreement",IF(Q118&lt;&gt;"","7 - Diligence",IF(P118&lt;&gt;"","6 - LOI Signed",IF(O118&lt;&gt;"","5 - Mgmt Meeting",IF(L118&lt;&gt;"","4 - IOI Received",IF(K118&lt;&gt;"","3 - CIM Sent",IF(J118&lt;&gt;"","2 - Teaser Sent",IF(I118&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T118&lt;&gt;"","9 - Closed",IF(S118&lt;&gt;"","8 - Definitive Agreement",IF(Q118&lt;&gt;"","7 - Diligence",IF(P118&lt;&gt;"","6 - LOI Signed",IF(O118&lt;&gt;"","5 - Mgmt Meeting",IF(L118&lt;&gt;"","4 - IOI Received",IF(K118&lt;&gt;"","3 - CIM Sent",IF(J118&lt;&gt;"","2 - NDA Signed",IF(I118&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W118" s="39">
-        <f ca="1">IF(COUNT(G118:T118)=0,"-",TODAY()-MAX(G118:T118))</f>
-        <v>137</v>
+        <f>IF(COUNT(G118:T118)=0,"-",Dashboard!$I$6-MAX(G118:T118))</f>
+        <v>141</v>
       </c>
       <c r="X118" s="40" t="s">
-        <v>96</v>
+        <v>819</v>
       </c>
     </row>
     <row r="119" spans="1:24" ht="15" customHeight="1">
@@ -12040,7 +12255,9 @@
         <v>46091</v>
       </c>
       <c r="H119" s="37"/>
-      <c r="I119" s="37"/>
+      <c r="I119" s="34">
+        <v>46091</v>
+      </c>
       <c r="J119" s="37"/>
       <c r="K119" s="37"/>
       <c r="L119" s="37"/>
@@ -12056,15 +12273,15 @@
         <v>89</v>
       </c>
       <c r="V119" s="39" t="str">
-        <f>IF(T119&lt;&gt;"","9 - Closed",IF(S119&lt;&gt;"","8 - Definitive Agreement",IF(Q119&lt;&gt;"","7 - Diligence",IF(P119&lt;&gt;"","6 - LOI Signed",IF(O119&lt;&gt;"","5 - Mgmt Meeting",IF(L119&lt;&gt;"","4 - IOI Received",IF(K119&lt;&gt;"","3 - CIM Sent",IF(J119&lt;&gt;"","2 - Teaser Sent",IF(I119&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T119&lt;&gt;"","9 - Closed",IF(S119&lt;&gt;"","8 - Definitive Agreement",IF(Q119&lt;&gt;"","7 - Diligence",IF(P119&lt;&gt;"","6 - LOI Signed",IF(O119&lt;&gt;"","5 - Mgmt Meeting",IF(L119&lt;&gt;"","4 - IOI Received",IF(K119&lt;&gt;"","3 - CIM Sent",IF(J119&lt;&gt;"","2 - NDA Signed",IF(I119&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W119" s="39">
-        <f ca="1">IF(COUNT(G119:T119)=0,"-",TODAY()-MAX(G119:T119))</f>
-        <v>149</v>
+        <f>IF(COUNT(G119:T119)=0,"-",Dashboard!$I$6-MAX(G119:T119))</f>
+        <v>153</v>
       </c>
       <c r="X119" s="40" t="s">
-        <v>90</v>
+        <v>818</v>
       </c>
     </row>
     <row r="120" spans="1:24" ht="15" customHeight="1">
@@ -12090,7 +12307,9 @@
         <v>46097</v>
       </c>
       <c r="H120" s="37"/>
-      <c r="I120" s="37"/>
+      <c r="I120" s="34">
+        <v>46097</v>
+      </c>
       <c r="J120" s="37"/>
       <c r="K120" s="37"/>
       <c r="L120" s="37"/>
@@ -12103,18 +12322,18 @@
       <c r="S120" s="37"/>
       <c r="T120" s="37"/>
       <c r="U120" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V120" s="39" t="str">
-        <f>IF(T120&lt;&gt;"","9 - Closed",IF(S120&lt;&gt;"","8 - Definitive Agreement",IF(Q120&lt;&gt;"","7 - Diligence",IF(P120&lt;&gt;"","6 - LOI Signed",IF(O120&lt;&gt;"","5 - Mgmt Meeting",IF(L120&lt;&gt;"","4 - IOI Received",IF(K120&lt;&gt;"","3 - CIM Sent",IF(J120&lt;&gt;"","2 - Teaser Sent",IF(I120&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T120&lt;&gt;"","9 - Closed",IF(S120&lt;&gt;"","8 - Definitive Agreement",IF(Q120&lt;&gt;"","7 - Diligence",IF(P120&lt;&gt;"","6 - LOI Signed",IF(O120&lt;&gt;"","5 - Mgmt Meeting",IF(L120&lt;&gt;"","4 - IOI Received",IF(K120&lt;&gt;"","3 - CIM Sent",IF(J120&lt;&gt;"","2 - NDA Signed",IF(I120&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W120" s="39">
-        <f ca="1">IF(COUNT(G120:T120)=0,"-",TODAY()-MAX(G120:T120))</f>
-        <v>143</v>
+        <f>IF(COUNT(G120:T120)=0,"-",Dashboard!$I$6-MAX(G120:T120))</f>
+        <v>147</v>
       </c>
       <c r="X120" s="40" t="s">
-        <v>96</v>
+        <v>819</v>
       </c>
     </row>
     <row r="121" spans="1:24" ht="15" customHeight="1">
@@ -12140,7 +12359,9 @@
         <v>46083</v>
       </c>
       <c r="H121" s="37"/>
-      <c r="I121" s="37"/>
+      <c r="I121" s="34">
+        <v>46083</v>
+      </c>
       <c r="J121" s="37"/>
       <c r="K121" s="37"/>
       <c r="L121" s="37"/>
@@ -12156,15 +12377,15 @@
         <v>89</v>
       </c>
       <c r="V121" s="39" t="str">
-        <f>IF(T121&lt;&gt;"","9 - Closed",IF(S121&lt;&gt;"","8 - Definitive Agreement",IF(Q121&lt;&gt;"","7 - Diligence",IF(P121&lt;&gt;"","6 - LOI Signed",IF(O121&lt;&gt;"","5 - Mgmt Meeting",IF(L121&lt;&gt;"","4 - IOI Received",IF(K121&lt;&gt;"","3 - CIM Sent",IF(J121&lt;&gt;"","2 - Teaser Sent",IF(I121&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T121&lt;&gt;"","9 - Closed",IF(S121&lt;&gt;"","8 - Definitive Agreement",IF(Q121&lt;&gt;"","7 - Diligence",IF(P121&lt;&gt;"","6 - LOI Signed",IF(O121&lt;&gt;"","5 - Mgmt Meeting",IF(L121&lt;&gt;"","4 - IOI Received",IF(K121&lt;&gt;"","3 - CIM Sent",IF(J121&lt;&gt;"","2 - NDA Signed",IF(I121&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W121" s="39">
-        <f ca="1">IF(COUNT(G121:T121)=0,"-",TODAY()-MAX(G121:T121))</f>
-        <v>157</v>
+        <f>IF(COUNT(G121:T121)=0,"-",Dashboard!$I$6-MAX(G121:T121))</f>
+        <v>161</v>
       </c>
       <c r="X121" s="40" t="s">
-        <v>90</v>
+        <v>818</v>
       </c>
     </row>
     <row r="122" spans="1:24" ht="15" customHeight="1">
@@ -12190,7 +12411,9 @@
         <v>46105</v>
       </c>
       <c r="H122" s="37"/>
-      <c r="I122" s="37"/>
+      <c r="I122" s="34">
+        <v>46105</v>
+      </c>
       <c r="J122" s="37"/>
       <c r="K122" s="37"/>
       <c r="L122" s="37"/>
@@ -12206,15 +12429,15 @@
         <v>89</v>
       </c>
       <c r="V122" s="39" t="str">
-        <f>IF(T122&lt;&gt;"","9 - Closed",IF(S122&lt;&gt;"","8 - Definitive Agreement",IF(Q122&lt;&gt;"","7 - Diligence",IF(P122&lt;&gt;"","6 - LOI Signed",IF(O122&lt;&gt;"","5 - Mgmt Meeting",IF(L122&lt;&gt;"","4 - IOI Received",IF(K122&lt;&gt;"","3 - CIM Sent",IF(J122&lt;&gt;"","2 - Teaser Sent",IF(I122&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T122&lt;&gt;"","9 - Closed",IF(S122&lt;&gt;"","8 - Definitive Agreement",IF(Q122&lt;&gt;"","7 - Diligence",IF(P122&lt;&gt;"","6 - LOI Signed",IF(O122&lt;&gt;"","5 - Mgmt Meeting",IF(L122&lt;&gt;"","4 - IOI Received",IF(K122&lt;&gt;"","3 - CIM Sent",IF(J122&lt;&gt;"","2 - NDA Signed",IF(I122&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W122" s="39">
-        <f ca="1">IF(COUNT(G122:T122)=0,"-",TODAY()-MAX(G122:T122))</f>
-        <v>135</v>
+        <f>IF(COUNT(G122:T122)=0,"-",Dashboard!$I$6-MAX(G122:T122))</f>
+        <v>139</v>
       </c>
       <c r="X122" s="40" t="s">
-        <v>90</v>
+        <v>818</v>
       </c>
     </row>
     <row r="123" spans="1:24" ht="15" customHeight="1">
@@ -12240,7 +12463,9 @@
         <v>46100</v>
       </c>
       <c r="H123" s="37"/>
-      <c r="I123" s="37"/>
+      <c r="I123" s="34">
+        <v>46100</v>
+      </c>
       <c r="J123" s="37"/>
       <c r="K123" s="37"/>
       <c r="L123" s="37"/>
@@ -12253,18 +12478,18 @@
       <c r="S123" s="37"/>
       <c r="T123" s="37"/>
       <c r="U123" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V123" s="39" t="str">
-        <f>IF(T123&lt;&gt;"","9 - Closed",IF(S123&lt;&gt;"","8 - Definitive Agreement",IF(Q123&lt;&gt;"","7 - Diligence",IF(P123&lt;&gt;"","6 - LOI Signed",IF(O123&lt;&gt;"","5 - Mgmt Meeting",IF(L123&lt;&gt;"","4 - IOI Received",IF(K123&lt;&gt;"","3 - CIM Sent",IF(J123&lt;&gt;"","2 - Teaser Sent",IF(I123&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T123&lt;&gt;"","9 - Closed",IF(S123&lt;&gt;"","8 - Definitive Agreement",IF(Q123&lt;&gt;"","7 - Diligence",IF(P123&lt;&gt;"","6 - LOI Signed",IF(O123&lt;&gt;"","5 - Mgmt Meeting",IF(L123&lt;&gt;"","4 - IOI Received",IF(K123&lt;&gt;"","3 - CIM Sent",IF(J123&lt;&gt;"","2 - NDA Signed",IF(I123&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W123" s="39">
-        <f ca="1">IF(COUNT(G123:T123)=0,"-",TODAY()-MAX(G123:T123))</f>
-        <v>140</v>
+        <f>IF(COUNT(G123:T123)=0,"-",Dashboard!$I$6-MAX(G123:T123))</f>
+        <v>144</v>
       </c>
       <c r="X123" s="40" t="s">
-        <v>96</v>
+        <v>819</v>
       </c>
     </row>
     <row r="124" spans="1:24" ht="15" customHeight="1">
@@ -12290,7 +12515,9 @@
         <v>46086</v>
       </c>
       <c r="H124" s="37"/>
-      <c r="I124" s="37"/>
+      <c r="I124" s="34">
+        <v>46086</v>
+      </c>
       <c r="J124" s="37"/>
       <c r="K124" s="37"/>
       <c r="L124" s="37"/>
@@ -12303,18 +12530,18 @@
       <c r="S124" s="37"/>
       <c r="T124" s="37"/>
       <c r="U124" s="38" t="s">
-        <v>52</v>
+        <v>190</v>
       </c>
       <c r="V124" s="39" t="str">
-        <f>IF(T124&lt;&gt;"","9 - Closed",IF(S124&lt;&gt;"","8 - Definitive Agreement",IF(Q124&lt;&gt;"","7 - Diligence",IF(P124&lt;&gt;"","6 - LOI Signed",IF(O124&lt;&gt;"","5 - Mgmt Meeting",IF(L124&lt;&gt;"","4 - IOI Received",IF(K124&lt;&gt;"","3 - CIM Sent",IF(J124&lt;&gt;"","2 - Teaser Sent",IF(I124&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T124&lt;&gt;"","9 - Closed",IF(S124&lt;&gt;"","8 - Definitive Agreement",IF(Q124&lt;&gt;"","7 - Diligence",IF(P124&lt;&gt;"","6 - LOI Signed",IF(O124&lt;&gt;"","5 - Mgmt Meeting",IF(L124&lt;&gt;"","4 - IOI Received",IF(K124&lt;&gt;"","3 - CIM Sent",IF(J124&lt;&gt;"","2 - NDA Signed",IF(I124&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W124" s="39">
-        <f ca="1">IF(COUNT(G124:T124)=0,"-",TODAY()-MAX(G124:T124))</f>
-        <v>154</v>
+        <f>IF(COUNT(G124:T124)=0,"-",Dashboard!$I$6-MAX(G124:T124))</f>
+        <v>158</v>
       </c>
       <c r="X124" s="40" t="s">
-        <v>96</v>
+        <v>819</v>
       </c>
     </row>
     <row r="125" spans="1:24" ht="15" customHeight="1">
@@ -12340,7 +12567,9 @@
         <v>46087</v>
       </c>
       <c r="H125" s="37"/>
-      <c r="I125" s="37"/>
+      <c r="I125" s="34">
+        <v>46087</v>
+      </c>
       <c r="J125" s="37"/>
       <c r="K125" s="37"/>
       <c r="L125" s="37"/>
@@ -12356,15 +12585,15 @@
         <v>89</v>
       </c>
       <c r="V125" s="39" t="str">
-        <f>IF(T125&lt;&gt;"","9 - Closed",IF(S125&lt;&gt;"","8 - Definitive Agreement",IF(Q125&lt;&gt;"","7 - Diligence",IF(P125&lt;&gt;"","6 - LOI Signed",IF(O125&lt;&gt;"","5 - Mgmt Meeting",IF(L125&lt;&gt;"","4 - IOI Received",IF(K125&lt;&gt;"","3 - CIM Sent",IF(J125&lt;&gt;"","2 - Teaser Sent",IF(I125&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T125&lt;&gt;"","9 - Closed",IF(S125&lt;&gt;"","8 - Definitive Agreement",IF(Q125&lt;&gt;"","7 - Diligence",IF(P125&lt;&gt;"","6 - LOI Signed",IF(O125&lt;&gt;"","5 - Mgmt Meeting",IF(L125&lt;&gt;"","4 - IOI Received",IF(K125&lt;&gt;"","3 - CIM Sent",IF(J125&lt;&gt;"","2 - NDA Signed",IF(I125&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>1 - Teaser Sent</v>
       </c>
       <c r="W125" s="39">
-        <f ca="1">IF(COUNT(G125:T125)=0,"-",TODAY()-MAX(G125:T125))</f>
-        <v>153</v>
+        <f>IF(COUNT(G125:T125)=0,"-",Dashboard!$I$6-MAX(G125:T125))</f>
+        <v>157</v>
       </c>
       <c r="X125" s="40" t="s">
-        <v>90</v>
+        <v>818</v>
       </c>
     </row>
     <row r="126" spans="1:24" ht="15" customHeight="1">
@@ -12400,11 +12629,11 @@
         <v>577</v>
       </c>
       <c r="V126" s="46" t="str">
-        <f>IF(T126&lt;&gt;"","9 - Closed",IF(S126&lt;&gt;"","8 - Definitive Agreement",IF(Q126&lt;&gt;"","7 - Diligence",IF(P126&lt;&gt;"","6 - LOI Signed",IF(O126&lt;&gt;"","5 - Mgmt Meeting",IF(L126&lt;&gt;"","4 - IOI Received",IF(K126&lt;&gt;"","3 - CIM Sent",IF(J126&lt;&gt;"","2 - Teaser Sent",IF(I126&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T126&lt;&gt;"","9 - Closed",IF(S126&lt;&gt;"","8 - Definitive Agreement",IF(Q126&lt;&gt;"","7 - Diligence",IF(P126&lt;&gt;"","6 - LOI Signed",IF(O126&lt;&gt;"","5 - Mgmt Meeting",IF(L126&lt;&gt;"","4 - IOI Received",IF(K126&lt;&gt;"","3 - CIM Sent",IF(J126&lt;&gt;"","2 - NDA Signed",IF(I126&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>0 - Not Contacted</v>
       </c>
       <c r="W126" s="47" t="str">
-        <f ca="1">IF(COUNT(G126:T126)=0,"-",TODAY()-MAX(G126:T126))</f>
+        <f>IF(COUNT(G126:T126)=0,"-",Dashboard!$I$6-MAX(G126:T126))</f>
         <v>-</v>
       </c>
       <c r="X126" s="48" t="s">
@@ -12444,11 +12673,11 @@
         <v>577</v>
       </c>
       <c r="V127" s="54" t="str">
-        <f>IF(T127&lt;&gt;"","9 - Closed",IF(S127&lt;&gt;"","8 - Definitive Agreement",IF(Q127&lt;&gt;"","7 - Diligence",IF(P127&lt;&gt;"","6 - LOI Signed",IF(O127&lt;&gt;"","5 - Mgmt Meeting",IF(L127&lt;&gt;"","4 - IOI Received",IF(K127&lt;&gt;"","3 - CIM Sent",IF(J127&lt;&gt;"","2 - Teaser Sent",IF(I127&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T127&lt;&gt;"","9 - Closed",IF(S127&lt;&gt;"","8 - Definitive Agreement",IF(Q127&lt;&gt;"","7 - Diligence",IF(P127&lt;&gt;"","6 - LOI Signed",IF(O127&lt;&gt;"","5 - Mgmt Meeting",IF(L127&lt;&gt;"","4 - IOI Received",IF(K127&lt;&gt;"","3 - CIM Sent",IF(J127&lt;&gt;"","2 - NDA Signed",IF(I127&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>0 - Not Contacted</v>
       </c>
       <c r="W127" s="55" t="str">
-        <f ca="1">IF(COUNT(G127:T127)=0,"-",TODAY()-MAX(G127:T127))</f>
+        <f>IF(COUNT(G127:T127)=0,"-",Dashboard!$I$6-MAX(G127:T127))</f>
         <v>-</v>
       </c>
       <c r="X127" s="56" t="s">
@@ -12488,11 +12717,11 @@
         <v>577</v>
       </c>
       <c r="V128" s="46" t="str">
-        <f>IF(T128&lt;&gt;"","9 - Closed",IF(S128&lt;&gt;"","8 - Definitive Agreement",IF(Q128&lt;&gt;"","7 - Diligence",IF(P128&lt;&gt;"","6 - LOI Signed",IF(O128&lt;&gt;"","5 - Mgmt Meeting",IF(L128&lt;&gt;"","4 - IOI Received",IF(K128&lt;&gt;"","3 - CIM Sent",IF(J128&lt;&gt;"","2 - Teaser Sent",IF(I128&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T128&lt;&gt;"","9 - Closed",IF(S128&lt;&gt;"","8 - Definitive Agreement",IF(Q128&lt;&gt;"","7 - Diligence",IF(P128&lt;&gt;"","6 - LOI Signed",IF(O128&lt;&gt;"","5 - Mgmt Meeting",IF(L128&lt;&gt;"","4 - IOI Received",IF(K128&lt;&gt;"","3 - CIM Sent",IF(J128&lt;&gt;"","2 - NDA Signed",IF(I128&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>0 - Not Contacted</v>
       </c>
       <c r="W128" s="47" t="str">
-        <f ca="1">IF(COUNT(G128:T128)=0,"-",TODAY()-MAX(G128:T128))</f>
+        <f>IF(COUNT(G128:T128)=0,"-",Dashboard!$I$6-MAX(G128:T128))</f>
         <v>-</v>
       </c>
       <c r="X128" s="48" t="s">
@@ -12532,11 +12761,11 @@
         <v>577</v>
       </c>
       <c r="V129" s="54" t="str">
-        <f>IF(T129&lt;&gt;"","9 - Closed",IF(S129&lt;&gt;"","8 - Definitive Agreement",IF(Q129&lt;&gt;"","7 - Diligence",IF(P129&lt;&gt;"","6 - LOI Signed",IF(O129&lt;&gt;"","5 - Mgmt Meeting",IF(L129&lt;&gt;"","4 - IOI Received",IF(K129&lt;&gt;"","3 - CIM Sent",IF(J129&lt;&gt;"","2 - Teaser Sent",IF(I129&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T129&lt;&gt;"","9 - Closed",IF(S129&lt;&gt;"","8 - Definitive Agreement",IF(Q129&lt;&gt;"","7 - Diligence",IF(P129&lt;&gt;"","6 - LOI Signed",IF(O129&lt;&gt;"","5 - Mgmt Meeting",IF(L129&lt;&gt;"","4 - IOI Received",IF(K129&lt;&gt;"","3 - CIM Sent",IF(J129&lt;&gt;"","2 - NDA Signed",IF(I129&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>0 - Not Contacted</v>
       </c>
       <c r="W129" s="55" t="str">
-        <f ca="1">IF(COUNT(G129:T129)=0,"-",TODAY()-MAX(G129:T129))</f>
+        <f>IF(COUNT(G129:T129)=0,"-",Dashboard!$I$6-MAX(G129:T129))</f>
         <v>-</v>
       </c>
       <c r="X129" s="56" t="s">
@@ -12576,11 +12805,11 @@
         <v>577</v>
       </c>
       <c r="V130" s="46" t="str">
-        <f>IF(T130&lt;&gt;"","9 - Closed",IF(S130&lt;&gt;"","8 - Definitive Agreement",IF(Q130&lt;&gt;"","7 - Diligence",IF(P130&lt;&gt;"","6 - LOI Signed",IF(O130&lt;&gt;"","5 - Mgmt Meeting",IF(L130&lt;&gt;"","4 - IOI Received",IF(K130&lt;&gt;"","3 - CIM Sent",IF(J130&lt;&gt;"","2 - Teaser Sent",IF(I130&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T130&lt;&gt;"","9 - Closed",IF(S130&lt;&gt;"","8 - Definitive Agreement",IF(Q130&lt;&gt;"","7 - Diligence",IF(P130&lt;&gt;"","6 - LOI Signed",IF(O130&lt;&gt;"","5 - Mgmt Meeting",IF(L130&lt;&gt;"","4 - IOI Received",IF(K130&lt;&gt;"","3 - CIM Sent",IF(J130&lt;&gt;"","2 - NDA Signed",IF(I130&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>0 - Not Contacted</v>
       </c>
       <c r="W130" s="47" t="str">
-        <f ca="1">IF(COUNT(G130:T130)=0,"-",TODAY()-MAX(G130:T130))</f>
+        <f>IF(COUNT(G130:T130)=0,"-",Dashboard!$I$6-MAX(G130:T130))</f>
         <v>-</v>
       </c>
       <c r="X130" s="48" t="s">
@@ -12620,11 +12849,11 @@
         <v>577</v>
       </c>
       <c r="V131" s="54" t="str">
-        <f>IF(T131&lt;&gt;"","9 - Closed",IF(S131&lt;&gt;"","8 - Definitive Agreement",IF(Q131&lt;&gt;"","7 - Diligence",IF(P131&lt;&gt;"","6 - LOI Signed",IF(O131&lt;&gt;"","5 - Mgmt Meeting",IF(L131&lt;&gt;"","4 - IOI Received",IF(K131&lt;&gt;"","3 - CIM Sent",IF(J131&lt;&gt;"","2 - Teaser Sent",IF(I131&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T131&lt;&gt;"","9 - Closed",IF(S131&lt;&gt;"","8 - Definitive Agreement",IF(Q131&lt;&gt;"","7 - Diligence",IF(P131&lt;&gt;"","6 - LOI Signed",IF(O131&lt;&gt;"","5 - Mgmt Meeting",IF(L131&lt;&gt;"","4 - IOI Received",IF(K131&lt;&gt;"","3 - CIM Sent",IF(J131&lt;&gt;"","2 - NDA Signed",IF(I131&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>0 - Not Contacted</v>
       </c>
       <c r="W131" s="55" t="str">
-        <f ca="1">IF(COUNT(G131:T131)=0,"-",TODAY()-MAX(G131:T131))</f>
+        <f>IF(COUNT(G131:T131)=0,"-",Dashboard!$I$6-MAX(G131:T131))</f>
         <v>-</v>
       </c>
       <c r="X131" s="56" t="s">
@@ -12664,11 +12893,11 @@
         <v>577</v>
       </c>
       <c r="V132" s="46" t="str">
-        <f>IF(T132&lt;&gt;"","9 - Closed",IF(S132&lt;&gt;"","8 - Definitive Agreement",IF(Q132&lt;&gt;"","7 - Diligence",IF(P132&lt;&gt;"","6 - LOI Signed",IF(O132&lt;&gt;"","5 - Mgmt Meeting",IF(L132&lt;&gt;"","4 - IOI Received",IF(K132&lt;&gt;"","3 - CIM Sent",IF(J132&lt;&gt;"","2 - Teaser Sent",IF(I132&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T132&lt;&gt;"","9 - Closed",IF(S132&lt;&gt;"","8 - Definitive Agreement",IF(Q132&lt;&gt;"","7 - Diligence",IF(P132&lt;&gt;"","6 - LOI Signed",IF(O132&lt;&gt;"","5 - Mgmt Meeting",IF(L132&lt;&gt;"","4 - IOI Received",IF(K132&lt;&gt;"","3 - CIM Sent",IF(J132&lt;&gt;"","2 - NDA Signed",IF(I132&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>0 - Not Contacted</v>
       </c>
       <c r="W132" s="47" t="str">
-        <f ca="1">IF(COUNT(G132:T132)=0,"-",TODAY()-MAX(G132:T132))</f>
+        <f>IF(COUNT(G132:T132)=0,"-",Dashboard!$I$6-MAX(G132:T132))</f>
         <v>-</v>
       </c>
       <c r="X132" s="48" t="s">
@@ -12708,11 +12937,11 @@
         <v>577</v>
       </c>
       <c r="V133" s="54" t="str">
-        <f>IF(T133&lt;&gt;"","9 - Closed",IF(S133&lt;&gt;"","8 - Definitive Agreement",IF(Q133&lt;&gt;"","7 - Diligence",IF(P133&lt;&gt;"","6 - LOI Signed",IF(O133&lt;&gt;"","5 - Mgmt Meeting",IF(L133&lt;&gt;"","4 - IOI Received",IF(K133&lt;&gt;"","3 - CIM Sent",IF(J133&lt;&gt;"","2 - Teaser Sent",IF(I133&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T133&lt;&gt;"","9 - Closed",IF(S133&lt;&gt;"","8 - Definitive Agreement",IF(Q133&lt;&gt;"","7 - Diligence",IF(P133&lt;&gt;"","6 - LOI Signed",IF(O133&lt;&gt;"","5 - Mgmt Meeting",IF(L133&lt;&gt;"","4 - IOI Received",IF(K133&lt;&gt;"","3 - CIM Sent",IF(J133&lt;&gt;"","2 - NDA Signed",IF(I133&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>0 - Not Contacted</v>
       </c>
       <c r="W133" s="55" t="str">
-        <f ca="1">IF(COUNT(G133:T133)=0,"-",TODAY()-MAX(G133:T133))</f>
+        <f>IF(COUNT(G133:T133)=0,"-",Dashboard!$I$6-MAX(G133:T133))</f>
         <v>-</v>
       </c>
       <c r="X133" s="56" t="s">
@@ -12752,11 +12981,11 @@
         <v>577</v>
       </c>
       <c r="V134" s="46" t="str">
-        <f>IF(T134&lt;&gt;"","9 - Closed",IF(S134&lt;&gt;"","8 - Definitive Agreement",IF(Q134&lt;&gt;"","7 - Diligence",IF(P134&lt;&gt;"","6 - LOI Signed",IF(O134&lt;&gt;"","5 - Mgmt Meeting",IF(L134&lt;&gt;"","4 - IOI Received",IF(K134&lt;&gt;"","3 - CIM Sent",IF(J134&lt;&gt;"","2 - Teaser Sent",IF(I134&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T134&lt;&gt;"","9 - Closed",IF(S134&lt;&gt;"","8 - Definitive Agreement",IF(Q134&lt;&gt;"","7 - Diligence",IF(P134&lt;&gt;"","6 - LOI Signed",IF(O134&lt;&gt;"","5 - Mgmt Meeting",IF(L134&lt;&gt;"","4 - IOI Received",IF(K134&lt;&gt;"","3 - CIM Sent",IF(J134&lt;&gt;"","2 - NDA Signed",IF(I134&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>0 - Not Contacted</v>
       </c>
       <c r="W134" s="47" t="str">
-        <f ca="1">IF(COUNT(G134:T134)=0,"-",TODAY()-MAX(G134:T134))</f>
+        <f>IF(COUNT(G134:T134)=0,"-",Dashboard!$I$6-MAX(G134:T134))</f>
         <v>-</v>
       </c>
       <c r="X134" s="48" t="s">
@@ -12796,11 +13025,11 @@
         <v>577</v>
       </c>
       <c r="V135" s="54" t="str">
-        <f>IF(T135&lt;&gt;"","9 - Closed",IF(S135&lt;&gt;"","8 - Definitive Agreement",IF(Q135&lt;&gt;"","7 - Diligence",IF(P135&lt;&gt;"","6 - LOI Signed",IF(O135&lt;&gt;"","5 - Mgmt Meeting",IF(L135&lt;&gt;"","4 - IOI Received",IF(K135&lt;&gt;"","3 - CIM Sent",IF(J135&lt;&gt;"","2 - Teaser Sent",IF(I135&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T135&lt;&gt;"","9 - Closed",IF(S135&lt;&gt;"","8 - Definitive Agreement",IF(Q135&lt;&gt;"","7 - Diligence",IF(P135&lt;&gt;"","6 - LOI Signed",IF(O135&lt;&gt;"","5 - Mgmt Meeting",IF(L135&lt;&gt;"","4 - IOI Received",IF(K135&lt;&gt;"","3 - CIM Sent",IF(J135&lt;&gt;"","2 - NDA Signed",IF(I135&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>0 - Not Contacted</v>
       </c>
       <c r="W135" s="55" t="str">
-        <f ca="1">IF(COUNT(G135:T135)=0,"-",TODAY()-MAX(G135:T135))</f>
+        <f>IF(COUNT(G135:T135)=0,"-",Dashboard!$I$6-MAX(G135:T135))</f>
         <v>-</v>
       </c>
       <c r="X135" s="56" t="s">
@@ -12840,11 +13069,11 @@
         <v>577</v>
       </c>
       <c r="V136" s="46" t="str">
-        <f>IF(T136&lt;&gt;"","9 - Closed",IF(S136&lt;&gt;"","8 - Definitive Agreement",IF(Q136&lt;&gt;"","7 - Diligence",IF(P136&lt;&gt;"","6 - LOI Signed",IF(O136&lt;&gt;"","5 - Mgmt Meeting",IF(L136&lt;&gt;"","4 - IOI Received",IF(K136&lt;&gt;"","3 - CIM Sent",IF(J136&lt;&gt;"","2 - Teaser Sent",IF(I136&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T136&lt;&gt;"","9 - Closed",IF(S136&lt;&gt;"","8 - Definitive Agreement",IF(Q136&lt;&gt;"","7 - Diligence",IF(P136&lt;&gt;"","6 - LOI Signed",IF(O136&lt;&gt;"","5 - Mgmt Meeting",IF(L136&lt;&gt;"","4 - IOI Received",IF(K136&lt;&gt;"","3 - CIM Sent",IF(J136&lt;&gt;"","2 - NDA Signed",IF(I136&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>0 - Not Contacted</v>
       </c>
       <c r="W136" s="47" t="str">
-        <f ca="1">IF(COUNT(G136:T136)=0,"-",TODAY()-MAX(G136:T136))</f>
+        <f>IF(COUNT(G136:T136)=0,"-",Dashboard!$I$6-MAX(G136:T136))</f>
         <v>-</v>
       </c>
       <c r="X136" s="48" t="s">
@@ -12884,11 +13113,11 @@
         <v>577</v>
       </c>
       <c r="V137" s="54" t="str">
-        <f>IF(T137&lt;&gt;"","9 - Closed",IF(S137&lt;&gt;"","8 - Definitive Agreement",IF(Q137&lt;&gt;"","7 - Diligence",IF(P137&lt;&gt;"","6 - LOI Signed",IF(O137&lt;&gt;"","5 - Mgmt Meeting",IF(L137&lt;&gt;"","4 - IOI Received",IF(K137&lt;&gt;"","3 - CIM Sent",IF(J137&lt;&gt;"","2 - Teaser Sent",IF(I137&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T137&lt;&gt;"","9 - Closed",IF(S137&lt;&gt;"","8 - Definitive Agreement",IF(Q137&lt;&gt;"","7 - Diligence",IF(P137&lt;&gt;"","6 - LOI Signed",IF(O137&lt;&gt;"","5 - Mgmt Meeting",IF(L137&lt;&gt;"","4 - IOI Received",IF(K137&lt;&gt;"","3 - CIM Sent",IF(J137&lt;&gt;"","2 - NDA Signed",IF(I137&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>0 - Not Contacted</v>
       </c>
       <c r="W137" s="55" t="str">
-        <f ca="1">IF(COUNT(G137:T137)=0,"-",TODAY()-MAX(G137:T137))</f>
+        <f>IF(COUNT(G137:T137)=0,"-",Dashboard!$I$6-MAX(G137:T137))</f>
         <v>-</v>
       </c>
       <c r="X137" s="56" t="s">
@@ -12928,11 +13157,11 @@
         <v>577</v>
       </c>
       <c r="V138" s="46" t="str">
-        <f>IF(T138&lt;&gt;"","9 - Closed",IF(S138&lt;&gt;"","8 - Definitive Agreement",IF(Q138&lt;&gt;"","7 - Diligence",IF(P138&lt;&gt;"","6 - LOI Signed",IF(O138&lt;&gt;"","5 - Mgmt Meeting",IF(L138&lt;&gt;"","4 - IOI Received",IF(K138&lt;&gt;"","3 - CIM Sent",IF(J138&lt;&gt;"","2 - Teaser Sent",IF(I138&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T138&lt;&gt;"","9 - Closed",IF(S138&lt;&gt;"","8 - Definitive Agreement",IF(Q138&lt;&gt;"","7 - Diligence",IF(P138&lt;&gt;"","6 - LOI Signed",IF(O138&lt;&gt;"","5 - Mgmt Meeting",IF(L138&lt;&gt;"","4 - IOI Received",IF(K138&lt;&gt;"","3 - CIM Sent",IF(J138&lt;&gt;"","2 - NDA Signed",IF(I138&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>0 - Not Contacted</v>
       </c>
       <c r="W138" s="47" t="str">
-        <f ca="1">IF(COUNT(G138:T138)=0,"-",TODAY()-MAX(G138:T138))</f>
+        <f>IF(COUNT(G138:T138)=0,"-",Dashboard!$I$6-MAX(G138:T138))</f>
         <v>-</v>
       </c>
       <c r="X138" s="48" t="s">
@@ -12972,11 +13201,11 @@
         <v>577</v>
       </c>
       <c r="V139" s="54" t="str">
-        <f>IF(T139&lt;&gt;"","9 - Closed",IF(S139&lt;&gt;"","8 - Definitive Agreement",IF(Q139&lt;&gt;"","7 - Diligence",IF(P139&lt;&gt;"","6 - LOI Signed",IF(O139&lt;&gt;"","5 - Mgmt Meeting",IF(L139&lt;&gt;"","4 - IOI Received",IF(K139&lt;&gt;"","3 - CIM Sent",IF(J139&lt;&gt;"","2 - Teaser Sent",IF(I139&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T139&lt;&gt;"","9 - Closed",IF(S139&lt;&gt;"","8 - Definitive Agreement",IF(Q139&lt;&gt;"","7 - Diligence",IF(P139&lt;&gt;"","6 - LOI Signed",IF(O139&lt;&gt;"","5 - Mgmt Meeting",IF(L139&lt;&gt;"","4 - IOI Received",IF(K139&lt;&gt;"","3 - CIM Sent",IF(J139&lt;&gt;"","2 - NDA Signed",IF(I139&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>0 - Not Contacted</v>
       </c>
       <c r="W139" s="55" t="str">
-        <f ca="1">IF(COUNT(G139:T139)=0,"-",TODAY()-MAX(G139:T139))</f>
+        <f>IF(COUNT(G139:T139)=0,"-",Dashboard!$I$6-MAX(G139:T139))</f>
         <v>-</v>
       </c>
       <c r="X139" s="56" t="s">
@@ -13016,11 +13245,11 @@
         <v>577</v>
       </c>
       <c r="V140" s="46" t="str">
-        <f>IF(T140&lt;&gt;"","9 - Closed",IF(S140&lt;&gt;"","8 - Definitive Agreement",IF(Q140&lt;&gt;"","7 - Diligence",IF(P140&lt;&gt;"","6 - LOI Signed",IF(O140&lt;&gt;"","5 - Mgmt Meeting",IF(L140&lt;&gt;"","4 - IOI Received",IF(K140&lt;&gt;"","3 - CIM Sent",IF(J140&lt;&gt;"","2 - Teaser Sent",IF(I140&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T140&lt;&gt;"","9 - Closed",IF(S140&lt;&gt;"","8 - Definitive Agreement",IF(Q140&lt;&gt;"","7 - Diligence",IF(P140&lt;&gt;"","6 - LOI Signed",IF(O140&lt;&gt;"","5 - Mgmt Meeting",IF(L140&lt;&gt;"","4 - IOI Received",IF(K140&lt;&gt;"","3 - CIM Sent",IF(J140&lt;&gt;"","2 - NDA Signed",IF(I140&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>0 - Not Contacted</v>
       </c>
       <c r="W140" s="47" t="str">
-        <f ca="1">IF(COUNT(G140:T140)=0,"-",TODAY()-MAX(G140:T140))</f>
+        <f>IF(COUNT(G140:T140)=0,"-",Dashboard!$I$6-MAX(G140:T140))</f>
         <v>-</v>
       </c>
       <c r="X140" s="48" t="s">
@@ -13060,11 +13289,11 @@
         <v>577</v>
       </c>
       <c r="V141" s="54" t="str">
-        <f>IF(T141&lt;&gt;"","9 - Closed",IF(S141&lt;&gt;"","8 - Definitive Agreement",IF(Q141&lt;&gt;"","7 - Diligence",IF(P141&lt;&gt;"","6 - LOI Signed",IF(O141&lt;&gt;"","5 - Mgmt Meeting",IF(L141&lt;&gt;"","4 - IOI Received",IF(K141&lt;&gt;"","3 - CIM Sent",IF(J141&lt;&gt;"","2 - Teaser Sent",IF(I141&lt;&gt;"","1 - NDA Signed","0 - Outreach")))))))))</f>
-        <v>0 - Outreach</v>
+        <f>IF(T141&lt;&gt;"","9 - Closed",IF(S141&lt;&gt;"","8 - Definitive Agreement",IF(Q141&lt;&gt;"","7 - Diligence",IF(P141&lt;&gt;"","6 - LOI Signed",IF(O141&lt;&gt;"","5 - Mgmt Meeting",IF(L141&lt;&gt;"","4 - IOI Received",IF(K141&lt;&gt;"","3 - CIM Sent",IF(J141&lt;&gt;"","2 - NDA Signed",IF(I141&lt;&gt;"","1 - Teaser Sent","0 - Not Contacted")))))))))</f>
+        <v>0 - Not Contacted</v>
       </c>
       <c r="W141" s="55" t="str">
-        <f ca="1">IF(COUNT(G141:T141)=0,"-",TODAY()-MAX(G141:T141))</f>
+        <f>IF(COUNT(G141:T141)=0,"-",Dashboard!$I$6-MAX(G141:T141))</f>
         <v>-</v>
       </c>
       <c r="X141" s="56" t="s">
@@ -13923,7 +14152,7 @@
         <v>46233</v>
       </c>
       <c r="G8" s="65" t="s">
-        <v>733</v>
+        <v>822</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" customHeight="1">
@@ -14426,7 +14655,7 @@
       <c r="E32" s="10"/>
       <c r="F32" s="9">
         <f>COUNTIF(E4:E29,"Complete")/COUNTA(E4:E29)</f>
-        <v>0.34615384615384615</v>
+        <v>0.346153846153846</v>
       </c>
       <c r="G32" s="9"/>
     </row>
@@ -14498,13 +14727,13 @@
     <row r="4" spans="1:2" ht="48" customHeight="1">
       <c r="A4" s="66"/>
       <c r="B4" s="68" t="s">
-        <v>788</v>
+        <v>824</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="48" customHeight="1">
       <c r="A5" s="66"/>
       <c r="B5" s="68" t="s">
-        <v>789</v>
+        <v>825</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="48" customHeight="1">
@@ -14531,7 +14760,7 @@
     <row r="10" spans="1:2" ht="33.75" customHeight="1">
       <c r="A10" s="66"/>
       <c r="B10" s="68" t="s">
-        <v>793</v>
+        <v>826</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="33.75" customHeight="1">
@@ -14549,7 +14778,7 @@
     <row r="13" spans="1:2" ht="34.5" customHeight="1">
       <c r="A13" s="66"/>
       <c r="B13" s="68" t="s">
-        <v>796</v>
+        <v>827</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="18" customHeight="1">
@@ -14565,19 +14794,19 @@
     <row r="16" spans="1:2" ht="33.75" customHeight="1">
       <c r="A16" s="66"/>
       <c r="B16" s="68" t="s">
-        <v>798</v>
+        <v>828</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="48" customHeight="1">
       <c r="A17" s="66"/>
       <c r="B17" s="68" t="s">
-        <v>799</v>
+        <v>829</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="33.75" customHeight="1">
       <c r="A18" s="66"/>
       <c r="B18" s="68" t="s">
-        <v>800</v>
+        <v>830</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="34.5" customHeight="1">

--- a/public/files/ironbend-buyer-tracker.xlsx
+++ b/public/files/ironbend-buyer-tracker.xlsx
@@ -199,7 +199,7 @@
     <t>VISUAL SUMMARY  —  LIVE CHARTS (LINKED TO BUYER TRACKER)</t>
   </si>
   <si>
-    <t>Chart source data (auto — mirrors the boxes above; do not edit)</t>
+    <t>Chart Data</t>
   </si>
   <si>
     <t>Active</t>
@@ -2587,7 +2587,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <i/>
       <sz val="9"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
@@ -2640,7 +2639,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <i/>
       <sz val="8"/>
       <color rgb="FFBF8F00"/>
       <name val="Arial"/>
@@ -2671,7 +2669,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <i/>
       <sz val="7"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
@@ -2709,7 +2706,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <i/>
       <sz val="8"/>
       <color rgb="FF808080"/>
       <name val="Arial"/>
@@ -2724,7 +2720,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <i/>
       <sz val="7"/>
       <color rgb="FF7F7F7F"/>
       <name val="Arial"/>
@@ -2785,7 +2780,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <i/>
       <sz val="8"/>
       <color rgb="FF7F7F7F"/>
       <name val="Arial"/>
@@ -2799,7 +2793,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <i/>
       <sz val="9"/>
       <color rgb="FF2F5597"/>
       <name val="Arial"/>
@@ -5331,9 +5324,7 @@
     </row>
     <row r="36" spans="1:11" ht="25.5" customHeight="1">
       <c r="A36" s="16"/>
-      <c r="B36" s="83" t="s">
-        <v>823</v>
-      </c>
+      <c r="B36" s="83"/>
       <c r="C36" s="83"/>
       <c r="D36" s="83"/>
       <c r="E36" s="83"/>
@@ -5544,9 +5535,7 @@
       <c r="X1" s="14"/>
     </row>
     <row r="2" spans="1:24" ht="13.5" customHeight="1">
-      <c r="A2" s="86" t="s">
-        <v>808</v>
-      </c>
+      <c r="A2" s="86"/>
       <c r="B2" s="86"/>
       <c r="C2" s="86"/>
       <c r="D2" s="86"/>
@@ -13950,9 +13939,7 @@
       <c r="I24" s="88"/>
     </row>
     <row r="26" spans="1:9" ht="39.75" customHeight="1">
-      <c r="A26" s="91" t="s">
-        <v>714</v>
-      </c>
+      <c r="A26" s="91"/>
       <c r="B26" s="91"/>
       <c r="C26" s="91"/>
       <c r="D26" s="91"/>
@@ -14007,9 +13994,7 @@
       <c r="G1" s="14"/>
     </row>
     <row r="2" spans="1:7" ht="13.5" customHeight="1">
-      <c r="A2" s="13" t="s">
-        <v>716</v>
-      </c>
+      <c r="A2" s="13"/>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
       <c r="D2" s="13"/>
